--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:L108"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,7 +413,7 @@
         <v>תאריך סריקה</v>
       </c>
       <c r="E1" t="str">
-        <v>תיאור</v>
+        <v>שעה</v>
       </c>
       <c r="F1" t="str">
         <v>משך</v>
@@ -448,24 +448,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
         <v>HELP(2)</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>4:19</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>Arctic Monkeys</v>
       </c>
-      <c r="H2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I2" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J2" t="str">
         <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
       </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
         <v>https://music.apple.com/us/album/opening-night/1870313498</v>
       </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
         <v>Opening Night - Arctic Monkeys</v>
       </c>
     </row>
@@ -483,24 +486,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
         <v>Cloud 9</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>3:29</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>Megan Moroney</v>
       </c>
-      <c r="H3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I3" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J3" t="str">
         <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
-      <c r="J3" t="str">
+      <c r="K3" t="str">
         <v>https://music.apple.com/us/album/wish-i-didnt/1851296746</v>
       </c>
-      <c r="K3" t="str">
+      <c r="L3" t="str">
         <v>Wish I Didn't - Megan Moroney</v>
       </c>
     </row>
@@ -518,24 +524,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
         <v>Don't Be Dumb</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>3:44</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>A$AP Rocky</v>
       </c>
-      <c r="H4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I4" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J4" t="str">
         <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
       </c>
-      <c r="J4" t="str">
+      <c r="K4" t="str">
         <v>https://music.apple.com/us/album/air-force-black-demarco/1862934946</v>
       </c>
-      <c r="K4" t="str">
+      <c r="L4" t="str">
         <v>AIR FORCE (BLACK DEMARCO) - A$AP Rocky</v>
       </c>
     </row>
@@ -553,24 +562,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
         <v>Wuthering Heights</v>
       </c>
-      <c r="F5" t="str">
+      <c r="G5" t="str">
         <v>2:24</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
         <v>Charli xcx</v>
       </c>
-      <c r="H5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I5" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J5" t="str">
         <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
       </c>
-      <c r="J5" t="str">
+      <c r="K5" t="str">
         <v>https://music.apple.com/us/album/wall-of-sound/1852566184</v>
       </c>
-      <c r="K5" t="str">
+      <c r="L5" t="str">
         <v>Wall of Sound - Charli xcx</v>
       </c>
     </row>
@@ -588,24 +600,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
         <v>Nothing's About to Happen to Me</v>
       </c>
-      <c r="F6" t="str">
+      <c r="G6" t="str">
         <v>3:09</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>Mitski</v>
       </c>
-      <c r="H6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I6" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J6" t="str">
         <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
-      <c r="J6" t="str">
+      <c r="K6" t="str">
         <v>https://music.apple.com/us/album/wheres-my-phone/1860622550</v>
       </c>
-      <c r="K6" t="str">
+      <c r="L6" t="str">
         <v>Where's My Phone? - Mitski</v>
       </c>
     </row>
@@ -623,24 +638,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
         <v>Do You Still Love Me?</v>
       </c>
-      <c r="F7" t="str">
+      <c r="G7" t="str">
         <v>3:54</v>
       </c>
-      <c r="G7" t="str">
+      <c r="H7" t="str">
         <v>Ella Mai</v>
       </c>
-      <c r="H7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I7" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J7" t="str">
         <v>https://music.apple.com/us/artist/ella-mai/1160482144</v>
       </c>
-      <c r="J7" t="str">
+      <c r="K7" t="str">
         <v>https://music.apple.com/us/album/100/1858754868</v>
       </c>
-      <c r="K7" t="str">
+      <c r="L7" t="str">
         <v>100 - Ella Mai</v>
       </c>
     </row>
@@ -658,24 +676,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
         <v>Por un P*****o no se llora (Salud mi Reina) - Single</v>
       </c>
-      <c r="F8" t="str">
+      <c r="G8" t="str">
         <v>2:31</v>
       </c>
-      <c r="G8" t="str">
+      <c r="H8" t="str">
         <v>Manuel Turizo</v>
       </c>
-      <c r="H8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I8" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J8" t="str">
         <v>https://music.apple.com/us/artist/manuel-turizo/1186116587</v>
       </c>
-      <c r="J8" t="str">
+      <c r="K8" t="str">
         <v>https://music.apple.com/us/album/por-un-p-o-no-se-llora-salud-mi-reina/1862587821</v>
       </c>
-      <c r="K8" t="str">
+      <c r="L8" t="str">
         <v>Por un P*****o no se llora (Salud mi Reina) - Manuel Turizo</v>
       </c>
     </row>
@@ -693,24 +714,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
         <v>Flo Jackson - Single</v>
       </c>
-      <c r="F9" t="str">
+      <c r="G9" t="str">
         <v>2:23</v>
       </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
         <v>Flo Milli</v>
       </c>
-      <c r="H9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I9" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J9" t="str">
         <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
       </c>
-      <c r="J9" t="str">
+      <c r="K9" t="str">
         <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
       </c>
-      <c r="K9" t="str">
+      <c r="L9" t="str">
         <v>Flo Jackson - Flo Milli</v>
       </c>
     </row>
@@ -728,24 +752,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
         <v>Ö</v>
       </c>
-      <c r="F10" t="str">
+      <c r="G10" t="str">
         <v>2:18</v>
       </c>
-      <c r="G10" t="str">
+      <c r="H10" t="str">
         <v>Fcukers</v>
       </c>
-      <c r="H10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I10" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J10" t="str">
         <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
-      <c r="J10" t="str">
+      <c r="K10" t="str">
         <v>https://music.apple.com/us/album/l-u-c-k-y/1861895134</v>
       </c>
-      <c r="K10" t="str">
+      <c r="L10" t="str">
         <v>L.U.C.K.Y - Fcukers</v>
       </c>
     </row>
@@ -763,24 +790,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
         <v>sounds for someone</v>
       </c>
-      <c r="F11" t="str">
+      <c r="G11" t="str">
         <v>3:06</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
         <v>Elmiene</v>
       </c>
-      <c r="H11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I11" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J11" t="str">
         <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
       </c>
-      <c r="J11" t="str">
+      <c r="K11" t="str">
         <v>https://music.apple.com/us/album/reclusive/1860405416</v>
       </c>
-      <c r="K11" t="str">
+      <c r="L11" t="str">
         <v>Reclusive - Elmiene</v>
       </c>
     </row>
@@ -798,24 +828,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
         <v>Creature of Habit</v>
       </c>
-      <c r="F12" t="str">
+      <c r="G12" t="str">
         <v>2:46</v>
       </c>
-      <c r="G12" t="str">
+      <c r="H12" t="str">
         <v>Courtney Barnett</v>
       </c>
-      <c r="H12" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I12" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J12" t="str">
         <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
-      <c r="J12" t="str">
+      <c r="K12" t="str">
         <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
       </c>
-      <c r="K12" t="str">
+      <c r="L12" t="str">
         <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
       </c>
     </row>
@@ -833,24 +866,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
         <v>Megadeth</v>
       </c>
-      <c r="F13" t="str">
+      <c r="G13" t="str">
         <v>4:40</v>
       </c>
-      <c r="G13" t="str">
+      <c r="H13" t="str">
         <v>Megadeth</v>
       </c>
-      <c r="H13" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I13" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J13" t="str">
         <v>https://music.apple.com/us/artist/megadeth/488289</v>
       </c>
-      <c r="J13" t="str">
+      <c r="K13" t="str">
         <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
       </c>
-      <c r="K13" t="str">
+      <c r="L13" t="str">
         <v>Puppet Parade - Megadeth</v>
       </c>
     </row>
@@ -868,24 +904,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
         <v>Cerulean</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
         <v>3:35</v>
       </c>
-      <c r="G14" t="str">
+      <c r="H14" t="str">
         <v>Danny L Harle</v>
       </c>
-      <c r="H14" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I14" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J14" t="str">
         <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
       </c>
-      <c r="J14" t="str">
+      <c r="K14" t="str">
         <v>https://music.apple.com/us/album/raft-in-the-sea/1847662970</v>
       </c>
-      <c r="K14" t="str">
+      <c r="L14" t="str">
         <v>Raft In The Sea - Danny L Harle</v>
       </c>
     </row>
@@ -903,24 +942,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
         <v>Butterfly</v>
       </c>
-      <c r="F15" t="str">
+      <c r="G15" t="str">
         <v>4:21</v>
       </c>
-      <c r="G15" t="str">
+      <c r="H15" t="str">
         <v>Daphni</v>
       </c>
-      <c r="H15" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I15" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J15" t="str">
         <v>https://music.apple.com/us/artist/daphni/1282779393</v>
       </c>
-      <c r="J15" t="str">
+      <c r="K15" t="str">
         <v>https://music.apple.com/us/album/good-night-baby/1849916838</v>
       </c>
-      <c r="K15" t="str">
+      <c r="L15" t="str">
         <v>Good Night Baby - Daphni</v>
       </c>
     </row>
@@ -938,24 +980,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
         <v>CAMBIARÉ - Single</v>
       </c>
-      <c r="F16" t="str">
+      <c r="G16" t="str">
         <v>3:01</v>
       </c>
-      <c r="G16" t="str">
+      <c r="H16" t="str">
         <v>Luis Fonsi</v>
       </c>
-      <c r="H16" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I16" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J16" t="str">
         <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
       </c>
-      <c r="J16" t="str">
+      <c r="K16" t="str">
         <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
       </c>
-      <c r="K16" t="str">
+      <c r="L16" t="str">
         <v>CAMBIARÉ - Luis Fonsi</v>
       </c>
     </row>
@@ -973,24 +1018,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
         <v>The Mountain</v>
       </c>
-      <c r="F17" t="str">
+      <c r="G17" t="str">
         <v>3:28</v>
       </c>
-      <c r="G17" t="str">
+      <c r="H17" t="str">
         <v>Gorillaz</v>
       </c>
-      <c r="H17" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I17" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J17" t="str">
         <v>https://music.apple.com/us/artist/gorillaz/567072</v>
       </c>
-      <c r="J17" t="str">
+      <c r="K17" t="str">
         <v>https://music.apple.com/us/album/orange-county-feat-bizarrap-kara-jackson-anoushka-shankar/1837237742</v>
       </c>
-      <c r="K17" t="str">
+      <c r="L17" t="str">
         <v>Orange County (feat. Bizarrap, Kara Jackson &amp; Anoushka Shankar) - Gorillaz</v>
       </c>
     </row>
@@ -1008,24 +1056,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
         <v>LA 8VA MARAVILLA</v>
       </c>
-      <c r="F18" t="str">
+      <c r="G18" t="str">
         <v>3:24</v>
       </c>
-      <c r="G18" t="str">
+      <c r="H18" t="str">
         <v>Arcángel</v>
       </c>
-      <c r="H18" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I18" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J18" t="str">
         <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
       </c>
-      <c r="J18" t="str">
+      <c r="K18" t="str">
         <v>https://music.apple.com/us/album/lluvia/1868476390</v>
       </c>
-      <c r="K18" t="str">
+      <c r="L18" t="str">
         <v>Lluvia - Arcángel</v>
       </c>
     </row>
@@ -1043,24 +1094,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
         <v>THE SIN : VANISH</v>
       </c>
-      <c r="F19" t="str">
+      <c r="G19" t="str">
         <v>2:19</v>
       </c>
-      <c r="G19" t="str">
+      <c r="H19" t="str">
         <v>ENHYPEN</v>
       </c>
-      <c r="H19" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I19" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J19" t="str">
         <v>https://music.apple.com/us/artist/enhypen/1541011620</v>
       </c>
-      <c r="J19" t="str">
+      <c r="K19" t="str">
         <v>https://music.apple.com/us/album/knife/1862720020</v>
       </c>
-      <c r="K19" t="str">
+      <c r="L19" t="str">
         <v>Knife - ENHYPEN</v>
       </c>
     </row>
@@ -1078,24 +1132,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
         <v>locket</v>
       </c>
-      <c r="F20" t="str">
+      <c r="G20" t="str">
         <v>3:42</v>
       </c>
-      <c r="G20" t="str">
+      <c r="H20" t="str">
         <v>Madison Beer</v>
       </c>
-      <c r="H20" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I20" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J20" t="str">
         <v>https://music.apple.com/us/artist/madison-beer/696146587</v>
       </c>
-      <c r="J20" t="str">
+      <c r="K20" t="str">
         <v>https://music.apple.com/us/album/bad-enough/1846949115</v>
       </c>
-      <c r="K20" t="str">
+      <c r="L20" t="str">
         <v>bad enough - Madison Beer</v>
       </c>
     </row>
@@ -1113,24 +1170,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
         <v>bad - Single</v>
       </c>
-      <c r="F21" t="str">
+      <c r="G21" t="str">
         <v>2:41</v>
       </c>
-      <c r="G21" t="str">
+      <c r="H21" t="str">
         <v>Saint Harison</v>
       </c>
-      <c r="H21" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I21" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J21" t="str">
         <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
-      <c r="J21" t="str">
+      <c r="K21" t="str">
         <v>https://music.apple.com/us/album/bad/1851566879</v>
       </c>
-      <c r="K21" t="str">
+      <c r="L21" t="str">
         <v>bad - Saint Harison</v>
       </c>
     </row>
@@ -1148,24 +1208,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
         <v>Whatever's Clever!</v>
       </c>
-      <c r="F22" t="str">
+      <c r="G22" t="str">
         <v>2:58</v>
       </c>
-      <c r="G22" t="str">
+      <c r="H22" t="str">
         <v>Charlie Puth</v>
       </c>
-      <c r="H22" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I22" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J22" t="str">
         <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
-      <c r="J22" t="str">
+      <c r="K22" t="str">
         <v>https://music.apple.com/us/album/beat-yourself-up/1845189970</v>
       </c>
-      <c r="K22" t="str">
+      <c r="L22" t="str">
         <v>Beat Yourself Up - Charlie Puth</v>
       </c>
     </row>
@@ -1183,24 +1246,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
         <v>luck... or something</v>
       </c>
-      <c r="F23" t="str">
+      <c r="G23" t="str">
         <v>2:52</v>
       </c>
-      <c r="G23" t="str">
+      <c r="H23" t="str">
         <v>Hilary Duff</v>
       </c>
-      <c r="H23" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I23" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J23" t="str">
         <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
       </c>
-      <c r="J23" t="str">
+      <c r="K23" t="str">
         <v>https://music.apple.com/us/album/roommates/1854567102</v>
       </c>
-      <c r="K23" t="str">
+      <c r="L23" t="str">
         <v>Roommates - Hilary Duff</v>
       </c>
     </row>
@@ -1218,24 +1284,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
         <v>Ambiguous Desire</v>
       </c>
-      <c r="F24" t="str">
+      <c r="G24" t="str">
         <v>2:57</v>
       </c>
-      <c r="G24" t="str">
+      <c r="H24" t="str">
         <v>Arlo Parks</v>
       </c>
-      <c r="H24" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I24" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J24" t="str">
         <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
-      <c r="J24" t="str">
+      <c r="K24" t="str">
         <v>https://music.apple.com/us/album/2sided/1862570378</v>
       </c>
-      <c r="K24" t="str">
+      <c r="L24" t="str">
         <v>2SIDED - Arlo Parks</v>
       </c>
     </row>
@@ -1253,24 +1322,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
         <v>ODYSSEY</v>
       </c>
-      <c r="F25" t="str">
+      <c r="G25" t="str">
         <v>2:48</v>
       </c>
-      <c r="G25" t="str">
+      <c r="H25" t="str">
         <v>ILLENIUM</v>
       </c>
-      <c r="H25" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I25" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J25" t="str">
         <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
-      <c r="J25" t="str">
+      <c r="K25" t="str">
         <v>https://music.apple.com/us/album/feel-alive/1851368154</v>
       </c>
-      <c r="K25" t="str">
+      <c r="L25" t="str">
         <v>Feel Alive - ILLENIUM</v>
       </c>
     </row>
@@ -1288,24 +1360,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
         <v>COSMIC OPERA ACT I</v>
       </c>
-      <c r="F26" t="str">
+      <c r="G26" t="str">
         <v>1:14</v>
       </c>
-      <c r="G26" t="str">
+      <c r="H26" t="str">
         <v>Labrinth</v>
       </c>
-      <c r="H26" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I26" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J26" t="str">
         <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
-      <c r="J26" t="str">
+      <c r="K26" t="str">
         <v>https://music.apple.com/us/album/god-spoke/1853069628</v>
       </c>
-      <c r="K26" t="str">
+      <c r="L26" t="str">
         <v>God Spoke - Labrinth</v>
       </c>
     </row>
@@ -1323,24 +1398,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
         <v>El Mundo Es Tuyo (Inspired by Clika The Movie)</v>
       </c>
-      <c r="F27" t="str">
+      <c r="G27" t="str">
         <v>2:35</v>
       </c>
-      <c r="G27" t="str">
+      <c r="H27" t="str">
         <v>Herencia de Patrones</v>
       </c>
-      <c r="H27" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I27" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J27" t="str">
         <v>https://music.apple.com/us/artist/herencia-de-patrones/1295294734</v>
       </c>
-      <c r="J27" t="str">
+      <c r="K27" t="str">
         <v>https://music.apple.com/us/album/risk-takers/1866642665</v>
       </c>
-      <c r="K27" t="str">
+      <c r="L27" t="str">
         <v>Risk Takers - Herencia de Patrones</v>
       </c>
     </row>
@@ -1358,24 +1436,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
         <v>Never Comin' Back - Single</v>
       </c>
-      <c r="F28" t="str">
+      <c r="G28" t="str">
         <v>3:57</v>
       </c>
-      <c r="G28" t="str">
+      <c r="H28" t="str">
         <v>Flatland Cavalry</v>
       </c>
-      <c r="H28" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I28" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J28" t="str">
         <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
-      <c r="J28" t="str">
+      <c r="K28" t="str">
         <v>https://music.apple.com/us/album/never-comin-back/1862970555</v>
       </c>
-      <c r="K28" t="str">
+      <c r="L28" t="str">
         <v>Never Comin' Back - Flatland Cavalry</v>
       </c>
     </row>
@@ -1393,24 +1474,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
         <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II)) - Single</v>
       </c>
-      <c r="F29" t="str">
+      <c r="G29" t="str">
         <v>3:18</v>
       </c>
-      <c r="G29" t="str">
+      <c r="H29" t="str">
         <v>Carter Faith</v>
       </c>
-      <c r="H29" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I29" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J29" t="str">
         <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
       </c>
-      <c r="J29" t="str">
+      <c r="K29" t="str">
         <v>https://music.apple.com/us/album/lay-your-heartache-onto-mine-songs-from-and-inspired/1867273471</v>
       </c>
-      <c r="K29" t="str">
+      <c r="L29" t="str">
         <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II)) - Carter Faith</v>
       </c>
     </row>
@@ -1428,24 +1512,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
         <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
       </c>
-      <c r="F30" t="str">
+      <c r="G30" t="str">
         <v>3:47</v>
       </c>
-      <c r="G30" t="str">
+      <c r="H30" t="str">
         <v>Dolly Parton</v>
       </c>
-      <c r="H30" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I30" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J30" t="str">
         <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
       </c>
-      <c r="J30" t="str">
+      <c r="K30" t="str">
         <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
       </c>
-      <c r="K30" t="str">
+      <c r="L30" t="str">
         <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
       </c>
     </row>
@@ -1463,24 +1550,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
         <v>Honora</v>
       </c>
-      <c r="F31" t="str">
+      <c r="G31" t="str">
         <v>5:41</v>
       </c>
-      <c r="G31" t="str">
+      <c r="H31" t="str">
         <v>Flea</v>
       </c>
-      <c r="H31" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I31" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J31" t="str">
         <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
-      <c r="J31" t="str">
+      <c r="K31" t="str">
         <v>https://music.apple.com/us/album/traffic-lights-feat-thom-yorke/1861644307</v>
       </c>
-      <c r="K31" t="str">
+      <c r="L31" t="str">
         <v>Traffic Lights (feat. Thom Yorke) - Flea</v>
       </c>
     </row>
@@ -1498,24 +1588,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
         <v>Heated Rivalry (Original Series Soundtrack)</v>
       </c>
-      <c r="F32" t="str">
+      <c r="G32" t="str">
         <v>4:26</v>
       </c>
-      <c r="G32" t="str">
+      <c r="H32" t="str">
         <v>Peter Peter</v>
       </c>
-      <c r="H32" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I32" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J32" t="str">
         <v>https://music.apple.com/us/artist/peter-peter/71305428</v>
       </c>
-      <c r="J32" t="str">
+      <c r="K32" t="str">
         <v>https://music.apple.com/us/album/inferno-from-heated-rivalry/1868783596</v>
       </c>
-      <c r="K32" t="str">
+      <c r="L32" t="str">
         <v>Inferno (from "Heated Rivalry") - Peter Peter</v>
       </c>
     </row>
@@ -1533,24 +1626,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
         <v>Kora - Single</v>
       </c>
-      <c r="F33" t="str">
+      <c r="G33" t="str">
         <v>2:00</v>
       </c>
-      <c r="G33" t="str">
+      <c r="H33" t="str">
         <v>Skrillex</v>
       </c>
-      <c r="H33" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I33" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J33" t="str">
         <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
-      <c r="J33" t="str">
+      <c r="K33" t="str">
         <v>https://music.apple.com/us/album/yo-yan/1867888650</v>
       </c>
-      <c r="K33" t="str">
+      <c r="L33" t="str">
         <v>Yo Yan - Skrillex</v>
       </c>
     </row>
@@ -1568,24 +1664,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
         <v>REAL, Vol. 1 - EP</v>
       </c>
-      <c r="F34" t="str">
+      <c r="G34" t="str">
         <v>3:08</v>
       </c>
-      <c r="G34" t="str">
+      <c r="H34" t="str">
         <v>Wizkid</v>
       </c>
-      <c r="H34" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I34" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J34" t="str">
         <v>https://music.apple.com/us/artist/wizkid/309335750</v>
       </c>
-      <c r="J34" t="str">
+      <c r="K34" t="str">
         <v>https://music.apple.com/us/album/jogodo/1867908237</v>
       </c>
-      <c r="K34" t="str">
+      <c r="L34" t="str">
         <v>Jogodo - Wizkid</v>
       </c>
     </row>
@@ -1603,24 +1702,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
         <v>Suffering From Success</v>
       </c>
-      <c r="F35" t="str">
+      <c r="G35" t="str">
         <v>3:00</v>
       </c>
-      <c r="G35" t="str">
+      <c r="H35" t="str">
         <v>Dee Mula</v>
       </c>
-      <c r="H35" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I35" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J35" t="str">
         <v>https://music.apple.com/us/artist/dee-mula/1330325377</v>
       </c>
-      <c r="J35" t="str">
+      <c r="K35" t="str">
         <v>https://music.apple.com/us/album/made-it-out-alive/1867596343</v>
       </c>
-      <c r="K35" t="str">
+      <c r="L35" t="str">
         <v>Made It Out Alive - Dee Mula</v>
       </c>
     </row>
@@ -1638,24 +1740,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
         <v>One of Them Ones - Single</v>
       </c>
-      <c r="F36" t="str">
+      <c r="G36" t="str">
         <v>3:05</v>
       </c>
-      <c r="G36" t="str">
+      <c r="H36" t="str">
         <v>Veeze</v>
       </c>
-      <c r="H36" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I36" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J36" t="str">
         <v>https://music.apple.com/us/artist/veeze/1464999308</v>
       </c>
-      <c r="J36" t="str">
+      <c r="K36" t="str">
         <v>https://music.apple.com/us/album/one-of-them-ones/1868850364</v>
       </c>
-      <c r="K36" t="str">
+      <c r="L36" t="str">
         <v>One of Them Ones - Veeze</v>
       </c>
     </row>
@@ -1673,24 +1778,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
         <v>Como Es Que Se Hace - Single</v>
       </c>
-      <c r="F37" t="str">
+      <c r="G37" t="str">
         <v>3:25</v>
       </c>
-      <c r="G37" t="str">
+      <c r="H37" t="str">
         <v>Yandel</v>
       </c>
-      <c r="H37" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I37" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J37" t="str">
         <v>https://music.apple.com/us/artist/yandel/72929426</v>
       </c>
-      <c r="J37" t="str">
+      <c r="K37" t="str">
         <v>https://music.apple.com/us/album/como-es-que-se-hace/1864227582</v>
       </c>
-      <c r="K37" t="str">
+      <c r="L37" t="str">
         <v>Como Es Que Se Hace - Yandel</v>
       </c>
     </row>
@@ -1708,24 +1816,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
         <v>Coke Wave 3.5: Narcos</v>
       </c>
-      <c r="F38" t="str">
+      <c r="G38" t="str">
         <v>2:16</v>
       </c>
-      <c r="G38" t="str">
+      <c r="H38" t="str">
         <v>French Montana</v>
       </c>
-      <c r="H38" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I38" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J38" t="str">
         <v>https://music.apple.com/us/artist/french-montana/475816358</v>
       </c>
-      <c r="J38" t="str">
+      <c r="K38" t="str">
         <v>https://music.apple.com/us/album/ever-since-u-left-me-i-went-deaf/1863124168</v>
       </c>
-      <c r="K38" t="str">
+      <c r="L38" t="str">
         <v>Ever Since U Left Me (I Went Deaf) - French Montana</v>
       </c>
     </row>
@@ -1743,24 +1854,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
         <v>Ay Dale - Single</v>
       </c>
-      <c r="F39" t="str">
+      <c r="G39" t="str">
         <v>2:26</v>
       </c>
-      <c r="G39" t="str">
+      <c r="H39" t="str">
         <v>Farruko</v>
       </c>
-      <c r="H39" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I39" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J39" t="str">
         <v>https://music.apple.com/us/artist/farruko/364377482</v>
       </c>
-      <c r="J39" t="str">
+      <c r="K39" t="str">
         <v>https://music.apple.com/us/album/ay-dale/1862897623</v>
       </c>
-      <c r="K39" t="str">
+      <c r="L39" t="str">
         <v>Ay Dale - Farruko</v>
       </c>
     </row>
@@ -1778,24 +1892,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
         <v>Slime Cry</v>
       </c>
-      <c r="F40" t="str">
+      <c r="G40" t="str">
         <v>2:45</v>
       </c>
-      <c r="G40" t="str">
+      <c r="H40" t="str">
         <v>YoungBoy Never Broke Again</v>
       </c>
-      <c r="H40" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I40" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J40" t="str">
         <v>https://music.apple.com/us/artist/youngboy-never-broke-again/1168822104</v>
       </c>
-      <c r="J40" t="str">
+      <c r="K40" t="str">
         <v>https://music.apple.com/us/album/teary-eyes/1869534167</v>
       </c>
-      <c r="K40" t="str">
+      <c r="L40" t="str">
         <v>Teary Eyes - YoungBoy Never Broke Again</v>
       </c>
     </row>
@@ -1813,24 +1930,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
         <v>KUNTOLOGY 101</v>
       </c>
-      <c r="F41" t="str">
+      <c r="G41" t="str">
         <v>2:50</v>
       </c>
-      <c r="G41" t="str">
+      <c r="H41" t="str">
         <v>Aliyah's Interlude</v>
       </c>
-      <c r="H41" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I41" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J41" t="str">
         <v>https://music.apple.com/us/artist/aliyahs-interlude/1708765232</v>
       </c>
-      <c r="J41" t="str">
+      <c r="K41" t="str">
         <v>https://music.apple.com/us/album/bop-it/1867023466</v>
       </c>
-      <c r="K41" t="str">
+      <c r="L41" t="str">
         <v>Bop It - Aliyah's Interlude</v>
       </c>
     </row>
@@ -1848,24 +1968,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
         <v>My Everything - Single</v>
       </c>
-      <c r="F42" t="str">
+      <c r="G42" t="str">
         <v>2:33</v>
       </c>
-      <c r="G42" t="str">
+      <c r="H42" t="str">
         <v>Lecrae</v>
       </c>
-      <c r="H42" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I42" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J42" t="str">
         <v>https://music.apple.com/us/artist/lecrae/130043072</v>
       </c>
-      <c r="J42" t="str">
+      <c r="K42" t="str">
         <v>https://music.apple.com/us/album/my-everything/1862940301</v>
       </c>
-      <c r="K42" t="str">
+      <c r="L42" t="str">
         <v>My Everything - Lecrae</v>
       </c>
     </row>
@@ -1883,24 +2006,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
         <v>Nat &amp; Alex Wolff</v>
       </c>
-      <c r="F43" t="str">
+      <c r="G43" t="str">
         <v>3:30</v>
       </c>
-      <c r="G43" t="str">
+      <c r="H43" t="str">
         <v>Nat &amp; Alex Wolff</v>
       </c>
-      <c r="H43" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I43" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J43" t="str">
         <v>https://music.apple.com/us/artist/nat-alex-wolff/470903139</v>
       </c>
-      <c r="J43" t="str">
+      <c r="K43" t="str">
         <v>https://music.apple.com/us/album/whole-other-life/1858374775</v>
       </c>
-      <c r="K43" t="str">
+      <c r="L43" t="str">
         <v>Whole Other Life - Nat &amp; Alex Wolff</v>
       </c>
     </row>
@@ -1918,24 +2044,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
         <v>Belladona</v>
       </c>
-      <c r="F44" t="str">
+      <c r="G44" t="str">
         <v>3:32</v>
       </c>
-      <c r="G44" t="str">
+      <c r="H44" t="str">
         <v>Kenia Os</v>
       </c>
-      <c r="H44" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I44" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J44" t="str">
         <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
-      <c r="J44" t="str">
+      <c r="K44" t="str">
         <v>https://music.apple.com/us/album/belladona/1862538030</v>
       </c>
-      <c r="K44" t="str">
+      <c r="L44" t="str">
         <v>Belladona - Kenia Os</v>
       </c>
     </row>
@@ -1953,24 +2082,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
         <v>Addicted to Love (From "Tell Me Lies (Season 3)") - Single</v>
       </c>
-      <c r="F45" t="str">
+      <c r="G45" t="str">
         <v>3:05</v>
       </c>
-      <c r="G45" t="str">
+      <c r="H45" t="str">
         <v>CHVRCHES</v>
       </c>
-      <c r="H45" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I45" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J45" t="str">
         <v>https://music.apple.com/us/artist/chvrches/566867492</v>
       </c>
-      <c r="J45" t="str">
+      <c r="K45" t="str">
         <v>https://music.apple.com/us/album/addicted-to-love-from-tell-me-lies-season-3/1867024879</v>
       </c>
-      <c r="K45" t="str">
+      <c r="L45" t="str">
         <v>Addicted to Love (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
       </c>
     </row>
@@ -1988,24 +2120,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
         <v>Lie2Me - Single</v>
       </c>
-      <c r="F46" t="str">
+      <c r="G46" t="str">
         <v>3:03</v>
       </c>
-      <c r="G46" t="str">
+      <c r="H46" t="str">
         <v>DC THE DON</v>
       </c>
-      <c r="H46" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I46" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J46" t="str">
         <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
       </c>
-      <c r="J46" t="str">
+      <c r="K46" t="str">
         <v>https://music.apple.com/us/album/lie2me/1862762674</v>
       </c>
-      <c r="K46" t="str">
+      <c r="L46" t="str">
         <v>Lie2Me - DC THE DON</v>
       </c>
     </row>
@@ -2023,24 +2158,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
         <v>High On Heaven - Single</v>
       </c>
-      <c r="F47" t="str">
+      <c r="G47" t="str">
         <v>3:19</v>
       </c>
-      <c r="G47" t="str">
+      <c r="H47" t="str">
         <v>Nessa Barrett</v>
       </c>
-      <c r="H47" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I47" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J47" t="str">
         <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
-      <c r="J47" t="str">
+      <c r="K47" t="str">
         <v>https://music.apple.com/us/album/high-on-heaven/1859071764</v>
       </c>
-      <c r="K47" t="str">
+      <c r="L47" t="str">
         <v>High On Heaven - Nessa Barrett</v>
       </c>
     </row>
@@ -2058,24 +2196,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
         <v>My Ego Told Me To</v>
       </c>
-      <c r="F48" t="str">
+      <c r="G48" t="str">
         <v>2:15</v>
       </c>
-      <c r="G48" t="str">
+      <c r="H48" t="str">
         <v>Leigh-Anne</v>
       </c>
-      <c r="H48" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I48" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J48" t="str">
         <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
       </c>
-      <c r="J48" t="str">
+      <c r="K48" t="str">
         <v>https://music.apple.com/us/album/most-wanted/1844865923</v>
       </c>
-      <c r="K48" t="str">
+      <c r="L48" t="str">
         <v>Most Wanted - Leigh-Anne</v>
       </c>
     </row>
@@ -2093,24 +2234,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
         <v>Charlie The Wonderdog (Original Songs from the Motion Picture) - Single</v>
       </c>
-      <c r="F49" t="str">
+      <c r="G49" t="str">
         <v>2:57</v>
       </c>
-      <c r="G49" t="str">
+      <c r="H49" t="str">
         <v>Bryan Adams</v>
       </c>
-      <c r="H49" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I49" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J49" t="str">
         <v>https://music.apple.com/us/artist/bryan-adams/85932</v>
       </c>
-      <c r="J49" t="str">
+      <c r="K49" t="str">
         <v>https://music.apple.com/us/album/anything-is-possible/1867583221</v>
       </c>
-      <c r="K49" t="str">
+      <c r="L49" t="str">
         <v>Anything Is Possible - Bryan Adams</v>
       </c>
     </row>
@@ -2128,24 +2272,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
         <v>Volcano - Single</v>
       </c>
-      <c r="F50" t="str">
+      <c r="G50" t="str">
         <v>2:28</v>
       </c>
-      <c r="G50" t="str">
+      <c r="H50" t="str">
         <v>Girl Tones</v>
       </c>
-      <c r="H50" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I50" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J50" t="str">
         <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
       </c>
-      <c r="J50" t="str">
+      <c r="K50" t="str">
         <v>https://music.apple.com/us/album/volcano/1862739923</v>
       </c>
-      <c r="K50" t="str">
+      <c r="L50" t="str">
         <v>Volcano - Girl Tones</v>
       </c>
     </row>
@@ -2163,24 +2310,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
         <v>Into Oblivion</v>
       </c>
-      <c r="F51" t="str">
+      <c r="G51" t="str">
         <v>3:34</v>
       </c>
-      <c r="G51" t="str">
+      <c r="H51" t="str">
         <v>Lamb of God</v>
       </c>
-      <c r="H51" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I51" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J51" t="str">
         <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
-      <c r="J51" t="str">
+      <c r="K51" t="str">
         <v>https://music.apple.com/us/album/into-oblivion/1868804163</v>
       </c>
-      <c r="K51" t="str">
+      <c r="L51" t="str">
         <v>Into Oblivion - Lamb of God</v>
       </c>
     </row>
@@ -2198,24 +2348,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
         <v>Listen Up!</v>
       </c>
-      <c r="F52" t="str">
+      <c r="G52" t="str">
         <v>3:19</v>
       </c>
-      <c r="G52" t="str">
+      <c r="H52" t="str">
         <v>New Found Glory</v>
       </c>
-      <c r="H52" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I52" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J52" t="str">
         <v>https://music.apple.com/us/artist/new-found-glory/65551</v>
       </c>
-      <c r="J52" t="str">
+      <c r="K52" t="str">
         <v>https://music.apple.com/us/album/beer-and-blood-stains/1838991916</v>
       </c>
-      <c r="K52" t="str">
+      <c r="L52" t="str">
         <v>Beer and Blood Stains - New Found Glory</v>
       </c>
     </row>
@@ -2233,24 +2386,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
         <v>Numb - Single</v>
       </c>
-      <c r="F53" t="str">
+      <c r="G53" t="str">
         <v>2:13</v>
       </c>
-      <c r="G53" t="str">
+      <c r="H53" t="str">
         <v>Marc E. Bassy</v>
       </c>
-      <c r="H53" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I53" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J53" t="str">
         <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
       </c>
-      <c r="J53" t="str">
+      <c r="K53" t="str">
         <v>https://music.apple.com/us/album/numb/1860136319</v>
       </c>
-      <c r="K53" t="str">
+      <c r="L53" t="str">
         <v>Numb - Marc E. Bassy</v>
       </c>
     </row>
@@ -2268,24 +2424,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
         <v>Saputjiji</v>
       </c>
-      <c r="F54" t="str">
+      <c r="G54" t="str">
         <v>1:33</v>
       </c>
-      <c r="G54" t="str">
+      <c r="H54" t="str">
         <v>Tanya Tagaq</v>
       </c>
-      <c r="H54" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I54" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J54" t="str">
         <v>https://music.apple.com/us/artist/tanya-tagaq/257545265</v>
       </c>
-      <c r="J54" t="str">
+      <c r="K54" t="str">
         <v>https://music.apple.com/us/album/foxtrot/1860109752</v>
       </c>
-      <c r="K54" t="str">
+      <c r="L54" t="str">
         <v>Foxtrot - Tanya Tagaq</v>
       </c>
     </row>
@@ -2303,24 +2462,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
         <v>Stand On My Shoulders</v>
       </c>
-      <c r="F55" t="str">
+      <c r="G55" t="str">
         <v>3:45</v>
       </c>
-      <c r="G55" t="str">
+      <c r="H55" t="str">
         <v>Ya Tseen</v>
       </c>
-      <c r="H55" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I55" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J55" t="str">
         <v>https://music.apple.com/us/artist/ya-tseen/1549782831</v>
       </c>
-      <c r="J55" t="str">
+      <c r="K55" t="str">
         <v>https://music.apple.com/us/album/digital-winter/1820332224</v>
       </c>
-      <c r="K55" t="str">
+      <c r="L55" t="str">
         <v>Digital Winter - Ya Tseen</v>
       </c>
     </row>
@@ -2338,24 +2500,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
         <v>Porcelain</v>
       </c>
-      <c r="F56" t="str">
+      <c r="G56" t="str">
         <v>3:10</v>
       </c>
-      <c r="G56" t="str">
+      <c r="H56" t="str">
         <v>Peach PRC</v>
       </c>
-      <c r="H56" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I56" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J56" t="str">
         <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
       </c>
-      <c r="J56" t="str">
+      <c r="K56" t="str">
         <v>https://music.apple.com/us/album/back-to-you/1861380240</v>
       </c>
-      <c r="K56" t="str">
+      <c r="L56" t="str">
         <v>Back To You - Peach PRC</v>
       </c>
     </row>
@@ -2373,24 +2538,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
         <v>Dreamer+</v>
       </c>
-      <c r="F57" t="str">
+      <c r="G57" t="str">
         <v>3:22</v>
       </c>
-      <c r="G57" t="str">
+      <c r="H57" t="str">
         <v>Sassy 009</v>
       </c>
-      <c r="H57" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I57" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J57" t="str">
         <v>https://music.apple.com/us/artist/sassy-009/1277035471</v>
       </c>
-      <c r="J57" t="str">
+      <c r="K57" t="str">
         <v>https://music.apple.com/us/album/sleepwalkers-pendulum/1826114506</v>
       </c>
-      <c r="K57" t="str">
+      <c r="L57" t="str">
         <v>Sleepwalker's Pendulum - Sassy 009</v>
       </c>
     </row>
@@ -2408,24 +2576,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
         <v>HEAD FIRST - EP</v>
       </c>
-      <c r="F58" t="str">
+      <c r="G58" t="str">
         <v>2:31</v>
       </c>
-      <c r="G58" t="str">
+      <c r="H58" t="str">
         <v>Corbyn Besson</v>
       </c>
-      <c r="H58" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I58" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J58" t="str">
         <v>https://music.apple.com/us/artist/corbyn-besson/810434797</v>
       </c>
-      <c r="J58" t="str">
+      <c r="K58" t="str">
         <v>https://music.apple.com/us/album/ruin-me/1850741514</v>
       </c>
-      <c r="K58" t="str">
+      <c r="L58" t="str">
         <v>Ruin Me - Corbyn Besson</v>
       </c>
     </row>
@@ -2443,24 +2614,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
         <v>the apple tree under the sea</v>
       </c>
-      <c r="F59" t="str">
+      <c r="G59" t="str">
         <v>4:26</v>
       </c>
-      <c r="G59" t="str">
+      <c r="H59" t="str">
         <v>hemlocke springs</v>
       </c>
-      <c r="H59" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I59" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J59" t="str">
         <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
-      <c r="J59" t="str">
+      <c r="K59" t="str">
         <v>https://music.apple.com/us/album/w-w-w-w-w/1846462383</v>
       </c>
-      <c r="K59" t="str">
+      <c r="L59" t="str">
         <v>w-w-w-w-w - hemlocke springs</v>
       </c>
     </row>
@@ -2478,24 +2652,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
         <v>Struggle Bus - Single</v>
       </c>
-      <c r="F60" t="str">
+      <c r="G60" t="str">
         <v>3:20</v>
       </c>
-      <c r="G60" t="str">
+      <c r="H60" t="str">
         <v>Iris Copperman</v>
       </c>
-      <c r="H60" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I60" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J60" t="str">
         <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
       </c>
-      <c r="J60" t="str">
+      <c r="K60" t="str">
         <v>https://music.apple.com/us/album/struggle-bus/1862024075</v>
       </c>
-      <c r="K60" t="str">
+      <c r="L60" t="str">
         <v>Struggle Bus - Iris Copperman</v>
       </c>
     </row>
@@ -2513,24 +2690,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
         <v>Over - Single</v>
       </c>
-      <c r="F61" t="str">
+      <c r="G61" t="str">
         <v>3:49</v>
       </c>
-      <c r="G61" t="str">
+      <c r="H61" t="str">
         <v>Sydney Rose</v>
       </c>
-      <c r="H61" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I61" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J61" t="str">
         <v>https://music.apple.com/us/artist/sydney-rose/354936789</v>
       </c>
-      <c r="J61" t="str">
+      <c r="K61" t="str">
         <v>https://music.apple.com/us/album/over/1862351811</v>
       </c>
-      <c r="K61" t="str">
+      <c r="L61" t="str">
         <v>Over - Sydney Rose</v>
       </c>
     </row>
@@ -2548,24 +2728,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
         <v>Lean - Single</v>
       </c>
-      <c r="F62" t="str">
+      <c r="G62" t="str">
         <v>3:53</v>
       </c>
-      <c r="G62" t="str">
+      <c r="H62" t="str">
         <v>Charlotte Day Wilson</v>
       </c>
-      <c r="H62" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I62" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J62" t="str">
         <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
       </c>
-      <c r="J62" t="str">
+      <c r="K62" t="str">
         <v>https://music.apple.com/us/album/lean/1862829538</v>
       </c>
-      <c r="K62" t="str">
+      <c r="L62" t="str">
         <v>Lean - Charlotte Day Wilson</v>
       </c>
     </row>
@@ -2583,24 +2766,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
         <v>F**k It Up - EP</v>
       </c>
-      <c r="F63" t="str">
+      <c r="G63" t="str">
         <v>3:32</v>
       </c>
-      <c r="G63" t="str">
+      <c r="H63" t="str">
         <v>Master Peace</v>
       </c>
-      <c r="H63" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I63" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J63" t="str">
         <v>https://music.apple.com/us/artist/master-peace/1477196856</v>
       </c>
-      <c r="J63" t="str">
+      <c r="K63" t="str">
         <v>https://music.apple.com/us/album/f-k-it-up/1849002928</v>
       </c>
-      <c r="K63" t="str">
+      <c r="L63" t="str">
         <v>F**k It Up - Master Peace</v>
       </c>
     </row>
@@ -2618,24 +2804,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
         <v>La Carrera - Single</v>
       </c>
-      <c r="F64" t="str">
+      <c r="G64" t="str">
         <v>3:40</v>
       </c>
-      <c r="G64" t="str">
+      <c r="H64" t="str">
         <v>Moa Rivera</v>
       </c>
-      <c r="H64" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I64" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J64" t="str">
         <v>https://music.apple.com/us/artist/moa-rivera/1636808812</v>
       </c>
-      <c r="J64" t="str">
+      <c r="K64" t="str">
         <v>https://music.apple.com/us/album/la-carrera/1863188474</v>
       </c>
-      <c r="K64" t="str">
+      <c r="L64" t="str">
         <v>La Carrera - Moa Rivera</v>
       </c>
     </row>
@@ -2653,24 +2842,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
         <v>No Lube So Rude</v>
       </c>
-      <c r="F65" t="str">
+      <c r="G65" t="str">
         <v>2:48</v>
       </c>
-      <c r="G65" t="str">
+      <c r="H65" t="str">
         <v>Peaches</v>
       </c>
-      <c r="H65" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I65" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J65" t="str">
         <v>https://music.apple.com/us/artist/peaches/3028600</v>
       </c>
-      <c r="J65" t="str">
+      <c r="K65" t="str">
         <v>https://music.apple.com/us/album/no-lube-so-rude/1856064995</v>
       </c>
-      <c r="K65" t="str">
+      <c r="L65" t="str">
         <v>No Lube So Rude - Peaches</v>
       </c>
     </row>
@@ -2688,24 +2880,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
         <v>Somersaults</v>
       </c>
-      <c r="F66" t="str">
+      <c r="G66" t="str">
         <v>4:32</v>
       </c>
-      <c r="G66" t="str">
+      <c r="H66" t="str">
         <v>deathcrash</v>
       </c>
-      <c r="H66" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I66" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J66" t="str">
         <v>https://music.apple.com/us/artist/deathcrash/1461469738</v>
       </c>
-      <c r="J66" t="str">
+      <c r="K66" t="str">
         <v>https://music.apple.com/us/album/somersaults/1847159406</v>
       </c>
-      <c r="K66" t="str">
+      <c r="L66" t="str">
         <v>Somersaults - deathcrash</v>
       </c>
     </row>
@@ -2723,24 +2918,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
         <v>Almost There</v>
       </c>
-      <c r="F67" t="str">
+      <c r="G67" t="str">
         <v>3:52</v>
       </c>
-      <c r="G67" t="str">
+      <c r="H67" t="str">
         <v>The Academy Is...</v>
       </c>
-      <c r="H67" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I67" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J67" t="str">
         <v>https://music.apple.com/us/artist/the-academy-is/75024274</v>
       </c>
-      <c r="J67" t="str">
+      <c r="K67" t="str">
         <v>https://music.apple.com/us/album/2005/1854873133</v>
       </c>
-      <c r="K67" t="str">
+      <c r="L67" t="str">
         <v>2005 - The Academy Is...</v>
       </c>
     </row>
@@ -2758,24 +2956,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
         <v>Palm Royale Season 2 (Apple TV Original Series Soundtrack)</v>
       </c>
-      <c r="F68" t="str">
+      <c r="G68" t="str">
         <v>4:14</v>
       </c>
-      <c r="G68" t="str">
+      <c r="H68" t="str">
         <v>Kristen Wiig</v>
       </c>
-      <c r="H68" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I68" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J68" t="str">
         <v>https://music.apple.com/us/artist/kristen-wiig/273077223</v>
       </c>
-      <c r="J68" t="str">
+      <c r="K68" t="str">
         <v>https://music.apple.com/us/album/i-had-a-ball/1863330900</v>
       </c>
-      <c r="K68" t="str">
+      <c r="L68" t="str">
         <v>I Had a Ball - Kristen Wiig</v>
       </c>
     </row>
@@ -2793,24 +2994,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
         <v>IDB - Single</v>
       </c>
-      <c r="F69" t="str">
+      <c r="G69" t="str">
         <v>2:52</v>
       </c>
-      <c r="G69" t="str">
+      <c r="H69" t="str">
         <v>42 Dugg</v>
       </c>
-      <c r="H69" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I69" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J69" t="str">
         <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
       </c>
-      <c r="J69" t="str">
+      <c r="K69" t="str">
         <v>https://music.apple.com/us/album/idb/1859084147</v>
       </c>
-      <c r="K69" t="str">
+      <c r="L69" t="str">
         <v>IDB - 42 Dugg</v>
       </c>
     </row>
@@ -2828,24 +3032,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
         <v>Feel This Way - Single</v>
       </c>
-      <c r="F70" t="str">
+      <c r="G70" t="str">
         <v>3:04</v>
       </c>
-      <c r="G70" t="str">
+      <c r="H70" t="str">
         <v>Josh Baker</v>
       </c>
-      <c r="H70" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I70" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J70" t="str">
         <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
       </c>
-      <c r="J70" t="str">
+      <c r="K70" t="str">
         <v>https://music.apple.com/us/album/feel-this-way/1862902476</v>
       </c>
-      <c r="K70" t="str">
+      <c r="L70" t="str">
         <v>Feel This Way - Josh Baker</v>
       </c>
     </row>
@@ -2863,24 +3070,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
         <v>Falling - Single</v>
       </c>
-      <c r="F71" t="str">
+      <c r="G71" t="str">
         <v>3:02</v>
       </c>
-      <c r="G71" t="str">
+      <c r="H71" t="str">
         <v>Shimza</v>
       </c>
-      <c r="H71" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I71" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J71" t="str">
         <v>https://music.apple.com/us/artist/shimza/697739898</v>
       </c>
-      <c r="J71" t="str">
+      <c r="K71" t="str">
         <v>https://music.apple.com/us/album/falling/1861598106</v>
       </c>
-      <c r="K71" t="str">
+      <c r="L71" t="str">
         <v>Falling - Shimza</v>
       </c>
     </row>
@@ -2898,24 +3108,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
         <v>Heavy On The Soul</v>
       </c>
-      <c r="F72" t="str">
+      <c r="G72" t="str">
         <v>3:37</v>
       </c>
-      <c r="G72" t="str">
+      <c r="H72" t="str">
         <v>Ty Myers</v>
       </c>
-      <c r="H72" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I72" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J72" t="str">
         <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
-      <c r="J72" t="str">
+      <c r="K72" t="str">
         <v>https://music.apple.com/us/album/message-to-you/1867275110</v>
       </c>
-      <c r="K72" t="str">
+      <c r="L72" t="str">
         <v>Message to You - Ty Myers</v>
       </c>
     </row>
@@ -2933,24 +3146,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
         <v>NOTHING IS REAL - Single</v>
       </c>
-      <c r="F73" t="str">
+      <c r="G73" t="str">
         <v>3:06</v>
       </c>
-      <c r="G73" t="str">
+      <c r="H73" t="str">
         <v>DESTIN CONRAD</v>
       </c>
-      <c r="H73" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I73" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J73" t="str">
         <v>https://music.apple.com/us/artist/destin-conrad/852999989</v>
       </c>
-      <c r="J73" t="str">
+      <c r="K73" t="str">
         <v>https://music.apple.com/us/album/nothing-is-real/1866859497</v>
       </c>
-      <c r="K73" t="str">
+      <c r="L73" t="str">
         <v>NOTHING IS REAL - DESTIN CONRAD</v>
       </c>
     </row>
@@ -2968,24 +3184,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
         <v>CUÉNTAME - Single</v>
       </c>
-      <c r="F74" t="str">
+      <c r="G74" t="str">
         <v>2:42</v>
       </c>
-      <c r="G74" t="str">
+      <c r="H74" t="str">
         <v>FloyyMenor</v>
       </c>
-      <c r="H74" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I74" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J74" t="str">
         <v>https://music.apple.com/us/artist/floyymenor/1676497551</v>
       </c>
-      <c r="J74" t="str">
+      <c r="K74" t="str">
         <v>https://music.apple.com/us/album/cu%C3%A9ntame/1862973853</v>
       </c>
-      <c r="K74" t="str">
+      <c r="L74" t="str">
         <v>CUÉNTAME - FloyyMenor</v>
       </c>
     </row>
@@ -3003,24 +3222,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
         <v>WOR$T GIRL IN AMERICA</v>
       </c>
-      <c r="F75" t="str">
+      <c r="G75" t="str">
         <v>4:47</v>
       </c>
-      <c r="G75" t="str">
+      <c r="H75" t="str">
         <v>Slayyyter</v>
       </c>
-      <c r="H75" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I75" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J75" t="str">
         <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
-      <c r="J75" t="str">
+      <c r="K75" t="str">
         <v>https://music.apple.com/us/album/dance/1867530577</v>
       </c>
-      <c r="K75" t="str">
+      <c r="L75" t="str">
         <v>DANCE... - Slayyyter</v>
       </c>
     </row>
@@ -3038,24 +3260,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
         <v>welcome to the circus - Single</v>
       </c>
-      <c r="F76" t="str">
+      <c r="G76" t="str">
         <v>2:29</v>
       </c>
-      <c r="G76" t="str">
+      <c r="H76" t="str">
         <v>Jagwar Twin</v>
       </c>
-      <c r="H76" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I76" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J76" t="str">
         <v>https://music.apple.com/us/artist/jagwar-twin/1429051937</v>
       </c>
-      <c r="J76" t="str">
+      <c r="K76" t="str">
         <v>https://music.apple.com/us/album/welcome-to-the-circus/1861011603</v>
       </c>
-      <c r="K76" t="str">
+      <c r="L76" t="str">
         <v>welcome to the circus - Jagwar Twin</v>
       </c>
     </row>
@@ -3073,24 +3298,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
         <v>playlist - Single</v>
       </c>
-      <c r="F77" t="str">
+      <c r="G77" t="str">
         <v>2:44</v>
       </c>
-      <c r="G77" t="str">
+      <c r="H77" t="str">
         <v>Tenroc</v>
       </c>
-      <c r="H77" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I77" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J77" t="str">
         <v>https://music.apple.com/us/artist/tenroc/1711844910</v>
       </c>
-      <c r="J77" t="str">
+      <c r="K77" t="str">
         <v>https://music.apple.com/us/album/playlist/1859009923</v>
       </c>
-      <c r="K77" t="str">
+      <c r="L77" t="str">
         <v>playlist - Tenroc</v>
       </c>
     </row>
@@ -3108,24 +3336,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
         <v>Marlboro Man - Single</v>
       </c>
-      <c r="F78" t="str">
+      <c r="G78" t="str">
         <v>3:23</v>
       </c>
-      <c r="G78" t="str">
+      <c r="H78" t="str">
         <v>Midland</v>
       </c>
-      <c r="H78" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I78" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J78" t="str">
         <v>https://music.apple.com/us/artist/midland/1171869852</v>
       </c>
-      <c r="J78" t="str">
+      <c r="K78" t="str">
         <v>https://music.apple.com/us/album/marlboro-man/1862008740</v>
       </c>
-      <c r="K78" t="str">
+      <c r="L78" t="str">
         <v>Marlboro Man - Midland</v>
       </c>
     </row>
@@ -3143,24 +3374,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
         <v>Enabling - Single</v>
       </c>
-      <c r="F79" t="str">
+      <c r="G79" t="str">
         <v>3:18</v>
       </c>
-      <c r="G79" t="str">
+      <c r="H79" t="str">
         <v>Tenille Townes</v>
       </c>
-      <c r="H79" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I79" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J79" t="str">
         <v>https://music.apple.com/us/artist/tenille-townes/1367713770</v>
       </c>
-      <c r="J79" t="str">
+      <c r="K79" t="str">
         <v>https://music.apple.com/us/album/enabling/1860992859</v>
       </c>
-      <c r="K79" t="str">
+      <c r="L79" t="str">
         <v>Enabling - Tenille Townes</v>
       </c>
     </row>
@@ -3178,24 +3412,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
         <v>Steel Town</v>
       </c>
-      <c r="F80" t="str">
+      <c r="G80" t="str">
         <v>3:53</v>
       </c>
-      <c r="G80" t="str">
+      <c r="H80" t="str">
         <v>Morgan Evans</v>
       </c>
-      <c r="H80" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I80" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J80" t="str">
         <v>https://music.apple.com/us/artist/morgan-evans/262665075</v>
       </c>
-      <c r="J80" t="str">
+      <c r="K80" t="str">
         <v>https://music.apple.com/us/album/two-broken-hearts/1841484758</v>
       </c>
-      <c r="K80" t="str">
+      <c r="L80" t="str">
         <v>Two Broken Hearts - Morgan Evans</v>
       </c>
     </row>
@@ -3213,24 +3450,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
         <v>Lost in My Bed - Single</v>
       </c>
-      <c r="F81" t="str">
+      <c r="G81" t="str">
         <v>3:46</v>
       </c>
-      <c r="G81" t="str">
+      <c r="H81" t="str">
         <v>Khalil</v>
       </c>
-      <c r="H81" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I81" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J81" t="str">
         <v>https://music.apple.com/us/artist/khalil/1223181975</v>
       </c>
-      <c r="J81" t="str">
+      <c r="K81" t="str">
         <v>https://music.apple.com/us/album/lost-in-my-bed/1862222272</v>
       </c>
-      <c r="K81" t="str">
+      <c r="L81" t="str">
         <v>Lost in My Bed - Khalil</v>
       </c>
     </row>
@@ -3248,24 +3488,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
         <v>Honey Water</v>
       </c>
-      <c r="F82" t="str">
+      <c r="G82" t="str">
         <v>1:58</v>
       </c>
-      <c r="G82" t="str">
+      <c r="H82" t="str">
         <v>Girlfriend</v>
       </c>
-      <c r="H82" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I82" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J82" t="str">
         <v>https://music.apple.com/us/artist/girlfriend/1511096374</v>
       </c>
-      <c r="J82" t="str">
+      <c r="K82" t="str">
         <v>https://music.apple.com/us/album/father-time/1858611265</v>
       </c>
-      <c r="K82" t="str">
+      <c r="L82" t="str">
         <v>Father Time - Girlfriend</v>
       </c>
     </row>
@@ -3283,24 +3526,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
         <v>MVLAN - Single</v>
       </c>
-      <c r="F83" t="str">
+      <c r="G83" t="str">
         <v>3:41</v>
       </c>
-      <c r="G83" t="str">
+      <c r="H83" t="str">
         <v>YOVNGCHIMI</v>
       </c>
-      <c r="H83" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I83" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J83" t="str">
         <v>https://music.apple.com/us/artist/yovngchimi/1558257759</v>
       </c>
-      <c r="J83" t="str">
+      <c r="K83" t="str">
         <v>https://music.apple.com/us/album/mvlan/1867584573</v>
       </c>
-      <c r="K83" t="str">
+      <c r="L83" t="str">
         <v>MVLAN - YOVNGCHIMI</v>
       </c>
     </row>
@@ -3318,24 +3564,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
         <v>Engines of Demolition</v>
       </c>
-      <c r="F84" t="str">
+      <c r="G84" t="str">
         <v>4:36</v>
       </c>
-      <c r="G84" t="str">
+      <c r="H84" t="str">
         <v>Black Label Society</v>
       </c>
-      <c r="H84" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I84" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J84" t="str">
         <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
       </c>
-      <c r="J84" t="str">
+      <c r="K84" t="str">
         <v>https://music.apple.com/us/album/name-in-blood/1859687597</v>
       </c>
-      <c r="K84" t="str">
+      <c r="L84" t="str">
         <v>Name In Blood - Black Label Society</v>
       </c>
     </row>
@@ -3353,24 +3602,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
         <v>Eyeball - EP</v>
       </c>
-      <c r="F85" t="str">
+      <c r="G85" t="str">
         <v>2:14</v>
       </c>
-      <c r="G85" t="str">
+      <c r="H85" t="str">
         <v>They Might Be Giants</v>
       </c>
-      <c r="H85" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I85" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J85" t="str">
         <v>https://music.apple.com/us/artist/they-might-be-giants/149020</v>
       </c>
-      <c r="J85" t="str">
+      <c r="K85" t="str">
         <v>https://music.apple.com/us/album/eyeball/1862539346</v>
       </c>
-      <c r="K85" t="str">
+      <c r="L85" t="str">
         <v>Eyeball - They Might Be Giants</v>
       </c>
     </row>
@@ -3388,24 +3640,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
         <v>Tenterhooks</v>
       </c>
-      <c r="F86" t="str">
+      <c r="G86" t="str">
         <v>3:55</v>
       </c>
-      <c r="G86" t="str">
+      <c r="H86" t="str">
         <v>Silversun Pickups</v>
       </c>
-      <c r="H86" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I86" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J86" t="str">
         <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
       </c>
-      <c r="J86" t="str">
+      <c r="K86" t="str">
         <v>https://music.apple.com/us/album/long-gone/1847573918</v>
       </c>
-      <c r="K86" t="str">
+      <c r="L86" t="str">
         <v>Long Gone - Silversun Pickups</v>
       </c>
     </row>
@@ -3423,24 +3678,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
         <v>iloveitiloveitiloveit - Single</v>
       </c>
-      <c r="F87" t="str">
+      <c r="G87" t="str">
         <v>3:03</v>
       </c>
-      <c r="G87" t="str">
+      <c r="H87" t="str">
         <v>Bella Kay</v>
       </c>
-      <c r="H87" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I87" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J87" t="str">
         <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
-      <c r="J87" t="str">
+      <c r="K87" t="str">
         <v>https://music.apple.com/us/album/iloveitiloveitiloveit/1867034426</v>
       </c>
-      <c r="K87" t="str">
+      <c r="L87" t="str">
         <v>iloveitiloveitiloveit - Bella Kay</v>
       </c>
     </row>
@@ -3458,24 +3716,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
         <v>To The Edge - Single</v>
       </c>
-      <c r="F88" t="str">
+      <c r="G88" t="str">
         <v>3:19</v>
       </c>
-      <c r="G88" t="str">
+      <c r="H88" t="str">
         <v>Alex Jude</v>
       </c>
-      <c r="H88" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I88" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J88" t="str">
         <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
       </c>
-      <c r="J88" t="str">
+      <c r="K88" t="str">
         <v>https://music.apple.com/us/album/to-the-edge/1863513887</v>
       </c>
-      <c r="K88" t="str">
+      <c r="L88" t="str">
         <v>To The Edge - Alex Jude</v>
       </c>
     </row>
@@ -3493,24 +3754,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
         <v>demons - Single</v>
       </c>
-      <c r="F89" t="str">
+      <c r="G89" t="str">
         <v>3:10</v>
       </c>
-      <c r="G89" t="str">
+      <c r="H89" t="str">
         <v>Josiah Queen</v>
       </c>
-      <c r="H89" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I89" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J89" t="str">
         <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
       </c>
-      <c r="J89" t="str">
+      <c r="K89" t="str">
         <v>https://music.apple.com/us/album/demons/1861978105</v>
       </c>
-      <c r="K89" t="str">
+      <c r="L89" t="str">
         <v>demons - Josiah Queen</v>
       </c>
     </row>
@@ -3528,24 +3792,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
         <v>Valentine</v>
       </c>
-      <c r="F90" t="str">
+      <c r="G90" t="str">
         <v>4:03</v>
       </c>
-      <c r="G90" t="str">
+      <c r="H90" t="str">
         <v>Courtney Marie Andrews</v>
       </c>
-      <c r="H90" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I90" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J90" t="str">
         <v>https://music.apple.com/us/artist/courtney-marie-andrews/287157006</v>
       </c>
-      <c r="J90" t="str">
+      <c r="K90" t="str">
         <v>https://music.apple.com/us/album/everyone-wants-to-feel-like-you-do/1841948802</v>
       </c>
-      <c r="K90" t="str">
+      <c r="L90" t="str">
         <v>Everyone Wants To Feel Like You Do - Courtney Marie Andrews</v>
       </c>
     </row>
@@ -3563,24 +3830,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
         <v>Nothing Comes Easy - Single</v>
       </c>
-      <c r="F91" t="str">
+      <c r="G91" t="str">
         <v>2:54</v>
       </c>
-      <c r="G91" t="str">
+      <c r="H91" t="str">
         <v>Joy Oladokun</v>
       </c>
-      <c r="H91" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I91" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J91" t="str">
         <v>https://music.apple.com/us/artist/joy-oladokun/699636664</v>
       </c>
-      <c r="J91" t="str">
+      <c r="K91" t="str">
         <v>https://music.apple.com/us/album/nothing-comes-easy/1862756744</v>
       </c>
-      <c r="K91" t="str">
+      <c r="L91" t="str">
         <v>Nothing Comes Easy - Joy Oladokun</v>
       </c>
     </row>
@@ -3598,24 +3868,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
         <v>Against the Dying of the Light</v>
       </c>
-      <c r="F92" t="str">
+      <c r="G92" t="str">
         <v>2:28</v>
       </c>
-      <c r="G92" t="str">
+      <c r="H92" t="str">
         <v>José González</v>
       </c>
-      <c r="H92" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I92" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J92" t="str">
         <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
       </c>
-      <c r="J92" t="str">
+      <c r="K92" t="str">
         <v>https://music.apple.com/us/album/against-the-dying-of-the-light/1860962162</v>
       </c>
-      <c r="K92" t="str">
+      <c r="L92" t="str">
         <v>Against the Dying of the Light - José González</v>
       </c>
     </row>
@@ -3633,24 +3906,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
         <v>Cynthia</v>
       </c>
-      <c r="F93" t="str">
+      <c r="G93" t="str">
         <v>2:30</v>
       </c>
-      <c r="G93" t="str">
+      <c r="H93" t="str">
         <v>Sydney Ross Mitchell</v>
       </c>
-      <c r="H93" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I93" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J93" t="str">
         <v>https://music.apple.com/us/artist/sydney-ross-mitchell/1373996317</v>
       </c>
-      <c r="J93" t="str">
+      <c r="K93" t="str">
         <v>https://music.apple.com/us/album/big-boy-problems/1851062193</v>
       </c>
-      <c r="K93" t="str">
+      <c r="L93" t="str">
         <v>Big Boy Problems - Sydney Ross Mitchell</v>
       </c>
     </row>
@@ -3668,24 +3944,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
         <v>Griever - Single</v>
       </c>
-      <c r="F94" t="str">
+      <c r="G94" t="str">
         <v>2:31</v>
       </c>
-      <c r="G94" t="str">
+      <c r="H94" t="str">
         <v>Avery Cochrane</v>
       </c>
-      <c r="H94" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I94" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J94" t="str">
         <v>https://music.apple.com/us/artist/avery-cochrane/1556978969</v>
       </c>
-      <c r="J94" t="str">
+      <c r="K94" t="str">
         <v>https://music.apple.com/us/album/griever/1860950897</v>
       </c>
-      <c r="K94" t="str">
+      <c r="L94" t="str">
         <v>Griever - Avery Cochrane</v>
       </c>
     </row>
@@ -3703,24 +3982,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
         <v>7 BESOS - Single</v>
       </c>
-      <c r="F95" t="str">
+      <c r="G95" t="str">
         <v>3:21</v>
       </c>
-      <c r="G95" t="str">
+      <c r="H95" t="str">
         <v>LEGADO 7</v>
       </c>
-      <c r="H95" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I95" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J95" t="str">
         <v>https://music.apple.com/us/artist/legado-7/997011422</v>
       </c>
-      <c r="J95" t="str">
+      <c r="K95" t="str">
         <v>https://music.apple.com/us/album/7-besos/1862927851</v>
       </c>
-      <c r="K95" t="str">
+      <c r="L95" t="str">
         <v>7 BESOS - LEGADO 7</v>
       </c>
     </row>
@@ -3738,24 +4020,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
         <v>UN LEÑO - Single</v>
       </c>
-      <c r="F96" t="str">
+      <c r="G96" t="str">
         <v>3:00</v>
       </c>
-      <c r="G96" t="str">
+      <c r="H96" t="str">
         <v>Armenta</v>
       </c>
-      <c r="H96" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I96" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J96" t="str">
         <v>https://music.apple.com/us/artist/armenta/1479504876</v>
       </c>
-      <c r="J96" t="str">
+      <c r="K96" t="str">
         <v>https://music.apple.com/us/album/un-le%C3%B1o/1862904402</v>
       </c>
-      <c r="K96" t="str">
+      <c r="L96" t="str">
         <v>UN LEÑO - Armenta</v>
       </c>
     </row>
@@ -3773,24 +4058,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
         <v>Mārara</v>
       </c>
-      <c r="F97" t="str">
+      <c r="G97" t="str">
         <v>3:46</v>
       </c>
-      <c r="G97" t="str">
+      <c r="H97" t="str">
         <v>15 15</v>
       </c>
-      <c r="H97" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I97" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J97" t="str">
         <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
-      <c r="J97" t="str">
+      <c r="K97" t="str">
         <v>https://music.apple.com/us/album/queens-goodbye/1858554036</v>
       </c>
-      <c r="K97" t="str">
+      <c r="L97" t="str">
         <v>Queen's Goodbye - 15 15</v>
       </c>
     </row>
@@ -3808,24 +4096,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
         <v>Melancholia - EP</v>
       </c>
-      <c r="F98" t="str">
+      <c r="G98" t="str">
         <v>3:24</v>
       </c>
-      <c r="G98" t="str">
+      <c r="H98" t="str">
         <v>JELISA</v>
       </c>
-      <c r="H98" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I98" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J98" t="str">
         <v>https://music.apple.com/us/artist/jelisa/1588318671</v>
       </c>
-      <c r="J98" t="str">
+      <c r="K98" t="str">
         <v>https://music.apple.com/us/album/bring-me-back-to-life/1851634783</v>
       </c>
-      <c r="K98" t="str">
+      <c r="L98" t="str">
         <v>Bring Me Back To Life - JELISA</v>
       </c>
     </row>
@@ -3843,24 +4134,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
         <v>I Don't Care - Single</v>
       </c>
-      <c r="F99" t="str">
+      <c r="G99" t="str">
         <v>3:49</v>
       </c>
-      <c r="G99" t="str">
+      <c r="H99" t="str">
         <v>Buffalo Traffic Jam</v>
       </c>
-      <c r="H99" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I99" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J99" t="str">
         <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
       </c>
-      <c r="J99" t="str">
+      <c r="K99" t="str">
         <v>https://music.apple.com/us/album/i-dont-care/1868429639</v>
       </c>
-      <c r="K99" t="str">
+      <c r="L99" t="str">
         <v>I Don't Care - Buffalo Traffic Jam</v>
       </c>
     </row>
@@ -3878,24 +4172,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
         <v>Elastico (feat. KATE LINN) - Single</v>
       </c>
-      <c r="F100" t="str">
+      <c r="G100" t="str">
         <v>3:20</v>
       </c>
-      <c r="G100" t="str">
+      <c r="H100" t="str">
         <v>Fantomel</v>
       </c>
-      <c r="H100" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I100" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J100" t="str">
         <v>https://music.apple.com/us/artist/fantomel/1736085960</v>
       </c>
-      <c r="J100" t="str">
+      <c r="K100" t="str">
         <v>https://music.apple.com/us/album/elastico-feat-kate-linn/1862157496</v>
       </c>
-      <c r="K100" t="str">
+      <c r="L100" t="str">
         <v>Elastico (feat. KATE LINN) - Fantomel</v>
       </c>
     </row>
@@ -3913,24 +4210,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
         <v>Black &amp; Gold - Single</v>
       </c>
-      <c r="F101" t="str">
+      <c r="G101" t="str">
         <v>3:12</v>
       </c>
-      <c r="G101" t="str">
+      <c r="H101" t="str">
         <v>Claptone</v>
       </c>
-      <c r="H101" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I101" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J101" t="str">
         <v>https://music.apple.com/us/artist/claptone/470488523</v>
       </c>
-      <c r="J101" t="str">
+      <c r="K101" t="str">
         <v>https://music.apple.com/us/album/black-gold/1853914793</v>
       </c>
-      <c r="K101" t="str">
+      <c r="L101" t="str">
         <v>Black &amp; Gold - Claptone</v>
       </c>
     </row>
@@ -3948,24 +4248,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
         <v>Close Your Eyes - Single</v>
       </c>
-      <c r="F102" t="str">
+      <c r="G102" t="str">
         <v>3:33</v>
       </c>
-      <c r="G102" t="str">
+      <c r="H102" t="str">
         <v>Adam Beyer</v>
       </c>
-      <c r="H102" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I102" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J102" t="str">
         <v>https://music.apple.com/us/artist/adam-beyer/101672291</v>
       </c>
-      <c r="J102" t="str">
+      <c r="K102" t="str">
         <v>https://music.apple.com/us/album/close-your-eyes/1860632569</v>
       </c>
-      <c r="K102" t="str">
+      <c r="L102" t="str">
         <v>Close Your Eyes - Adam Beyer</v>
       </c>
     </row>
@@ -3983,24 +4286,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
         <v>Movement - Single</v>
       </c>
-      <c r="F103" t="str">
+      <c r="G103" t="str">
         <v>3:07</v>
       </c>
-      <c r="G103" t="str">
+      <c r="H103" t="str">
         <v>Crankdat</v>
       </c>
-      <c r="H103" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I103" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J103" t="str">
         <v>https://music.apple.com/us/artist/crankdat/1073027547</v>
       </c>
-      <c r="J103" t="str">
+      <c r="K103" t="str">
         <v>https://music.apple.com/us/album/movement/1867063796</v>
       </c>
-      <c r="K103" t="str">
+      <c r="L103" t="str">
         <v>Movement - Crankdat</v>
       </c>
     </row>
@@ -4018,24 +4324,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
         <v>Ayi Giri / Dopamine Machine - Single</v>
       </c>
-      <c r="F104" t="str">
+      <c r="G104" t="str">
         <v>3:06</v>
       </c>
-      <c r="G104" t="str">
+      <c r="H104" t="str">
         <v>Lilly Palmer</v>
       </c>
-      <c r="H104" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I104" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J104" t="str">
         <v>https://music.apple.com/us/artist/lilly-palmer/340777023</v>
       </c>
-      <c r="J104" t="str">
+      <c r="K104" t="str">
         <v>https://music.apple.com/us/album/ayi-giri/1867306650</v>
       </c>
-      <c r="K104" t="str">
+      <c r="L104" t="str">
         <v>Ayi Giri - Lilly Palmer</v>
       </c>
     </row>
@@ -4053,24 +4362,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
         <v>It's A Sin - Single</v>
       </c>
-      <c r="F105" t="str">
+      <c r="G105" t="str">
         <v>4:40</v>
       </c>
-      <c r="G105" t="str">
+      <c r="H105" t="str">
         <v>Ghost</v>
       </c>
-      <c r="H105" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I105" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J105" t="str">
         <v>https://music.apple.com/us/artist/ghost/600730426</v>
       </c>
-      <c r="J105" t="str">
+      <c r="K105" t="str">
         <v>https://music.apple.com/us/album/its-a-sin/1861930280</v>
       </c>
-      <c r="K105" t="str">
+      <c r="L105" t="str">
         <v>It's A Sin - Ghost</v>
       </c>
     </row>
@@ -4088,24 +4400,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E106" t="str">
+        <v/>
+      </c>
+      <c r="F106" t="str">
         <v>Krushers Of The World</v>
       </c>
-      <c r="F106" t="str">
+      <c r="G106" t="str">
         <v>4:20</v>
       </c>
-      <c r="G106" t="str">
+      <c r="H106" t="str">
         <v>Kreator</v>
       </c>
-      <c r="H106" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I106" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J106" t="str">
         <v>https://music.apple.com/us/artist/kreator/3258504</v>
       </c>
-      <c r="J106" t="str">
+      <c r="K106" t="str">
         <v>https://music.apple.com/us/album/krushers-of-the-world/1837718517</v>
       </c>
-      <c r="K106" t="str">
+      <c r="L106" t="str">
         <v>Krushers Of The World - Kreator</v>
       </c>
     </row>
@@ -4123,24 +4438,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107" t="str">
         <v>Peace In Place</v>
       </c>
-      <c r="F107" t="str">
+      <c r="G107" t="str">
         <v>3:24</v>
       </c>
-      <c r="G107" t="str">
+      <c r="H107" t="str">
         <v>Poison the Well</v>
       </c>
-      <c r="H107" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I107" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J107" t="str">
         <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
       </c>
-      <c r="J107" t="str">
+      <c r="K107" t="str">
         <v>https://music.apple.com/us/album/thoroughbreds/1863532634</v>
       </c>
-      <c r="K107" t="str">
+      <c r="L107" t="str">
         <v>Thoroughbreds - Poison the Well</v>
       </c>
     </row>
@@ -4158,30 +4476,33 @@
         <v>2026-01-22</v>
       </c>
       <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108" t="str">
         <v>Descent</v>
       </c>
-      <c r="F108" t="str">
+      <c r="G108" t="str">
         <v>3:17</v>
       </c>
-      <c r="G108" t="str">
+      <c r="H108" t="str">
         <v>Immolation</v>
       </c>
-      <c r="H108" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I108" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J108" t="str">
         <v>https://music.apple.com/us/artist/immolation/64874488</v>
       </c>
-      <c r="J108" t="str">
+      <c r="K108" t="str">
         <v>https://music.apple.com/us/album/adversary/1861901597</v>
       </c>
-      <c r="K108" t="str">
+      <c r="L108" t="str">
         <v>Adversary - Immolation</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L108"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L108"/>
+  <dimension ref="A1:L109"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,40 +436,40 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Opening Night</v>
+        <v>Aperture</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
+        <v>https://music.apple.com/us/song/aperture/1870984033</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>HELP(2)</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G2" t="str">
-        <v>4:19</v>
+        <v>5:11</v>
       </c>
       <c r="H2" t="str">
-        <v>Arctic Monkeys</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
+        <v>https://music.apple.com/us/album/aperture/1870984032</v>
       </c>
       <c r="L2" t="str">
-        <v>Opening Night - Arctic Monkeys</v>
+        <v>Aperture - Harry Styles</v>
       </c>
     </row>
     <row r="3">
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/wish-i-didnt/1851297073</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/air-force-black-demarco/1862935169</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/wall-of-sound/1852566426</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/wheres-my-phone/1860622553</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/100/1858754874</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/por-un-p-o-no-se-llora-salud-mi-reina/1862587826</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -702,40 +702,40 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Flo Jackson</v>
+        <v>Opening Night</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
+        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Flo Jackson - Single</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G9" t="str">
-        <v>2:23</v>
+        <v>4:19</v>
       </c>
       <c r="H9" t="str">
-        <v>Flo Milli</v>
+        <v>Arctic Monkeys</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
+        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
+        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
       </c>
       <c r="L9" t="str">
-        <v>Flo Jackson - Flo Milli</v>
+        <v>Opening Night - Arctic Monkeys</v>
       </c>
     </row>
     <row r="10">
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/l-u-c-k-y/1861895147</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/reclusive/1860405760</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -816,78 +816,78 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Site Unseen (feat. Waxahatchee)</v>
+        <v>Flo Jackson</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
+        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>Creature of Habit</v>
+        <v>Flo Jackson - Single</v>
       </c>
       <c r="G12" t="str">
-        <v>2:46</v>
+        <v>2:23</v>
       </c>
       <c r="H12" t="str">
-        <v>Courtney Barnett</v>
+        <v>Flo Milli</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
+        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
       </c>
       <c r="L12" t="str">
-        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
+        <v>Flo Jackson - Flo Milli</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Puppet Parade</v>
+        <v>Site Unseen (feat. Waxahatchee)</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
+        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Megadeth</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G13" t="str">
-        <v>4:40</v>
+        <v>2:46</v>
       </c>
       <c r="H13" t="str">
-        <v>Megadeth</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/megadeth/488289</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
+        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
       </c>
       <c r="L13" t="str">
-        <v>Puppet Parade - Megadeth</v>
+        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
       </c>
     </row>
     <row r="14">
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/raft-in-the-sea/1847662987</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/good-night-baby/1849917462</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -968,3541 +968,3579 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>CAMBIARÉ</v>
+        <v>Puppet Parade</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
+        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>CAMBIARÉ - Single</v>
+        <v>Megadeth</v>
       </c>
       <c r="G16" t="str">
-        <v>3:01</v>
+        <v>4:40</v>
       </c>
       <c r="H16" t="str">
-        <v>Luis Fonsi</v>
+        <v>Megadeth</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
+        <v>https://music.apple.com/us/artist/megadeth/488289</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
+        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
       </c>
       <c r="L16" t="str">
-        <v>CAMBIARÉ - Luis Fonsi</v>
+        <v>Puppet Parade - Megadeth</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Orange County (feat. Bizarrap, Kara Jackson &amp; Anoushka Shankar)</v>
+        <v>CAMBIARÉ</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/orange-county-feat-bizarrap-kara-jackson-anoushka-shankar/1837237867</v>
+        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>The Mountain</v>
+        <v>CAMBIARÉ - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>3:28</v>
+        <v>3:01</v>
       </c>
       <c r="H17" t="str">
-        <v>Gorillaz</v>
+        <v>Luis Fonsi</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
+        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/orange-county-feat-bizarrap-kara-jackson-anoushka-shankar/1837237742</v>
+        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
       </c>
       <c r="L17" t="str">
-        <v>Orange County (feat. Bizarrap, Kara Jackson &amp; Anoushka Shankar) - Gorillaz</v>
+        <v>CAMBIARÉ - Luis Fonsi</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Lluvia</v>
+        <v>Orange County (feat. Bizarrap, Kara Jackson &amp; Anoushka Shankar)</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/lluvia/1868476403</v>
+        <v>https://music.apple.com/us/song/orange-county-feat-bizarrap-kara-jackson-anoushka-shankar/1837237867</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>LA 8VA MARAVILLA</v>
+        <v>The Mountain</v>
       </c>
       <c r="G18" t="str">
-        <v>3:24</v>
+        <v>3:28</v>
       </c>
       <c r="H18" t="str">
-        <v>Arcángel</v>
+        <v>Gorillaz</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/lluvia/1868476390</v>
+        <v>https://music.apple.com/us/album/orange-county-feat-bizarrap-kara-jackson-anoushka-shankar/1837237742</v>
       </c>
       <c r="L18" t="str">
-        <v>Lluvia - Arcángel</v>
+        <v>Orange County (feat. Bizarrap, Kara Jackson &amp; Anoushka Shankar) - Gorillaz</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Knife</v>
+        <v>Lluvia</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/knife/1862720450</v>
+        <v>https://music.apple.com/us/song/lluvia/1868476403</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>THE SIN : VANISH</v>
+        <v>LA 8VA MARAVILLA</v>
       </c>
       <c r="G19" t="str">
-        <v>2:19</v>
+        <v>3:24</v>
       </c>
       <c r="H19" t="str">
-        <v>ENHYPEN</v>
+        <v>Arcángel</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/enhypen/1541011620</v>
+        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/knife/1862720020</v>
+        <v>https://music.apple.com/us/album/lluvia/1868476390</v>
       </c>
       <c r="L19" t="str">
-        <v>Knife - ENHYPEN</v>
+        <v>Lluvia - Arcángel</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>bad enough</v>
+        <v>Knife</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/bad-enough/1846949125</v>
+        <v>https://music.apple.com/us/song/knife/1862720450</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>locket</v>
+        <v>THE SIN : VANISH</v>
       </c>
       <c r="G20" t="str">
-        <v>3:42</v>
+        <v>2:19</v>
       </c>
       <c r="H20" t="str">
-        <v>Madison Beer</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/madison-beer/696146587</v>
+        <v>https://music.apple.com/us/artist/enhypen/1541011620</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/bad-enough/1846949115</v>
+        <v>https://music.apple.com/us/album/knife/1862720020</v>
       </c>
       <c r="L20" t="str">
-        <v>bad enough - Madison Beer</v>
+        <v>Knife - ENHYPEN</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>bad</v>
+        <v>bad enough</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/bad/1851566880</v>
+        <v>https://music.apple.com/us/song/bad-enough/1846949125</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>bad - Single</v>
+        <v>locket</v>
       </c>
       <c r="G21" t="str">
-        <v>2:41</v>
+        <v>3:42</v>
       </c>
       <c r="H21" t="str">
-        <v>Saint Harison</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/madison-beer/696146587</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/bad/1851566879</v>
+        <v>https://music.apple.com/us/album/bad-enough/1846949115</v>
       </c>
       <c r="L21" t="str">
-        <v>bad - Saint Harison</v>
+        <v>bad enough - Madison Beer</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Beat Yourself Up</v>
+        <v>bad</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/beat-yourself-up/1845189973</v>
+        <v>https://music.apple.com/us/song/bad/1851566880</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Whatever's Clever!</v>
+        <v>bad - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>2:58</v>
+        <v>2:41</v>
       </c>
       <c r="H22" t="str">
-        <v>Charlie Puth</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/beat-yourself-up/1845189970</v>
+        <v>https://music.apple.com/us/album/bad/1851566879</v>
       </c>
       <c r="L22" t="str">
-        <v>Beat Yourself Up - Charlie Puth</v>
+        <v>bad - Saint Harison</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Roommates</v>
+        <v>Beat Yourself Up</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/roommates/1854567105</v>
+        <v>https://music.apple.com/us/song/beat-yourself-up/1845189973</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>luck... or something</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G23" t="str">
-        <v>2:52</v>
+        <v>2:58</v>
       </c>
       <c r="H23" t="str">
-        <v>Hilary Duff</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/roommates/1854567102</v>
+        <v>https://music.apple.com/us/album/beat-yourself-up/1845189970</v>
       </c>
       <c r="L23" t="str">
-        <v>Roommates - Hilary Duff</v>
+        <v>Beat Yourself Up - Charlie Puth</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2SIDED</v>
+        <v>Roommates</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/2sided/1862571197</v>
+        <v>https://music.apple.com/us/song/roommates/1854567105</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Ambiguous Desire</v>
+        <v>luck... or something</v>
       </c>
       <c r="G24" t="str">
-        <v>2:57</v>
+        <v>2:52</v>
       </c>
       <c r="H24" t="str">
-        <v>Arlo Parks</v>
+        <v>Hilary Duff</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/2sided/1862570378</v>
+        <v>https://music.apple.com/us/album/roommates/1854567102</v>
       </c>
       <c r="L24" t="str">
-        <v>2SIDED - Arlo Parks</v>
+        <v>Roommates - Hilary Duff</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Feel Alive</v>
+        <v>2SIDED</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/feel-alive/1851368171</v>
+        <v>https://music.apple.com/us/song/2sided/1862571197</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>ODYSSEY</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G25" t="str">
-        <v>2:48</v>
+        <v>2:57</v>
       </c>
       <c r="H25" t="str">
-        <v>ILLENIUM</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/feel-alive/1851368154</v>
+        <v>https://music.apple.com/us/album/2sided/1862570378</v>
       </c>
       <c r="L25" t="str">
-        <v>Feel Alive - ILLENIUM</v>
+        <v>2SIDED - Arlo Parks</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>God Spoke</v>
+        <v>Feel Alive</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/god-spoke/1853069638</v>
+        <v>https://music.apple.com/us/song/feel-alive/1851368171</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>COSMIC OPERA ACT I</v>
+        <v>ODYSSEY</v>
       </c>
       <c r="G26" t="str">
-        <v>1:14</v>
+        <v>2:48</v>
       </c>
       <c r="H26" t="str">
-        <v>Labrinth</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/god-spoke/1853069628</v>
+        <v>https://music.apple.com/us/album/feel-alive/1851368154</v>
       </c>
       <c r="L26" t="str">
-        <v>God Spoke - Labrinth</v>
+        <v>Feel Alive - ILLENIUM</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Risk Takers</v>
+        <v>God Spoke</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/risk-takers/1866642666</v>
+        <v>https://music.apple.com/us/song/god-spoke/1853069638</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>El Mundo Es Tuyo (Inspired by Clika The Movie)</v>
+        <v>COSMIC OPERA ACT I</v>
       </c>
       <c r="G27" t="str">
-        <v>2:35</v>
+        <v>1:14</v>
       </c>
       <c r="H27" t="str">
-        <v>Herencia de Patrones</v>
+        <v>Labrinth</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/herencia-de-patrones/1295294734</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/risk-takers/1866642665</v>
+        <v>https://music.apple.com/us/album/god-spoke/1853069628</v>
       </c>
       <c r="L27" t="str">
-        <v>Risk Takers - Herencia de Patrones</v>
+        <v>God Spoke - Labrinth</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Never Comin' Back</v>
+        <v>Risk Takers</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/never-comin-back/1862970557</v>
+        <v>https://music.apple.com/us/song/risk-takers/1866642666</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Never Comin' Back - Single</v>
+        <v>El Mundo Es Tuyo (Inspired by Clika The Movie)</v>
       </c>
       <c r="G28" t="str">
-        <v>3:57</v>
+        <v>2:35</v>
       </c>
       <c r="H28" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Herencia de Patrones</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/herencia-de-patrones/1295294734</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/never-comin-back/1862970555</v>
+        <v>https://music.apple.com/us/album/risk-takers/1866642665</v>
       </c>
       <c r="L28" t="str">
-        <v>Never Comin' Back - Flatland Cavalry</v>
+        <v>Risk Takers - Herencia de Patrones</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II))</v>
+        <v>Never Comin' Back</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/lay-your-heartache-onto-mine-songs-from-and-inspired/1867273711</v>
+        <v>https://music.apple.com/us/song/never-comin-back/1862970557</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II)) - Single</v>
+        <v>Never Comin' Back - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>3:18</v>
+        <v>3:57</v>
       </c>
       <c r="H29" t="str">
-        <v>Carter Faith</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/lay-your-heartache-onto-mine-songs-from-and-inspired/1867273471</v>
+        <v>https://music.apple.com/us/album/never-comin-back/1862970555</v>
       </c>
       <c r="L29" t="str">
-        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II)) - Carter Faith</v>
+        <v>Never Comin' Back - Flatland Cavalry</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
+        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II))</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
+        <v>https://music.apple.com/us/song/lay-your-heartache-onto-mine-songs-from-and-inspired/1867273711</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
+        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II)) - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>3:47</v>
+        <v>3:18</v>
       </c>
       <c r="H30" t="str">
-        <v>Dolly Parton</v>
+        <v>Carter Faith</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
+        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
+        <v>https://music.apple.com/us/album/lay-your-heartache-onto-mine-songs-from-and-inspired/1867273471</v>
       </c>
       <c r="L30" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
+        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II)) - Carter Faith</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Traffic Lights (feat. Thom Yorke)</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/traffic-lights-feat-thom-yorke/1861644315</v>
+        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Honora</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>5:41</v>
+        <v>3:47</v>
       </c>
       <c r="H31" t="str">
-        <v>Flea</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/traffic-lights-feat-thom-yorke/1861644307</v>
+        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
       </c>
       <c r="L31" t="str">
-        <v>Traffic Lights (feat. Thom Yorke) - Flea</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Inferno (from "Heated Rivalry")</v>
+        <v>Traffic Lights (feat. Thom Yorke)</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/inferno-from-heated-rivalry/1868783886</v>
+        <v>https://music.apple.com/us/song/traffic-lights-feat-thom-yorke/1861644315</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Heated Rivalry (Original Series Soundtrack)</v>
+        <v>Honora</v>
       </c>
       <c r="G32" t="str">
-        <v>4:26</v>
+        <v>5:41</v>
       </c>
       <c r="H32" t="str">
-        <v>Peter Peter</v>
+        <v>Flea</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/peter-peter/71305428</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/inferno-from-heated-rivalry/1868783596</v>
+        <v>https://music.apple.com/us/album/traffic-lights-feat-thom-yorke/1861644307</v>
       </c>
       <c r="L32" t="str">
-        <v>Inferno (from "Heated Rivalry") - Peter Peter</v>
+        <v>Traffic Lights (feat. Thom Yorke) - Flea</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Yo Yan</v>
+        <v>Inferno (from "Heated Rivalry")</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/yo-yan/1867888651</v>
+        <v>https://music.apple.com/us/song/inferno-from-heated-rivalry/1868783886</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Kora - Single</v>
+        <v>Heated Rivalry (Original Series Soundtrack)</v>
       </c>
       <c r="G33" t="str">
-        <v>2:00</v>
+        <v>4:26</v>
       </c>
       <c r="H33" t="str">
-        <v>Skrillex</v>
+        <v>Peter Peter</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/peter-peter/71305428</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/yo-yan/1867888650</v>
+        <v>https://music.apple.com/us/album/inferno-from-heated-rivalry/1868783596</v>
       </c>
       <c r="L33" t="str">
-        <v>Yo Yan - Skrillex</v>
+        <v>Inferno (from "Heated Rivalry") - Peter Peter</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Jogodo</v>
+        <v>Yo Yan</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/jogodo/1867908454</v>
+        <v>https://music.apple.com/us/song/yo-yan/1867888651</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>REAL, Vol. 1 - EP</v>
+        <v>Kora - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>3:08</v>
+        <v>2:00</v>
       </c>
       <c r="H34" t="str">
-        <v>Wizkid</v>
+        <v>Skrillex</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/jogodo/1867908237</v>
+        <v>https://music.apple.com/us/album/yo-yan/1867888650</v>
       </c>
       <c r="L34" t="str">
-        <v>Jogodo - Wizkid</v>
+        <v>Yo Yan - Skrillex</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Made It Out Alive</v>
+        <v>Jogodo</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/made-it-out-alive/1867596345</v>
+        <v>https://music.apple.com/us/song/jogodo/1867908454</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Suffering From Success</v>
+        <v>REAL, Vol. 1 - EP</v>
       </c>
       <c r="G35" t="str">
-        <v>3:00</v>
+        <v>3:08</v>
       </c>
       <c r="H35" t="str">
-        <v>Dee Mula</v>
+        <v>Wizkid</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/dee-mula/1330325377</v>
+        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/made-it-out-alive/1867596343</v>
+        <v>https://music.apple.com/us/album/jogodo/1867908237</v>
       </c>
       <c r="L35" t="str">
-        <v>Made It Out Alive - Dee Mula</v>
+        <v>Jogodo - Wizkid</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>One of Them Ones</v>
+        <v>Made It Out Alive</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/one-of-them-ones/1868850365</v>
+        <v>https://music.apple.com/us/song/made-it-out-alive/1867596345</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>One of Them Ones - Single</v>
+        <v>Suffering From Success</v>
       </c>
       <c r="G36" t="str">
-        <v>3:05</v>
+        <v>3:00</v>
       </c>
       <c r="H36" t="str">
-        <v>Veeze</v>
+        <v>Dee Mula</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
+        <v>https://music.apple.com/us/artist/dee-mula/1330325377</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/one-of-them-ones/1868850364</v>
+        <v>https://music.apple.com/us/album/made-it-out-alive/1867596343</v>
       </c>
       <c r="L36" t="str">
-        <v>One of Them Ones - Veeze</v>
+        <v>Made It Out Alive - Dee Mula</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Como Es Que Se Hace</v>
+        <v>One of Them Ones</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/como-es-que-se-hace/1864227584</v>
+        <v>https://music.apple.com/us/song/one-of-them-ones/1868850365</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Como Es Que Se Hace - Single</v>
+        <v>One of Them Ones - Single</v>
       </c>
       <c r="G37" t="str">
-        <v>3:25</v>
+        <v>3:05</v>
       </c>
       <c r="H37" t="str">
-        <v>Yandel</v>
+        <v>Veeze</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/yandel/72929426</v>
+        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/como-es-que-se-hace/1864227582</v>
+        <v>https://music.apple.com/us/album/one-of-them-ones/1868850364</v>
       </c>
       <c r="L37" t="str">
-        <v>Como Es Que Se Hace - Yandel</v>
+        <v>One of Them Ones - Veeze</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Ever Since U Left Me (I Went Deaf)</v>
+        <v>Como Es Que Se Hace</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/ever-since-u-left-me-i-went-deaf/1863124175</v>
+        <v>https://music.apple.com/us/song/como-es-que-se-hace/1864227584</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Coke Wave 3.5: Narcos</v>
+        <v>Como Es Que Se Hace - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>2:16</v>
+        <v>3:25</v>
       </c>
       <c r="H38" t="str">
-        <v>French Montana</v>
+        <v>Yandel</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/french-montana/475816358</v>
+        <v>https://music.apple.com/us/artist/yandel/72929426</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/ever-since-u-left-me-i-went-deaf/1863124168</v>
+        <v>https://music.apple.com/us/album/como-es-que-se-hace/1864227582</v>
       </c>
       <c r="L38" t="str">
-        <v>Ever Since U Left Me (I Went Deaf) - French Montana</v>
+        <v>Como Es Que Se Hace - Yandel</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Ay Dale</v>
+        <v>Ever Since U Left Me (I Went Deaf)</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/ay-dale/1862897966</v>
+        <v>https://music.apple.com/us/song/ever-since-u-left-me-i-went-deaf/1863124175</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Ay Dale - Single</v>
+        <v>Coke Wave 3.5: Narcos</v>
       </c>
       <c r="G39" t="str">
-        <v>2:26</v>
+        <v>2:16</v>
       </c>
       <c r="H39" t="str">
-        <v>Farruko</v>
+        <v>French Montana</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/farruko/364377482</v>
+        <v>https://music.apple.com/us/artist/french-montana/475816358</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/ay-dale/1862897623</v>
+        <v>https://music.apple.com/us/album/ever-since-u-left-me-i-went-deaf/1863124168</v>
       </c>
       <c r="L39" t="str">
-        <v>Ay Dale - Farruko</v>
+        <v>Ever Since U Left Me (I Went Deaf) - French Montana</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Teary Eyes</v>
+        <v>Ay Dale</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/teary-eyes/1869534187</v>
+        <v>https://music.apple.com/us/song/ay-dale/1862897966</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Slime Cry</v>
+        <v>Ay Dale - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>2:45</v>
+        <v>2:26</v>
       </c>
       <c r="H40" t="str">
-        <v>YoungBoy Never Broke Again</v>
+        <v>Farruko</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/youngboy-never-broke-again/1168822104</v>
+        <v>https://music.apple.com/us/artist/farruko/364377482</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/teary-eyes/1869534167</v>
+        <v>https://music.apple.com/us/album/ay-dale/1862897623</v>
       </c>
       <c r="L40" t="str">
-        <v>Teary Eyes - YoungBoy Never Broke Again</v>
+        <v>Ay Dale - Farruko</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Bop It</v>
+        <v>Teary Eyes</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/bop-it/1867023470</v>
+        <v>https://music.apple.com/us/song/teary-eyes/1869534187</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>KUNTOLOGY 101</v>
+        <v>Slime Cry</v>
       </c>
       <c r="G41" t="str">
-        <v>2:50</v>
+        <v>2:45</v>
       </c>
       <c r="H41" t="str">
-        <v>Aliyah's Interlude</v>
+        <v>YoungBoy Never Broke Again</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/aliyahs-interlude/1708765232</v>
+        <v>https://music.apple.com/us/artist/youngboy-never-broke-again/1168822104</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/bop-it/1867023466</v>
+        <v>https://music.apple.com/us/album/teary-eyes/1869534167</v>
       </c>
       <c r="L41" t="str">
-        <v>Bop It - Aliyah's Interlude</v>
+        <v>Teary Eyes - YoungBoy Never Broke Again</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>My Everything</v>
+        <v>Bop It</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/my-everything/1862940302</v>
+        <v>https://music.apple.com/us/song/bop-it/1867023470</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>My Everything - Single</v>
+        <v>KUNTOLOGY 101</v>
       </c>
       <c r="G42" t="str">
-        <v>2:33</v>
+        <v>2:50</v>
       </c>
       <c r="H42" t="str">
-        <v>Lecrae</v>
+        <v>Aliyah's Interlude</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
+        <v>https://music.apple.com/us/artist/aliyahs-interlude/1708765232</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/my-everything/1862940301</v>
+        <v>https://music.apple.com/us/album/bop-it/1867023466</v>
       </c>
       <c r="L42" t="str">
-        <v>My Everything - Lecrae</v>
+        <v>Bop It - Aliyah's Interlude</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Whole Other Life</v>
+        <v>My Everything</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/whole-other-life/1858374798</v>
+        <v>https://music.apple.com/us/song/my-everything/1862940302</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Nat &amp; Alex Wolff</v>
+        <v>My Everything - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>3:30</v>
+        <v>2:33</v>
       </c>
       <c r="H43" t="str">
-        <v>Nat &amp; Alex Wolff</v>
+        <v>Lecrae</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/nat-alex-wolff/470903139</v>
+        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/whole-other-life/1858374775</v>
+        <v>https://music.apple.com/us/album/my-everything/1862940301</v>
       </c>
       <c r="L43" t="str">
-        <v>Whole Other Life - Nat &amp; Alex Wolff</v>
+        <v>My Everything - Lecrae</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Belladona</v>
+        <v>Whole Other Life</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/belladona/1862538378</v>
+        <v>https://music.apple.com/us/song/whole-other-life/1858374798</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Belladona</v>
+        <v>Nat &amp; Alex Wolff</v>
       </c>
       <c r="G44" t="str">
-        <v>3:32</v>
+        <v>3:30</v>
       </c>
       <c r="H44" t="str">
-        <v>Kenia Os</v>
+        <v>Nat &amp; Alex Wolff</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/nat-alex-wolff/470903139</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/belladona/1862538030</v>
+        <v>https://music.apple.com/us/album/whole-other-life/1858374775</v>
       </c>
       <c r="L44" t="str">
-        <v>Belladona - Kenia Os</v>
+        <v>Whole Other Life - Nat &amp; Alex Wolff</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Addicted to Love (From "Tell Me Lies (Season 3)")</v>
+        <v>Belladona</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/addicted-to-love-from-tell-me-lies-season-3/1867024880</v>
+        <v>https://music.apple.com/us/song/belladona/1862538378</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Addicted to Love (From "Tell Me Lies (Season 3)") - Single</v>
+        <v>Belladona</v>
       </c>
       <c r="G45" t="str">
-        <v>3:05</v>
+        <v>3:32</v>
       </c>
       <c r="H45" t="str">
-        <v>CHVRCHES</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/addicted-to-love-from-tell-me-lies-season-3/1867024879</v>
+        <v>https://music.apple.com/us/album/belladona/1862538030</v>
       </c>
       <c r="L45" t="str">
-        <v>Addicted to Love (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
+        <v>Belladona - Kenia Os</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Lie2Me</v>
+        <v>Addicted to Love (From "Tell Me Lies (Season 3)")</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/lie2me/1862762675</v>
+        <v>https://music.apple.com/us/song/addicted-to-love-from-tell-me-lies-season-3/1867024880</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Lie2Me - Single</v>
+        <v>Addicted to Love (From "Tell Me Lies (Season 3)") - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>3:03</v>
+        <v>3:05</v>
       </c>
       <c r="H46" t="str">
-        <v>DC THE DON</v>
+        <v>CHVRCHES</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/lie2me/1862762674</v>
+        <v>https://music.apple.com/us/album/addicted-to-love-from-tell-me-lies-season-3/1867024879</v>
       </c>
       <c r="L46" t="str">
-        <v>Lie2Me - DC THE DON</v>
+        <v>Addicted to Love (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>High On Heaven</v>
+        <v>Lie2Me</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/high-on-heaven/1859071765</v>
+        <v>https://music.apple.com/us/song/lie2me/1862762675</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>High On Heaven - Single</v>
+        <v>Lie2Me - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>3:19</v>
+        <v>3:03</v>
       </c>
       <c r="H47" t="str">
-        <v>Nessa Barrett</v>
+        <v>DC THE DON</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/high-on-heaven/1859071764</v>
+        <v>https://music.apple.com/us/album/lie2me/1862762674</v>
       </c>
       <c r="L47" t="str">
-        <v>High On Heaven - Nessa Barrett</v>
+        <v>Lie2Me - DC THE DON</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Most Wanted</v>
+        <v>High On Heaven</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/most-wanted/1844866135</v>
+        <v>https://music.apple.com/us/song/high-on-heaven/1859071765</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>My Ego Told Me To</v>
+        <v>High On Heaven - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>2:15</v>
+        <v>3:19</v>
       </c>
       <c r="H48" t="str">
-        <v>Leigh-Anne</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/most-wanted/1844865923</v>
+        <v>https://music.apple.com/us/album/high-on-heaven/1859071764</v>
       </c>
       <c r="L48" t="str">
-        <v>Most Wanted - Leigh-Anne</v>
+        <v>High On Heaven - Nessa Barrett</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Anything Is Possible</v>
+        <v>Most Wanted</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/anything-is-possible/1867583228</v>
+        <v>https://music.apple.com/us/song/most-wanted/1844866135</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Charlie The Wonderdog (Original Songs from the Motion Picture) - Single</v>
+        <v>My Ego Told Me To</v>
       </c>
       <c r="G49" t="str">
-        <v>2:57</v>
+        <v>2:15</v>
       </c>
       <c r="H49" t="str">
-        <v>Bryan Adams</v>
+        <v>Leigh-Anne</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/bryan-adams/85932</v>
+        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/anything-is-possible/1867583221</v>
+        <v>https://music.apple.com/us/album/most-wanted/1844865923</v>
       </c>
       <c r="L49" t="str">
-        <v>Anything Is Possible - Bryan Adams</v>
+        <v>Most Wanted - Leigh-Anne</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Volcano</v>
+        <v>Anything Is Possible</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/volcano/1862739924</v>
+        <v>https://music.apple.com/us/song/anything-is-possible/1867583228</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Volcano - Single</v>
+        <v>Charlie The Wonderdog (Original Songs from the Motion Picture) - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>2:28</v>
+        <v>2:57</v>
       </c>
       <c r="H50" t="str">
-        <v>Girl Tones</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
+        <v>https://music.apple.com/us/artist/bryan-adams/85932</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/volcano/1862739923</v>
+        <v>https://music.apple.com/us/album/anything-is-possible/1867583221</v>
       </c>
       <c r="L50" t="str">
-        <v>Volcano - Girl Tones</v>
+        <v>Anything Is Possible - Bryan Adams</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Into Oblivion</v>
+        <v>Volcano</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/into-oblivion/1868804164</v>
+        <v>https://music.apple.com/us/song/volcano/1862739924</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Into Oblivion</v>
+        <v>Volcano - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>3:34</v>
+        <v>2:28</v>
       </c>
       <c r="H51" t="str">
-        <v>Lamb of God</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/into-oblivion/1868804163</v>
+        <v>https://music.apple.com/us/album/volcano/1862739923</v>
       </c>
       <c r="L51" t="str">
-        <v>Into Oblivion - Lamb of God</v>
+        <v>Volcano - Girl Tones</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Beer and Blood Stains</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/beer-and-blood-stains/1838992321</v>
+        <v>https://music.apple.com/us/song/into-oblivion/1868804164</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Listen Up!</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G52" t="str">
-        <v>3:19</v>
+        <v>3:34</v>
       </c>
       <c r="H52" t="str">
-        <v>New Found Glory</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/new-found-glory/65551</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/beer-and-blood-stains/1838991916</v>
+        <v>https://music.apple.com/us/album/into-oblivion/1868804163</v>
       </c>
       <c r="L52" t="str">
-        <v>Beer and Blood Stains - New Found Glory</v>
+        <v>Into Oblivion - Lamb of God</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Numb</v>
+        <v>Beer and Blood Stains</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/numb/1860136324</v>
+        <v>https://music.apple.com/us/song/beer-and-blood-stains/1838992321</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Numb - Single</v>
+        <v>Listen Up!</v>
       </c>
       <c r="G53" t="str">
-        <v>2:13</v>
+        <v>3:19</v>
       </c>
       <c r="H53" t="str">
-        <v>Marc E. Bassy</v>
+        <v>New Found Glory</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
+        <v>https://music.apple.com/us/artist/new-found-glory/65551</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/numb/1860136319</v>
+        <v>https://music.apple.com/us/album/beer-and-blood-stains/1838991916</v>
       </c>
       <c r="L53" t="str">
-        <v>Numb - Marc E. Bassy</v>
+        <v>Beer and Blood Stains - New Found Glory</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Foxtrot</v>
+        <v>Numb</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/foxtrot/1860110201</v>
+        <v>https://music.apple.com/us/song/numb/1860136324</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Saputjiji</v>
+        <v>Numb - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>1:33</v>
+        <v>2:13</v>
       </c>
       <c r="H54" t="str">
-        <v>Tanya Tagaq</v>
+        <v>Marc E. Bassy</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/tanya-tagaq/257545265</v>
+        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/foxtrot/1860109752</v>
+        <v>https://music.apple.com/us/album/numb/1860136319</v>
       </c>
       <c r="L54" t="str">
-        <v>Foxtrot - Tanya Tagaq</v>
+        <v>Numb - Marc E. Bassy</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Digital Winter</v>
+        <v>Foxtrot</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/digital-winter/1820332238</v>
+        <v>https://music.apple.com/us/song/foxtrot/1860110201</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Stand On My Shoulders</v>
+        <v>Saputjiji</v>
       </c>
       <c r="G55" t="str">
-        <v>3:45</v>
+        <v>1:33</v>
       </c>
       <c r="H55" t="str">
-        <v>Ya Tseen</v>
+        <v>Tanya Tagaq</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/ya-tseen/1549782831</v>
+        <v>https://music.apple.com/us/artist/tanya-tagaq/257545265</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/digital-winter/1820332224</v>
+        <v>https://music.apple.com/us/album/foxtrot/1860109752</v>
       </c>
       <c r="L55" t="str">
-        <v>Digital Winter - Ya Tseen</v>
+        <v>Foxtrot - Tanya Tagaq</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Back To You</v>
+        <v>Digital Winter</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/back-to-you/1861380254</v>
+        <v>https://music.apple.com/us/song/digital-winter/1820332238</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Porcelain</v>
+        <v>Stand On My Shoulders</v>
       </c>
       <c r="G56" t="str">
-        <v>3:10</v>
+        <v>3:45</v>
       </c>
       <c r="H56" t="str">
-        <v>Peach PRC</v>
+        <v>Ya Tseen</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
+        <v>https://music.apple.com/us/artist/ya-tseen/1549782831</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/back-to-you/1861380240</v>
+        <v>https://music.apple.com/us/album/digital-winter/1820332224</v>
       </c>
       <c r="L56" t="str">
-        <v>Back To You - Peach PRC</v>
+        <v>Digital Winter - Ya Tseen</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Sleepwalker's Pendulum</v>
+        <v>Back To You</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/sleepwalkers-pendulum/1826115116</v>
+        <v>https://music.apple.com/us/song/back-to-you/1861380254</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Dreamer+</v>
+        <v>Porcelain</v>
       </c>
       <c r="G57" t="str">
-        <v>3:22</v>
+        <v>3:10</v>
       </c>
       <c r="H57" t="str">
-        <v>Sassy 009</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/sassy-009/1277035471</v>
+        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/sleepwalkers-pendulum/1826114506</v>
+        <v>https://music.apple.com/us/album/back-to-you/1861380240</v>
       </c>
       <c r="L57" t="str">
-        <v>Sleepwalker's Pendulum - Sassy 009</v>
+        <v>Back To You - Peach PRC</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Ruin Me</v>
+        <v>Sleepwalker's Pendulum</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/ruin-me/1850741533</v>
+        <v>https://music.apple.com/us/song/sleepwalkers-pendulum/1826115116</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>HEAD FIRST - EP</v>
+        <v>Dreamer+</v>
       </c>
       <c r="G58" t="str">
-        <v>2:31</v>
+        <v>3:22</v>
       </c>
       <c r="H58" t="str">
-        <v>Corbyn Besson</v>
+        <v>Sassy 009</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/corbyn-besson/810434797</v>
+        <v>https://music.apple.com/us/artist/sassy-009/1277035471</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/ruin-me/1850741514</v>
+        <v>https://music.apple.com/us/album/sleepwalkers-pendulum/1826114506</v>
       </c>
       <c r="L58" t="str">
-        <v>Ruin Me - Corbyn Besson</v>
+        <v>Sleepwalker's Pendulum - Sassy 009</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>w-w-w-w-w</v>
+        <v>Ruin Me</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/w-w-w-w-w/1846462521</v>
+        <v>https://music.apple.com/us/song/ruin-me/1850741533</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>the apple tree under the sea</v>
+        <v>HEAD FIRST - EP</v>
       </c>
       <c r="G59" t="str">
-        <v>4:26</v>
+        <v>2:31</v>
       </c>
       <c r="H59" t="str">
-        <v>hemlocke springs</v>
+        <v>Corbyn Besson</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/corbyn-besson/810434797</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/w-w-w-w-w/1846462383</v>
+        <v>https://music.apple.com/us/album/ruin-me/1850741514</v>
       </c>
       <c r="L59" t="str">
-        <v>w-w-w-w-w - hemlocke springs</v>
+        <v>Ruin Me - Corbyn Besson</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Struggle Bus</v>
+        <v>w-w-w-w-w</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/struggle-bus/1862024076</v>
+        <v>https://music.apple.com/us/song/w-w-w-w-w/1846462521</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Struggle Bus - Single</v>
+        <v>the apple tree under the sea</v>
       </c>
       <c r="G60" t="str">
-        <v>3:20</v>
+        <v>4:26</v>
       </c>
       <c r="H60" t="str">
-        <v>Iris Copperman</v>
+        <v>hemlocke springs</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
+        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/struggle-bus/1862024075</v>
+        <v>https://music.apple.com/us/album/w-w-w-w-w/1846462383</v>
       </c>
       <c r="L60" t="str">
-        <v>Struggle Bus - Iris Copperman</v>
+        <v>w-w-w-w-w - hemlocke springs</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Over</v>
+        <v>Struggle Bus</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/over/1862351820</v>
+        <v>https://music.apple.com/us/song/struggle-bus/1862024076</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Over - Single</v>
+        <v>Struggle Bus - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>3:49</v>
+        <v>3:20</v>
       </c>
       <c r="H61" t="str">
-        <v>Sydney Rose</v>
+        <v>Iris Copperman</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/sydney-rose/354936789</v>
+        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/over/1862351811</v>
+        <v>https://music.apple.com/us/album/struggle-bus/1862024075</v>
       </c>
       <c r="L61" t="str">
-        <v>Over - Sydney Rose</v>
+        <v>Struggle Bus - Iris Copperman</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Lean</v>
+        <v>Over</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/lean/1862829540</v>
+        <v>https://music.apple.com/us/song/over/1862351820</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Lean - Single</v>
+        <v>Over - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>3:53</v>
+        <v>3:49</v>
       </c>
       <c r="H62" t="str">
-        <v>Charlotte Day Wilson</v>
+        <v>Sydney Rose</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
+        <v>https://music.apple.com/us/artist/sydney-rose/354936789</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/lean/1862829538</v>
+        <v>https://music.apple.com/us/album/over/1862351811</v>
       </c>
       <c r="L62" t="str">
-        <v>Lean - Charlotte Day Wilson</v>
+        <v>Over - Sydney Rose</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>F**k It Up</v>
+        <v>Lean</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/f-k-it-up/1849002929</v>
+        <v>https://music.apple.com/us/song/lean/1862829540</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>F**k It Up - EP</v>
+        <v>Lean - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>3:32</v>
+        <v>3:53</v>
       </c>
       <c r="H63" t="str">
-        <v>Master Peace</v>
+        <v>Charlotte Day Wilson</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/master-peace/1477196856</v>
+        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/f-k-it-up/1849002928</v>
+        <v>https://music.apple.com/us/album/lean/1862829538</v>
       </c>
       <c r="L63" t="str">
-        <v>F**k It Up - Master Peace</v>
+        <v>Lean - Charlotte Day Wilson</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>La Carrera</v>
+        <v>F**k It Up</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/la-carrera/1863188476</v>
+        <v>https://music.apple.com/us/song/f-k-it-up/1849002929</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>La Carrera - Single</v>
+        <v>F**k It Up - EP</v>
       </c>
       <c r="G64" t="str">
-        <v>3:40</v>
+        <v>3:32</v>
       </c>
       <c r="H64" t="str">
-        <v>Moa Rivera</v>
+        <v>Master Peace</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/moa-rivera/1636808812</v>
+        <v>https://music.apple.com/us/artist/master-peace/1477196856</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/la-carrera/1863188474</v>
+        <v>https://music.apple.com/us/album/f-k-it-up/1849002928</v>
       </c>
       <c r="L64" t="str">
-        <v>La Carrera - Moa Rivera</v>
+        <v>F**k It Up - Master Peace</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>No Lube So Rude</v>
+        <v>La Carrera</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/no-lube-so-rude/1856065376</v>
+        <v>https://music.apple.com/us/song/la-carrera/1863188476</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>No Lube So Rude</v>
+        <v>La Carrera - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>2:48</v>
+        <v>3:40</v>
       </c>
       <c r="H65" t="str">
-        <v>Peaches</v>
+        <v>Moa Rivera</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/peaches/3028600</v>
+        <v>https://music.apple.com/us/artist/moa-rivera/1636808812</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/no-lube-so-rude/1856064995</v>
+        <v>https://music.apple.com/us/album/la-carrera/1863188474</v>
       </c>
       <c r="L65" t="str">
-        <v>No Lube So Rude - Peaches</v>
+        <v>La Carrera - Moa Rivera</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Somersaults</v>
+        <v>No Lube So Rude</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/somersaults/1847159408</v>
+        <v>https://music.apple.com/us/song/no-lube-so-rude/1856065376</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Somersaults</v>
+        <v>No Lube So Rude</v>
       </c>
       <c r="G66" t="str">
-        <v>4:32</v>
+        <v>2:48</v>
       </c>
       <c r="H66" t="str">
-        <v>deathcrash</v>
+        <v>Peaches</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/deathcrash/1461469738</v>
+        <v>https://music.apple.com/us/artist/peaches/3028600</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/somersaults/1847159406</v>
+        <v>https://music.apple.com/us/album/no-lube-so-rude/1856064995</v>
       </c>
       <c r="L66" t="str">
-        <v>Somersaults - deathcrash</v>
+        <v>No Lube So Rude - Peaches</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2005</v>
+        <v>Somersaults</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/2005/1854873143</v>
+        <v>https://music.apple.com/us/song/somersaults/1847159408</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Almost There</v>
+        <v>Somersaults</v>
       </c>
       <c r="G67" t="str">
-        <v>3:52</v>
+        <v>4:32</v>
       </c>
       <c r="H67" t="str">
-        <v>The Academy Is...</v>
+        <v>deathcrash</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/the-academy-is/75024274</v>
+        <v>https://music.apple.com/us/artist/deathcrash/1461469738</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/2005/1854873133</v>
+        <v>https://music.apple.com/us/album/somersaults/1847159406</v>
       </c>
       <c r="L67" t="str">
-        <v>2005 - The Academy Is...</v>
+        <v>Somersaults - deathcrash</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>I Had a Ball</v>
+        <v>2005</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-ball/1863330906</v>
+        <v>https://music.apple.com/us/song/2005/1854873143</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Palm Royale Season 2 (Apple TV Original Series Soundtrack)</v>
+        <v>Almost There</v>
       </c>
       <c r="G68" t="str">
-        <v>4:14</v>
+        <v>3:52</v>
       </c>
       <c r="H68" t="str">
-        <v>Kristen Wiig</v>
+        <v>The Academy Is...</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/kristen-wiig/273077223</v>
+        <v>https://music.apple.com/us/artist/the-academy-is/75024274</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-ball/1863330900</v>
+        <v>https://music.apple.com/us/album/2005/1854873133</v>
       </c>
       <c r="L68" t="str">
-        <v>I Had a Ball - Kristen Wiig</v>
+        <v>2005 - The Academy Is...</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>IDB</v>
+        <v>I Had a Ball</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/idb/1859084151</v>
+        <v>https://music.apple.com/us/song/i-had-a-ball/1863330906</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>IDB - Single</v>
+        <v>Palm Royale Season 2 (Apple TV Original Series Soundtrack)</v>
       </c>
       <c r="G69" t="str">
-        <v>2:52</v>
+        <v>4:14</v>
       </c>
       <c r="H69" t="str">
-        <v>42 Dugg</v>
+        <v>Kristen Wiig</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
+        <v>https://music.apple.com/us/artist/kristen-wiig/273077223</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/idb/1859084147</v>
+        <v>https://music.apple.com/us/album/i-had-a-ball/1863330900</v>
       </c>
       <c r="L69" t="str">
-        <v>IDB - 42 Dugg</v>
+        <v>I Had a Ball - Kristen Wiig</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Feel This Way</v>
+        <v>IDB</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/feel-this-way/1862902478</v>
+        <v>https://music.apple.com/us/song/idb/1859084151</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Feel This Way - Single</v>
+        <v>IDB - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>3:04</v>
+        <v>2:52</v>
       </c>
       <c r="H70" t="str">
-        <v>Josh Baker</v>
+        <v>42 Dugg</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
+        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/feel-this-way/1862902476</v>
+        <v>https://music.apple.com/us/album/idb/1859084147</v>
       </c>
       <c r="L70" t="str">
-        <v>Feel This Way - Josh Baker</v>
+        <v>IDB - 42 Dugg</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Falling</v>
+        <v>Feel This Way</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/falling/1861598107</v>
+        <v>https://music.apple.com/us/song/feel-this-way/1862902478</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Falling - Single</v>
+        <v>Feel This Way - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>3:02</v>
+        <v>3:04</v>
       </c>
       <c r="H71" t="str">
-        <v>Shimza</v>
+        <v>Josh Baker</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/shimza/697739898</v>
+        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/falling/1861598106</v>
+        <v>https://music.apple.com/us/album/feel-this-way/1862902476</v>
       </c>
       <c r="L71" t="str">
-        <v>Falling - Shimza</v>
+        <v>Feel This Way - Josh Baker</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Message to You</v>
+        <v>Falling</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/message-to-you/1867275596</v>
+        <v>https://music.apple.com/us/song/falling/1861598107</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Falling - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:37</v>
+        <v>3:02</v>
       </c>
       <c r="H72" t="str">
-        <v>Ty Myers</v>
+        <v>Shimza</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/shimza/697739898</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/message-to-you/1867275110</v>
+        <v>https://music.apple.com/us/album/falling/1861598106</v>
       </c>
       <c r="L72" t="str">
-        <v>Message to You - Ty Myers</v>
+        <v>Falling - Shimza</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>NOTHING IS REAL</v>
+        <v>Message to You</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/nothing-is-real/1866859742</v>
+        <v>https://music.apple.com/us/song/message-to-you/1867275596</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>NOTHING IS REAL - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G73" t="str">
-        <v>3:06</v>
+        <v>3:37</v>
       </c>
       <c r="H73" t="str">
-        <v>DESTIN CONRAD</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/destin-conrad/852999989</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/nothing-is-real/1866859497</v>
+        <v>https://music.apple.com/us/album/message-to-you/1867275110</v>
       </c>
       <c r="L73" t="str">
-        <v>NOTHING IS REAL - DESTIN CONRAD</v>
+        <v>Message to You - Ty Myers</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>CUÉNTAME</v>
+        <v>NOTHING IS REAL</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/cu%C3%A9ntame/1862973854</v>
+        <v>https://music.apple.com/us/song/nothing-is-real/1866859742</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>CUÉNTAME - Single</v>
+        <v>NOTHING IS REAL - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>2:42</v>
+        <v>3:06</v>
       </c>
       <c r="H74" t="str">
-        <v>FloyyMenor</v>
+        <v>DESTIN CONRAD</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/floyymenor/1676497551</v>
+        <v>https://music.apple.com/us/artist/destin-conrad/852999989</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/cu%C3%A9ntame/1862973853</v>
+        <v>https://music.apple.com/us/album/nothing-is-real/1866859497</v>
       </c>
       <c r="L74" t="str">
-        <v>CUÉNTAME - FloyyMenor</v>
+        <v>NOTHING IS REAL - DESTIN CONRAD</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>DANCE...</v>
+        <v>CUÉNTAME</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/dance/1867531306</v>
+        <v>https://music.apple.com/us/song/cu%C3%A9ntame/1862973854</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>CUÉNTAME - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>4:47</v>
+        <v>2:42</v>
       </c>
       <c r="H75" t="str">
-        <v>Slayyyter</v>
+        <v>FloyyMenor</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/floyymenor/1676497551</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/dance/1867530577</v>
+        <v>https://music.apple.com/us/album/cu%C3%A9ntame/1862973853</v>
       </c>
       <c r="L75" t="str">
-        <v>DANCE... - Slayyyter</v>
+        <v>CUÉNTAME - FloyyMenor</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>welcome to the circus</v>
+        <v>DANCE...</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/welcome-to-the-circus/1861011604</v>
+        <v>https://music.apple.com/us/song/dance/1867531306</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>welcome to the circus - Single</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G76" t="str">
-        <v>2:29</v>
+        <v>4:47</v>
       </c>
       <c r="H76" t="str">
-        <v>Jagwar Twin</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/jagwar-twin/1429051937</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/welcome-to-the-circus/1861011603</v>
+        <v>https://music.apple.com/us/album/dance/1867530577</v>
       </c>
       <c r="L76" t="str">
-        <v>welcome to the circus - Jagwar Twin</v>
+        <v>DANCE... - Slayyyter</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>playlist</v>
+        <v>welcome to the circus</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/playlist/1859009927</v>
+        <v>https://music.apple.com/us/song/welcome-to-the-circus/1861011604</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>playlist - Single</v>
+        <v>welcome to the circus - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>2:44</v>
+        <v>2:29</v>
       </c>
       <c r="H77" t="str">
-        <v>Tenroc</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/tenroc/1711844910</v>
+        <v>https://music.apple.com/us/artist/jagwar-twin/1429051937</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/playlist/1859009923</v>
+        <v>https://music.apple.com/us/album/welcome-to-the-circus/1861011603</v>
       </c>
       <c r="L77" t="str">
-        <v>playlist - Tenroc</v>
+        <v>welcome to the circus - Jagwar Twin</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Marlboro Man</v>
+        <v>playlist</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/marlboro-man/1862008741</v>
+        <v>https://music.apple.com/us/song/playlist/1859009927</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Marlboro Man - Single</v>
+        <v>playlist - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>3:23</v>
+        <v>2:44</v>
       </c>
       <c r="H78" t="str">
-        <v>Midland</v>
+        <v>Tenroc</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/midland/1171869852</v>
+        <v>https://music.apple.com/us/artist/tenroc/1711844910</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/marlboro-man/1862008740</v>
+        <v>https://music.apple.com/us/album/playlist/1859009923</v>
       </c>
       <c r="L78" t="str">
-        <v>Marlboro Man - Midland</v>
+        <v>playlist - Tenroc</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Enabling</v>
+        <v>Marlboro Man</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/enabling/1860993048</v>
+        <v>https://music.apple.com/us/song/marlboro-man/1862008741</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Enabling - Single</v>
+        <v>Marlboro Man - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:18</v>
+        <v>3:23</v>
       </c>
       <c r="H79" t="str">
-        <v>Tenille Townes</v>
+        <v>Midland</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/tenille-townes/1367713770</v>
+        <v>https://music.apple.com/us/artist/midland/1171869852</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/enabling/1860992859</v>
+        <v>https://music.apple.com/us/album/marlboro-man/1862008740</v>
       </c>
       <c r="L79" t="str">
-        <v>Enabling - Tenille Townes</v>
+        <v>Marlboro Man - Midland</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Two Broken Hearts</v>
+        <v>Enabling</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/two-broken-hearts/1841485428</v>
+        <v>https://music.apple.com/us/song/enabling/1860993048</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Steel Town</v>
+        <v>Enabling - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:53</v>
+        <v>3:18</v>
       </c>
       <c r="H80" t="str">
-        <v>Morgan Evans</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/morgan-evans/262665075</v>
+        <v>https://music.apple.com/us/artist/tenille-townes/1367713770</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/two-broken-hearts/1841484758</v>
+        <v>https://music.apple.com/us/album/enabling/1860992859</v>
       </c>
       <c r="L80" t="str">
-        <v>Two Broken Hearts - Morgan Evans</v>
+        <v>Enabling - Tenille Townes</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Lost in My Bed</v>
+        <v>Two Broken Hearts</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/lost-in-my-bed/1862222274</v>
+        <v>https://music.apple.com/us/song/two-broken-hearts/1841485428</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Lost in My Bed - Single</v>
+        <v>Steel Town</v>
       </c>
       <c r="G81" t="str">
-        <v>3:46</v>
+        <v>3:53</v>
       </c>
       <c r="H81" t="str">
-        <v>Khalil</v>
+        <v>Morgan Evans</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/khalil/1223181975</v>
+        <v>https://music.apple.com/us/artist/morgan-evans/262665075</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/lost-in-my-bed/1862222272</v>
+        <v>https://music.apple.com/us/album/two-broken-hearts/1841484758</v>
       </c>
       <c r="L81" t="str">
-        <v>Lost in My Bed - Khalil</v>
+        <v>Two Broken Hearts - Morgan Evans</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Father Time</v>
+        <v>Lost in My Bed</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/father-time/1858611581</v>
+        <v>https://music.apple.com/us/song/lost-in-my-bed/1862222274</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Honey Water</v>
+        <v>Lost in My Bed - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>1:58</v>
+        <v>3:46</v>
       </c>
       <c r="H82" t="str">
-        <v>Girlfriend</v>
+        <v>Khalil</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/girlfriend/1511096374</v>
+        <v>https://music.apple.com/us/artist/khalil/1223181975</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/father-time/1858611265</v>
+        <v>https://music.apple.com/us/album/lost-in-my-bed/1862222272</v>
       </c>
       <c r="L82" t="str">
-        <v>Father Time - Girlfriend</v>
+        <v>Lost in My Bed - Khalil</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>MVLAN</v>
+        <v>Father Time</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/mvlan/1867584574</v>
+        <v>https://music.apple.com/us/song/father-time/1858611581</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>MVLAN - Single</v>
+        <v>Honey Water</v>
       </c>
       <c r="G83" t="str">
-        <v>3:41</v>
+        <v>1:58</v>
       </c>
       <c r="H83" t="str">
-        <v>YOVNGCHIMI</v>
+        <v>Girlfriend</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/yovngchimi/1558257759</v>
+        <v>https://music.apple.com/us/artist/girlfriend/1511096374</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/mvlan/1867584573</v>
+        <v>https://music.apple.com/us/album/father-time/1858611265</v>
       </c>
       <c r="L83" t="str">
-        <v>MVLAN - YOVNGCHIMI</v>
+        <v>Father Time - Girlfriend</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Name In Blood</v>
+        <v>MVLAN</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/name-in-blood/1859687600</v>
+        <v>https://music.apple.com/us/song/mvlan/1867584574</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Engines of Demolition</v>
+        <v>MVLAN - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>4:36</v>
+        <v>3:41</v>
       </c>
       <c r="H84" t="str">
-        <v>Black Label Society</v>
+        <v>YOVNGCHIMI</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
+        <v>https://music.apple.com/us/artist/yovngchimi/1558257759</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/name-in-blood/1859687597</v>
+        <v>https://music.apple.com/us/album/mvlan/1867584573</v>
       </c>
       <c r="L84" t="str">
-        <v>Name In Blood - Black Label Society</v>
+        <v>MVLAN - YOVNGCHIMI</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Eyeball</v>
+        <v>Name In Blood</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/eyeball/1862539350</v>
+        <v>https://music.apple.com/us/song/name-in-blood/1859687600</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Eyeball - EP</v>
+        <v>Engines of Demolition</v>
       </c>
       <c r="G85" t="str">
-        <v>2:14</v>
+        <v>4:36</v>
       </c>
       <c r="H85" t="str">
-        <v>They Might Be Giants</v>
+        <v>Black Label Society</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/they-might-be-giants/149020</v>
+        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/eyeball/1862539346</v>
+        <v>https://music.apple.com/us/album/name-in-blood/1859687597</v>
       </c>
       <c r="L85" t="str">
-        <v>Eyeball - They Might Be Giants</v>
+        <v>Name In Blood - Black Label Society</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Long Gone</v>
+        <v>Eyeball</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/long-gone/1847573926</v>
+        <v>https://music.apple.com/us/song/eyeball/1862539350</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Tenterhooks</v>
+        <v>Eyeball - EP</v>
       </c>
       <c r="G86" t="str">
-        <v>3:55</v>
+        <v>2:14</v>
       </c>
       <c r="H86" t="str">
-        <v>Silversun Pickups</v>
+        <v>They Might Be Giants</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
+        <v>https://music.apple.com/us/artist/they-might-be-giants/149020</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/long-gone/1847573918</v>
+        <v>https://music.apple.com/us/album/eyeball/1862539346</v>
       </c>
       <c r="L86" t="str">
-        <v>Long Gone - Silversun Pickups</v>
+        <v>Eyeball - They Might Be Giants</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>iloveitiloveitiloveit</v>
+        <v>Long Gone</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/iloveitiloveitiloveit/1867034427</v>
+        <v>https://music.apple.com/us/song/long-gone/1847573926</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>iloveitiloveitiloveit - Single</v>
+        <v>Tenterhooks</v>
       </c>
       <c r="G87" t="str">
-        <v>3:03</v>
+        <v>3:55</v>
       </c>
       <c r="H87" t="str">
-        <v>Bella Kay</v>
+        <v>Silversun Pickups</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/iloveitiloveitiloveit/1867034426</v>
+        <v>https://music.apple.com/us/album/long-gone/1847573918</v>
       </c>
       <c r="L87" t="str">
-        <v>iloveitiloveitiloveit - Bella Kay</v>
+        <v>Long Gone - Silversun Pickups</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>To The Edge</v>
+        <v>iloveitiloveitiloveit</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/to-the-edge/1863513891</v>
+        <v>https://music.apple.com/us/song/iloveitiloveitiloveit/1867034427</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>To The Edge - Single</v>
+        <v>iloveitiloveitiloveit - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>3:19</v>
+        <v>3:03</v>
       </c>
       <c r="H88" t="str">
-        <v>Alex Jude</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/to-the-edge/1863513887</v>
+        <v>https://music.apple.com/us/album/iloveitiloveitiloveit/1867034426</v>
       </c>
       <c r="L88" t="str">
-        <v>To The Edge - Alex Jude</v>
+        <v>iloveitiloveitiloveit - Bella Kay</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>demons</v>
+        <v>To The Edge</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/demons/1861978106</v>
+        <v>https://music.apple.com/us/song/to-the-edge/1863513891</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>demons - Single</v>
+        <v>To The Edge - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>3:10</v>
+        <v>3:19</v>
       </c>
       <c r="H89" t="str">
-        <v>Josiah Queen</v>
+        <v>Alex Jude</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
+        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/demons/1861978105</v>
+        <v>https://music.apple.com/us/album/to-the-edge/1863513887</v>
       </c>
       <c r="L89" t="str">
-        <v>demons - Josiah Queen</v>
+        <v>To The Edge - Alex Jude</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Everyone Wants To Feel Like You Do</v>
+        <v>demons</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/everyone-wants-to-feel-like-you-do/1841949027</v>
+        <v>https://music.apple.com/us/song/demons/1861978106</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Valentine</v>
+        <v>demons - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>4:03</v>
+        <v>3:10</v>
       </c>
       <c r="H90" t="str">
-        <v>Courtney Marie Andrews</v>
+        <v>Josiah Queen</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/courtney-marie-andrews/287157006</v>
+        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/everyone-wants-to-feel-like-you-do/1841948802</v>
+        <v>https://music.apple.com/us/album/demons/1861978105</v>
       </c>
       <c r="L90" t="str">
-        <v>Everyone Wants To Feel Like You Do - Courtney Marie Andrews</v>
+        <v>demons - Josiah Queen</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Nothing Comes Easy</v>
+        <v>Everyone Wants To Feel Like You Do</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/nothing-comes-easy/1862757046</v>
+        <v>https://music.apple.com/us/song/everyone-wants-to-feel-like-you-do/1841949027</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Nothing Comes Easy - Single</v>
+        <v>Valentine</v>
       </c>
       <c r="G91" t="str">
-        <v>2:54</v>
+        <v>4:03</v>
       </c>
       <c r="H91" t="str">
-        <v>Joy Oladokun</v>
+        <v>Courtney Marie Andrews</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/joy-oladokun/699636664</v>
+        <v>https://music.apple.com/us/artist/courtney-marie-andrews/287157006</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/nothing-comes-easy/1862756744</v>
+        <v>https://music.apple.com/us/album/everyone-wants-to-feel-like-you-do/1841948802</v>
       </c>
       <c r="L91" t="str">
-        <v>Nothing Comes Easy - Joy Oladokun</v>
+        <v>Everyone Wants To Feel Like You Do - Courtney Marie Andrews</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Against the Dying of the Light</v>
+        <v>Nothing Comes Easy</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/against-the-dying-of-the-light/1860962165</v>
+        <v>https://music.apple.com/us/song/nothing-comes-easy/1862757046</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Against the Dying of the Light</v>
+        <v>Nothing Comes Easy - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>2:28</v>
+        <v>2:54</v>
       </c>
       <c r="H92" t="str">
-        <v>José González</v>
+        <v>Joy Oladokun</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
+        <v>https://music.apple.com/us/artist/joy-oladokun/699636664</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/against-the-dying-of-the-light/1860962162</v>
+        <v>https://music.apple.com/us/album/nothing-comes-easy/1862756744</v>
       </c>
       <c r="L92" t="str">
-        <v>Against the Dying of the Light - José González</v>
+        <v>Nothing Comes Easy - Joy Oladokun</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Big Boy Problems</v>
+        <v>Against the Dying of the Light</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/big-boy-problems/1851062438</v>
+        <v>https://music.apple.com/us/song/against-the-dying-of-the-light/1860962165</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Cynthia</v>
+        <v>Against the Dying of the Light</v>
       </c>
       <c r="G93" t="str">
-        <v>2:30</v>
+        <v>2:28</v>
       </c>
       <c r="H93" t="str">
-        <v>Sydney Ross Mitchell</v>
+        <v>José González</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/sydney-ross-mitchell/1373996317</v>
+        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/big-boy-problems/1851062193</v>
+        <v>https://music.apple.com/us/album/against-the-dying-of-the-light/1860962162</v>
       </c>
       <c r="L93" t="str">
-        <v>Big Boy Problems - Sydney Ross Mitchell</v>
+        <v>Against the Dying of the Light - José González</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Griever</v>
+        <v>Big Boy Problems</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/griever/1860950900</v>
+        <v>https://music.apple.com/us/song/big-boy-problems/1851062438</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Griever - Single</v>
+        <v>Cynthia</v>
       </c>
       <c r="G94" t="str">
-        <v>2:31</v>
+        <v>2:30</v>
       </c>
       <c r="H94" t="str">
-        <v>Avery Cochrane</v>
+        <v>Sydney Ross Mitchell</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/avery-cochrane/1556978969</v>
+        <v>https://music.apple.com/us/artist/sydney-ross-mitchell/1373996317</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/griever/1860950897</v>
+        <v>https://music.apple.com/us/album/big-boy-problems/1851062193</v>
       </c>
       <c r="L94" t="str">
-        <v>Griever - Avery Cochrane</v>
+        <v>Big Boy Problems - Sydney Ross Mitchell</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>7 BESOS</v>
+        <v>Griever</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/7-besos/1862927855</v>
+        <v>https://music.apple.com/us/song/griever/1860950900</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>7 BESOS - Single</v>
+        <v>Griever - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>3:21</v>
+        <v>2:31</v>
       </c>
       <c r="H95" t="str">
-        <v>LEGADO 7</v>
+        <v>Avery Cochrane</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
+        <v>https://music.apple.com/us/artist/avery-cochrane/1556978969</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/7-besos/1862927851</v>
+        <v>https://music.apple.com/us/album/griever/1860950897</v>
       </c>
       <c r="L95" t="str">
-        <v>7 BESOS - LEGADO 7</v>
+        <v>Griever - Avery Cochrane</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>UN LEÑO</v>
+        <v>7 BESOS</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/un-le%C3%B1o/1862904727</v>
+        <v>https://music.apple.com/us/song/7-besos/1862927855</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>UN LEÑO - Single</v>
+        <v>7 BESOS - Single</v>
       </c>
       <c r="G96" t="str">
-        <v>3:00</v>
+        <v>3:21</v>
       </c>
       <c r="H96" t="str">
-        <v>Armenta</v>
+        <v>LEGADO 7</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/armenta/1479504876</v>
+        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/un-le%C3%B1o/1862904402</v>
+        <v>https://music.apple.com/us/album/7-besos/1862927851</v>
       </c>
       <c r="L96" t="str">
-        <v>UN LEÑO - Armenta</v>
+        <v>7 BESOS - LEGADO 7</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Queen's Goodbye</v>
+        <v>UN LEÑO</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/queens-goodbye/1858554528</v>
+        <v>https://music.apple.com/us/song/un-le%C3%B1o/1862904727</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Mārara</v>
+        <v>UN LEÑO - Single</v>
       </c>
       <c r="G97" t="str">
-        <v>3:46</v>
+        <v>3:00</v>
       </c>
       <c r="H97" t="str">
-        <v>15 15</v>
+        <v>Armenta</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
+        <v>https://music.apple.com/us/artist/armenta/1479504876</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/queens-goodbye/1858554036</v>
+        <v>https://music.apple.com/us/album/un-le%C3%B1o/1862904402</v>
       </c>
       <c r="L97" t="str">
-        <v>Queen's Goodbye - 15 15</v>
+        <v>UN LEÑO - Armenta</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Bring Me Back To Life</v>
+        <v>Queen's Goodbye</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/bring-me-back-to-life/1851634795</v>
+        <v>https://music.apple.com/us/song/queens-goodbye/1858554528</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>Melancholia - EP</v>
+        <v>Mārara</v>
       </c>
       <c r="G98" t="str">
-        <v>3:24</v>
+        <v>3:46</v>
       </c>
       <c r="H98" t="str">
-        <v>JELISA</v>
+        <v>15 15</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/jelisa/1588318671</v>
+        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/bring-me-back-to-life/1851634783</v>
+        <v>https://music.apple.com/us/album/queens-goodbye/1858554036</v>
       </c>
       <c r="L98" t="str">
-        <v>Bring Me Back To Life - JELISA</v>
+        <v>Queen's Goodbye - 15 15</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>I Don't Care</v>
+        <v>Bring Me Back To Life</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/i-dont-care/1868429644</v>
+        <v>https://music.apple.com/us/song/bring-me-back-to-life/1851634795</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>I Don't Care - Single</v>
+        <v>Melancholia - EP</v>
       </c>
       <c r="G99" t="str">
-        <v>3:49</v>
+        <v>3:24</v>
       </c>
       <c r="H99" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>JELISA</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/jelisa/1588318671</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/i-dont-care/1868429639</v>
+        <v>https://music.apple.com/us/album/bring-me-back-to-life/1851634783</v>
       </c>
       <c r="L99" t="str">
-        <v>I Don't Care - Buffalo Traffic Jam</v>
+        <v>Bring Me Back To Life - JELISA</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Elastico (feat. KATE LINN)</v>
+        <v>I Don't Care</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/elastico-feat-kate-linn/1862157500</v>
+        <v>https://music.apple.com/us/song/i-dont-care/1868429644</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>Elastico (feat. KATE LINN) - Single</v>
+        <v>I Don't Care - Single</v>
       </c>
       <c r="G100" t="str">
-        <v>3:20</v>
+        <v>3:49</v>
       </c>
       <c r="H100" t="str">
-        <v>Fantomel</v>
+        <v>Buffalo Traffic Jam</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/fantomel/1736085960</v>
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
       </c>
       <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/elastico-feat-kate-linn/1862157496</v>
+        <v>https://music.apple.com/us/album/i-dont-care/1868429639</v>
       </c>
       <c r="L100" t="str">
-        <v>Elastico (feat. KATE LINN) - Fantomel</v>
+        <v>I Don't Care - Buffalo Traffic Jam</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Black &amp; Gold</v>
+        <v>Elastico (feat. KATE LINN)</v>
       </c>
       <c r="B101" t="str">
         <v/>
       </c>
       <c r="C101" t="str">
-        <v>https://music.apple.com/us/song/black-gold/1853914794</v>
+        <v>https://music.apple.com/us/song/elastico-feat-kate-linn/1862157500</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>Black &amp; Gold - Single</v>
+        <v>Elastico (feat. KATE LINN) - Single</v>
       </c>
       <c r="G101" t="str">
-        <v>3:12</v>
+        <v>3:20</v>
       </c>
       <c r="H101" t="str">
-        <v>Claptone</v>
+        <v>Fantomel</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J101" t="str">
-        <v>https://music.apple.com/us/artist/claptone/470488523</v>
+        <v>https://music.apple.com/us/artist/fantomel/1736085960</v>
       </c>
       <c r="K101" t="str">
-        <v>https://music.apple.com/us/album/black-gold/1853914793</v>
+        <v>https://music.apple.com/us/album/elastico-feat-kate-linn/1862157496</v>
       </c>
       <c r="L101" t="str">
-        <v>Black &amp; Gold - Claptone</v>
+        <v>Elastico (feat. KATE LINN) - Fantomel</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Close Your Eyes</v>
+        <v>Black &amp; Gold</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/close-your-eyes/1860632907</v>
+        <v>https://music.apple.com/us/song/black-gold/1853914794</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E102" t="str">
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Close Your Eyes - Single</v>
+        <v>Black &amp; Gold - Single</v>
       </c>
       <c r="G102" t="str">
-        <v>3:33</v>
+        <v>3:12</v>
       </c>
       <c r="H102" t="str">
-        <v>Adam Beyer</v>
+        <v>Claptone</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/adam-beyer/101672291</v>
+        <v>https://music.apple.com/us/artist/claptone/470488523</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/close-your-eyes/1860632569</v>
+        <v>https://music.apple.com/us/album/black-gold/1853914793</v>
       </c>
       <c r="L102" t="str">
-        <v>Close Your Eyes - Adam Beyer</v>
+        <v>Black &amp; Gold - Claptone</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Movement</v>
+        <v>Close Your Eyes</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/movement/1867063797</v>
+        <v>https://music.apple.com/us/song/close-your-eyes/1860632907</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E103" t="str">
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Movement - Single</v>
+        <v>Close Your Eyes - Single</v>
       </c>
       <c r="G103" t="str">
-        <v>3:07</v>
+        <v>3:33</v>
       </c>
       <c r="H103" t="str">
-        <v>Crankdat</v>
+        <v>Adam Beyer</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/crankdat/1073027547</v>
+        <v>https://music.apple.com/us/artist/adam-beyer/101672291</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/movement/1867063796</v>
+        <v>https://music.apple.com/us/album/close-your-eyes/1860632569</v>
       </c>
       <c r="L103" t="str">
-        <v>Movement - Crankdat</v>
+        <v>Close Your Eyes - Adam Beyer</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Ayi Giri</v>
+        <v>Movement</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/ayi-giri/1867306651</v>
+        <v>https://music.apple.com/us/song/movement/1867063797</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E104" t="str">
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Ayi Giri / Dopamine Machine - Single</v>
+        <v>Movement - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>3:06</v>
+        <v>3:07</v>
       </c>
       <c r="H104" t="str">
-        <v>Lilly Palmer</v>
+        <v>Crankdat</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/lilly-palmer/340777023</v>
+        <v>https://music.apple.com/us/artist/crankdat/1073027547</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/ayi-giri/1867306650</v>
+        <v>https://music.apple.com/us/album/movement/1867063796</v>
       </c>
       <c r="L104" t="str">
-        <v>Ayi Giri - Lilly Palmer</v>
+        <v>Movement - Crankdat</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>It's A Sin</v>
+        <v>Ayi Giri</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/its-a-sin/1861930282</v>
+        <v>https://music.apple.com/us/song/ayi-giri/1867306651</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E105" t="str">
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>It's A Sin - Single</v>
+        <v>Ayi Giri / Dopamine Machine - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>4:40</v>
+        <v>3:06</v>
       </c>
       <c r="H105" t="str">
-        <v>Ghost</v>
+        <v>Lilly Palmer</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/ghost/600730426</v>
+        <v>https://music.apple.com/us/artist/lilly-palmer/340777023</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/its-a-sin/1861930280</v>
+        <v>https://music.apple.com/us/album/ayi-giri/1867306650</v>
       </c>
       <c r="L105" t="str">
-        <v>It's A Sin - Ghost</v>
+        <v>Ayi Giri - Lilly Palmer</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Krushers Of The World</v>
+        <v>It's A Sin</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/krushers-of-the-world/1837718526</v>
+        <v>https://music.apple.com/us/song/its-a-sin/1861930282</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E106" t="str">
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Krushers Of The World</v>
+        <v>It's A Sin - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>4:20</v>
+        <v>4:40</v>
       </c>
       <c r="H106" t="str">
-        <v>Kreator</v>
+        <v>Ghost</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/kreator/3258504</v>
+        <v>https://music.apple.com/us/artist/ghost/600730426</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/krushers-of-the-world/1837718517</v>
+        <v>https://music.apple.com/us/album/its-a-sin/1861930280</v>
       </c>
       <c r="L106" t="str">
-        <v>Krushers Of The World - Kreator</v>
+        <v>It's A Sin - Ghost</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Thoroughbreds</v>
+        <v>Krushers Of The World</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/thoroughbreds/1863532917</v>
+        <v>https://music.apple.com/us/song/krushers-of-the-world/1837718526</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E107" t="str">
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Peace In Place</v>
+        <v>Krushers Of The World</v>
       </c>
       <c r="G107" t="str">
-        <v>3:24</v>
+        <v>4:20</v>
       </c>
       <c r="H107" t="str">
-        <v>Poison the Well</v>
+        <v>Kreator</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+        <v>https://music.apple.com/us/artist/kreator/3258504</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/thoroughbreds/1863532634</v>
+        <v>https://music.apple.com/us/album/krushers-of-the-world/1837718517</v>
       </c>
       <c r="L107" t="str">
-        <v>Thoroughbreds - Poison the Well</v>
+        <v>Krushers Of The World - Kreator</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
+        <v>Thoroughbreds</v>
+      </c>
+      <c r="B108" t="str">
+        <v/>
+      </c>
+      <c r="C108" t="str">
+        <v>https://music.apple.com/us/song/thoroughbreds/1863532917</v>
+      </c>
+      <c r="D108" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108" t="str">
+        <v>Peace In Place</v>
+      </c>
+      <c r="G108" t="str">
+        <v>3:24</v>
+      </c>
+      <c r="H108" t="str">
+        <v>Poison the Well</v>
+      </c>
+      <c r="I108" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J108" t="str">
+        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+      </c>
+      <c r="K108" t="str">
+        <v>https://music.apple.com/us/album/thoroughbreds/1863532634</v>
+      </c>
+      <c r="L108" t="str">
+        <v>Thoroughbreds - Poison the Well</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
         <v>Adversary</v>
       </c>
-      <c r="B108" t="str">
-        <v/>
-      </c>
-      <c r="C108" t="str">
+      <c r="B109" t="str">
+        <v/>
+      </c>
+      <c r="C109" t="str">
         <v>https://music.apple.com/us/song/adversary/1861901940</v>
       </c>
-      <c r="D108" t="str">
-        <v>2026-01-22</v>
-      </c>
-      <c r="E108" t="str">
-        <v/>
-      </c>
-      <c r="F108" t="str">
+      <c r="D109" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E109" t="str">
+        <v/>
+      </c>
+      <c r="F109" t="str">
         <v>Descent</v>
       </c>
-      <c r="G108" t="str">
+      <c r="G109" t="str">
         <v>3:17</v>
       </c>
-      <c r="H108" t="str">
+      <c r="H109" t="str">
         <v>Immolation</v>
       </c>
-      <c r="I108" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J108" t="str">
+      <c r="I109" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J109" t="str">
         <v>https://music.apple.com/us/artist/immolation/64874488</v>
       </c>
-      <c r="K108" t="str">
+      <c r="K109" t="str">
         <v>https://music.apple.com/us/album/adversary/1861901597</v>
       </c>
-      <c r="L108" t="str">
+      <c r="L109" t="str">
         <v>Adversary - Immolation</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L109"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L109"/>
+  <dimension ref="A1:L89"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -474,13 +474,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Wish I Didn't</v>
+        <v>Opening Night</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>https://music.apple.com/us/song/wish-i-didnt/1851297073</v>
+        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-23</v>
@@ -489,36 +489,36 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>Cloud 9</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G3" t="str">
-        <v>3:29</v>
+        <v>4:19</v>
       </c>
       <c r="H3" t="str">
-        <v>Megan Moroney</v>
+        <v>Arctic Monkeys</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
       </c>
       <c r="K3" t="str">
-        <v>https://music.apple.com/us/album/wish-i-didnt/1851296746</v>
+        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
       </c>
       <c r="L3" t="str">
-        <v>Wish I Didn't - Megan Moroney</v>
+        <v>Opening Night - Arctic Monkeys</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>AIR FORCE (BLACK DEMARCO)</v>
+        <v>FLACKITO JODYE (feat. Tokischa)</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>https://music.apple.com/us/song/air-force-black-demarco/1862935169</v>
+        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-23</v>
@@ -530,7 +530,7 @@
         <v>Don't Be Dumb</v>
       </c>
       <c r="G4" t="str">
-        <v>3:44</v>
+        <v>2:20</v>
       </c>
       <c r="H4" t="str">
         <v>A$AP Rocky</v>
@@ -542,21 +542,21 @@
         <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
       </c>
       <c r="K4" t="str">
-        <v>https://music.apple.com/us/album/air-force-black-demarco/1862934946</v>
+        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
       </c>
       <c r="L4" t="str">
-        <v>AIR FORCE (BLACK DEMARCO) - A$AP Rocky</v>
+        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Wall of Sound</v>
+        <v>CAMBIARÉ</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/wall-of-sound/1852566426</v>
+        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-23</v>
@@ -565,36 +565,36 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>Wuthering Heights</v>
+        <v>CAMBIARÉ - Single</v>
       </c>
       <c r="G5" t="str">
-        <v>2:24</v>
+        <v>3:01</v>
       </c>
       <c r="H5" t="str">
-        <v>Charli xcx</v>
+        <v>Luis Fonsi</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/wall-of-sound/1852566184</v>
+        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
       </c>
       <c r="L5" t="str">
-        <v>Wall of Sound - Charli xcx</v>
+        <v>CAMBIARÉ - Luis Fonsi</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Where's My Phone?</v>
+        <v>Last of a Dying Breed</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/wheres-my-phone/1860622553</v>
+        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-23</v>
@@ -603,36 +603,36 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G6" t="str">
-        <v>3:09</v>
+        <v>2:29</v>
       </c>
       <c r="H6" t="str">
-        <v>Mitski</v>
+        <v>Joji</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/wheres-my-phone/1860622550</v>
+        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
       </c>
       <c r="L6" t="str">
-        <v>Where's My Phone? - Mitski</v>
+        <v>Last of a Dying Breed - Joji</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>100</v>
+        <v>High Key</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/100/1858754874</v>
+        <v>https://music.apple.com/us/song/high-key/1847702418</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-23</v>
@@ -641,36 +641,36 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>Do You Still Love Me?</v>
+        <v>Vacancy</v>
       </c>
       <c r="G7" t="str">
-        <v>3:54</v>
+        <v>2:12</v>
       </c>
       <c r="H7" t="str">
-        <v>Ella Mai</v>
+        <v>Ari Lennox</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
-        <v>https://music.apple.com/us/artist/ella-mai/1160482144</v>
+        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/100/1858754868</v>
+        <v>https://music.apple.com/us/album/high-key/1847702412</v>
       </c>
       <c r="L7" t="str">
-        <v>100 - Ella Mai</v>
+        <v>High Key - Ari Lennox</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Por un P*****o no se llora (Salud mi Reina)</v>
+        <v>scared</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/por-un-p-o-no-se-llora-salud-mi-reina/1862587826</v>
+        <v>https://music.apple.com/us/song/scared/1862292863</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-23</v>
@@ -679,36 +679,36 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>Por un P*****o no se llora (Salud mi Reina) - Single</v>
+        <v>scared - Single</v>
       </c>
       <c r="G8" t="str">
-        <v>2:31</v>
+        <v>4:03</v>
       </c>
       <c r="H8" t="str">
-        <v>Manuel Turizo</v>
+        <v>Fred again..</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/manuel-turizo/1186116587</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/por-un-p-o-no-se-llora-salud-mi-reina/1862587821</v>
+        <v>https://music.apple.com/us/album/scared/1862292862</v>
       </c>
       <c r="L8" t="str">
-        <v>Por un P*****o no se llora (Salud mi Reina) - Manuel Turizo</v>
+        <v>scared - Fred again..</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Opening Night</v>
+        <v>Death of Love</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
+        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-23</v>
@@ -717,36 +717,36 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>HELP(2)</v>
+        <v>Trying Times</v>
       </c>
       <c r="G9" t="str">
-        <v>4:19</v>
+        <v>3:26</v>
       </c>
       <c r="H9" t="str">
-        <v>Arctic Monkeys</v>
+        <v>James Blake</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
+        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
       </c>
       <c r="L9" t="str">
-        <v>Opening Night - Arctic Monkeys</v>
+        <v>Death of Love - James Blake</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>L.U.C.K.Y</v>
+        <v>Big Ole Fancy House</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/l-u-c-k-y/1861895147</v>
+        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-23</v>
@@ -755,36 +755,36 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>Ö</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G10" t="str">
-        <v>2:18</v>
+        <v>4:03</v>
       </c>
       <c r="H10" t="str">
-        <v>Fcukers</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/l-u-c-k-y/1861895134</v>
+        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
       </c>
       <c r="L10" t="str">
-        <v>L.U.C.K.Y - Fcukers</v>
+        <v>Big Ole Fancy House - Parker McCollum</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Reclusive</v>
+        <v>Flo Jackson</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/reclusive/1860405760</v>
+        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-23</v>
@@ -793,36 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>sounds for someone</v>
+        <v>Flo Jackson - Single</v>
       </c>
       <c r="G11" t="str">
-        <v>3:06</v>
+        <v>2:23</v>
       </c>
       <c r="H11" t="str">
-        <v>Elmiene</v>
+        <v>Flo Milli</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
+        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/reclusive/1860405416</v>
+        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
       </c>
       <c r="L11" t="str">
-        <v>Reclusive - Elmiene</v>
+        <v>Flo Jackson - Flo Milli</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Flo Jackson</v>
+        <v>Site Unseen (feat. Waxahatchee)</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
+        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-23</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>Flo Jackson - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G12" t="str">
-        <v>2:23</v>
+        <v>2:46</v>
       </c>
       <c r="H12" t="str">
-        <v>Flo Milli</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
+        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
       </c>
       <c r="L12" t="str">
-        <v>Flo Jackson - Flo Milli</v>
+        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Site Unseen (feat. Waxahatchee)</v>
+        <v>Puppet Parade</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
+        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-23</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Creature of Habit</v>
+        <v>Megadeth</v>
       </c>
       <c r="G13" t="str">
-        <v>2:46</v>
+        <v>4:40</v>
       </c>
       <c r="H13" t="str">
-        <v>Courtney Barnett</v>
+        <v>Megadeth</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/megadeth/488289</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
+        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
       </c>
       <c r="L13" t="str">
-        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
+        <v>Puppet Parade - Megadeth</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Raft In The Sea</v>
+        <v>To Love Somebody</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/raft-in-the-sea/1847662987</v>
+        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-23</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>Cerulean</v>
+        <v>Cruel World</v>
       </c>
       <c r="G14" t="str">
-        <v>3:35</v>
+        <v>3:57</v>
       </c>
       <c r="H14" t="str">
-        <v>Danny L Harle</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/raft-in-the-sea/1847662970</v>
+        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
       </c>
       <c r="L14" t="str">
-        <v>Raft In The Sea - Danny L Harle</v>
+        <v>To Love Somebody - Holly Humberstone</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Good Night Baby</v>
+        <v>Nothing Is Impossible With You</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/good-night-baby/1849917462</v>
+        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-23</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Butterfly</v>
+        <v>Nothing Is Impossible With You - Single</v>
       </c>
       <c r="G15" t="str">
-        <v>4:21</v>
+        <v>4:14</v>
       </c>
       <c r="H15" t="str">
-        <v>Daphni</v>
+        <v>Cleo Sol</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/daphni/1282779393</v>
+        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/good-night-baby/1849916838</v>
+        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
       </c>
       <c r="L15" t="str">
-        <v>Good Night Baby - Daphni</v>
+        <v>Nothing Is Impossible With You - Cleo Sol</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Puppet Parade</v>
+        <v>HYPNOTIZE</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
+        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-23</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Megadeth</v>
+        <v>THE CORE - 核</v>
       </c>
       <c r="G16" t="str">
-        <v>4:40</v>
+        <v>2:50</v>
       </c>
       <c r="H16" t="str">
-        <v>Megadeth</v>
+        <v>XG</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/megadeth/488289</v>
+        <v>https://music.apple.com/us/artist/xg/1609409493</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
+        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
       </c>
       <c r="L16" t="str">
-        <v>Puppet Parade - Megadeth</v>
+        <v>HYPNOTIZE - XG</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>CAMBIARÉ</v>
+        <v>Dead End</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
+        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-23</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>CAMBIARÉ - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G17" t="str">
-        <v>3:01</v>
+        <v>4:05</v>
       </c>
       <c r="H17" t="str">
-        <v>Luis Fonsi</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
+        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
       </c>
       <c r="L17" t="str">
-        <v>CAMBIARÉ - Luis Fonsi</v>
+        <v>Dead End - Snail Mail</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Orange County (feat. Bizarrap, Kara Jackson &amp; Anoushka Shankar)</v>
+        <v>Do I Wanna Know?</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/orange-county-feat-bizarrap-kara-jackson-anoushka-shankar/1837237867</v>
+        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-23</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>The Mountain</v>
+        <v>Do I Wanna Know? - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>3:28</v>
+        <v>3:52</v>
       </c>
       <c r="H18" t="str">
-        <v>Gorillaz</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
+        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/orange-county-feat-bizarrap-kara-jackson-anoushka-shankar/1837237742</v>
+        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
       </c>
       <c r="L18" t="str">
-        <v>Orange County (feat. Bizarrap, Kara Jackson &amp; Anoushka Shankar) - Gorillaz</v>
+        <v>Do I Wanna Know? - Dove Cameron</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Lluvia</v>
+        <v>Una y Otra Vez</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/lluvia/1868476403</v>
+        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-23</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>LA 8VA MARAVILLA</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G19" t="str">
-        <v>3:24</v>
+        <v>3:02</v>
       </c>
       <c r="H19" t="str">
-        <v>Arcángel</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/lluvia/1868476390</v>
+        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
       </c>
       <c r="L19" t="str">
-        <v>Lluvia - Arcángel</v>
+        <v>Una y Otra Vez - Kenia Os</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Knife</v>
+        <v>BAD</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/knife/1862720450</v>
+        <v>https://music.apple.com/us/song/bad/1869095326</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-23</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>THE SIN : VANISH</v>
+        <v>BAD - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>2:19</v>
+        <v>2:15</v>
       </c>
       <c r="H20" t="str">
-        <v>ENHYPEN</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/enhypen/1541011620</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/knife/1862720020</v>
+        <v>https://music.apple.com/us/album/bad/1869095325</v>
       </c>
       <c r="L20" t="str">
-        <v>Knife - ENHYPEN</v>
+        <v>BAD - Chelsea Cutler</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>bad enough</v>
+        <v>Losing You</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/bad-enough/1846949125</v>
+        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-23</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>locket</v>
+        <v>F.I.G</v>
       </c>
       <c r="G21" t="str">
-        <v>3:42</v>
+        <v>2:22</v>
       </c>
       <c r="H21" t="str">
-        <v>Madison Beer</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/madison-beer/696146587</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/bad-enough/1846949115</v>
+        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
       </c>
       <c r="L21" t="str">
-        <v>bad enough - Madison Beer</v>
+        <v>Losing You - Naomi Scott</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>bad</v>
+        <v>Me Voy A La C******a</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/bad/1851566880</v>
+        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-23</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>bad - Single</v>
+        <v>Infinito</v>
       </c>
       <c r="G22" t="str">
-        <v>2:41</v>
+        <v>2:14</v>
       </c>
       <c r="H22" t="str">
-        <v>Saint Harison</v>
+        <v>Yandel</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/yandel/72929426</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/bad/1851566879</v>
+        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
       </c>
       <c r="L22" t="str">
-        <v>bad - Saint Harison</v>
+        <v>Me Voy A La C******a - Yandel</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Beat Yourself Up</v>
+        <v>Sexy For Me</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/beat-yourself-up/1845189973</v>
+        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-23</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Whatever's Clever!</v>
+        <v>The Last Dance (Part 1)</v>
       </c>
       <c r="G23" t="str">
-        <v>2:58</v>
+        <v>2:08</v>
       </c>
       <c r="H23" t="str">
-        <v>Charlie Puth</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/beat-yourself-up/1845189970</v>
+        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
       </c>
       <c r="L23" t="str">
-        <v>Beat Yourself Up - Charlie Puth</v>
+        <v>Sexy For Me - Jason Derulo</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Roommates</v>
+        <v>Turbulence</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/roommates/1854567105</v>
+        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-23</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>luck... or something</v>
+        <v>REAL, Vol. 1 - EP</v>
       </c>
       <c r="G24" t="str">
-        <v>2:52</v>
+        <v>2:25</v>
       </c>
       <c r="H24" t="str">
-        <v>Hilary Duff</v>
+        <v>Wizkid</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
+        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/roommates/1854567102</v>
+        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
       </c>
       <c r="L24" t="str">
-        <v>Roommates - Hilary Duff</v>
+        <v>Turbulence - Wizkid</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2SIDED</v>
+        <v>I’m Good (From The Movie “GOAT”)</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/2sided/1862571197</v>
+        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-23</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Ambiguous Desire</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G25" t="str">
-        <v>2:57</v>
+        <v>2:59</v>
       </c>
       <c r="H25" t="str">
-        <v>Arlo Parks</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/2sided/1862570378</v>
+        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L25" t="str">
-        <v>2SIDED - Arlo Parks</v>
+        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Feel Alive</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/feel-alive/1851368171</v>
+        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-23</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>ODYSSEY</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
       </c>
       <c r="G26" t="str">
-        <v>2:48</v>
+        <v>3:47</v>
       </c>
       <c r="H26" t="str">
-        <v>ILLENIUM</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/feel-alive/1851368154</v>
+        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
       </c>
       <c r="L26" t="str">
-        <v>Feel Alive - ILLENIUM</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>God Spoke</v>
+        <v>ESCONDIDAS</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/god-spoke/1853069638</v>
+        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-23</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>COSMIC OPERA ACT I</v>
+        <v>SILENCIO HABLA</v>
       </c>
       <c r="G27" t="str">
-        <v>1:14</v>
+        <v>2:53</v>
       </c>
       <c r="H27" t="str">
-        <v>Labrinth</v>
+        <v>Oscar Ortiz</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/god-spoke/1853069628</v>
+        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
       </c>
       <c r="L27" t="str">
-        <v>God Spoke - Labrinth</v>
+        <v>ESCONDIDAS - Oscar Ortiz</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Risk Takers</v>
+        <v>Alabama Beauty Queen</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/risk-takers/1866642666</v>
+        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-23</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>El Mundo Es Tuyo (Inspired by Clika The Movie)</v>
+        <v>Act I</v>
       </c>
       <c r="G28" t="str">
-        <v>2:35</v>
+        <v>3:43</v>
       </c>
       <c r="H28" t="str">
-        <v>Herencia de Patrones</v>
+        <v>Kashus Culpepper</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/herencia-de-patrones/1295294734</v>
+        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/risk-takers/1866642665</v>
+        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
       </c>
       <c r="L28" t="str">
-        <v>Risk Takers - Herencia de Patrones</v>
+        <v>Alabama Beauty Queen - Kashus Culpepper</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Never Comin' Back</v>
+        <v>Imposter</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/never-comin-back/1862970557</v>
+        <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-23</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Never Comin' Back - Single</v>
+        <v>How Did I Get Here?</v>
       </c>
       <c r="G29" t="str">
-        <v>3:57</v>
+        <v>2:38</v>
       </c>
       <c r="H29" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/never-comin-back/1862970555</v>
+        <v>https://music.apple.com/us/album/imposter/1842408037</v>
       </c>
       <c r="L29" t="str">
-        <v>Never Comin' Back - Flatland Cavalry</v>
+        <v>Imposter - Louis Tomlinson</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II))</v>
+        <v>Puddles (Zero 7 Remix)</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/lay-your-heartache-onto-mine-songs-from-and-inspired/1867273711</v>
+        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-23</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II)) - Single</v>
+        <v>Puddles (Zero 7 Remix) - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>3:18</v>
+        <v>6:01</v>
       </c>
       <c r="H30" t="str">
-        <v>Carter Faith</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/lay-your-heartache-onto-mine-songs-from-and-inspired/1867273471</v>
+        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
       </c>
       <c r="L30" t="str">
-        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II)) - Carter Faith</v>
+        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
+        <v>Little Miss (Misdemeanor)</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
+        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-23</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
+        <v>Little Miss (Misdemeanor) - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>3:47</v>
+        <v>2:24</v>
       </c>
       <c r="H31" t="str">
-        <v>Dolly Parton</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
+        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
       </c>
       <c r="L31" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
+        <v>Little Miss (Misdemeanor) - GIRLSET</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Traffic Lights (feat. Thom Yorke)</v>
+        <v>I Could Get Used To This</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/traffic-lights-feat-thom-yorke/1861644315</v>
+        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-23</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Honora</v>
+        <v>I Could Get Used To This - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>5:41</v>
+        <v>3:41</v>
       </c>
       <c r="H32" t="str">
-        <v>Flea</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/traffic-lights-feat-thom-yorke/1861644307</v>
+        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
       </c>
       <c r="L32" t="str">
-        <v>Traffic Lights (feat. Thom Yorke) - Flea</v>
+        <v>I Could Get Used To This - Jessie Ware</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Inferno (from "Heated Rivalry")</v>
+        <v>LA VILLA</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/inferno-from-heated-rivalry/1868783886</v>
+        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-23</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Heated Rivalry (Original Series Soundtrack)</v>
+        <v>HOPI SENDÉ</v>
       </c>
       <c r="G33" t="str">
-        <v>4:26</v>
+        <v>3:12</v>
       </c>
       <c r="H33" t="str">
-        <v>Peter Peter</v>
+        <v>Ryan Castro</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/peter-peter/71305428</v>
+        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/inferno-from-heated-rivalry/1868783596</v>
+        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
       </c>
       <c r="L33" t="str">
-        <v>Inferno (from "Heated Rivalry") - Peter Peter</v>
+        <v>LA VILLA - Ryan Castro</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Yo Yan</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/yo-yan/1867888651</v>
+        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-23</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Kora - Single</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G34" t="str">
-        <v>2:00</v>
+        <v>3:27</v>
       </c>
       <c r="H34" t="str">
-        <v>Skrillex</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/yo-yan/1867888650</v>
+        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
       </c>
       <c r="L34" t="str">
-        <v>Yo Yan - Skrillex</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Jogodo</v>
+        <v>Thick One</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/jogodo/1867908454</v>
+        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-23</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>REAL, Vol. 1 - EP</v>
+        <v>Part 3</v>
       </c>
       <c r="G35" t="str">
-        <v>3:08</v>
+        <v>2:49</v>
       </c>
       <c r="H35" t="str">
-        <v>Wizkid</v>
+        <v>42 Dugg</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
+        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/jogodo/1867908237</v>
+        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
       </c>
       <c r="L35" t="str">
-        <v>Jogodo - Wizkid</v>
+        <v>Thick One - 42 Dugg</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Made It Out Alive</v>
+        <v>How Much Did You Get For Your Soul</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/made-it-out-alive/1867596345</v>
+        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-23</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Suffering From Success</v>
+        <v>World's Gone Wrong</v>
       </c>
       <c r="G36" t="str">
-        <v>3:00</v>
+        <v>3:59</v>
       </c>
       <c r="H36" t="str">
-        <v>Dee Mula</v>
+        <v>Lucinda Williams</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/dee-mula/1330325377</v>
+        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/made-it-out-alive/1867596343</v>
+        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
       </c>
       <c r="L36" t="str">
-        <v>Made It Out Alive - Dee Mula</v>
+        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>One of Them Ones</v>
+        <v>THUM</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/one-of-them-ones/1868850365</v>
+        <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-23</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>One of Them Ones - Single</v>
+        <v>THUM - Single</v>
       </c>
       <c r="G37" t="str">
-        <v>3:05</v>
+        <v>2:11</v>
       </c>
       <c r="H37" t="str">
-        <v>Veeze</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/one-of-them-ones/1868850364</v>
+        <v>https://music.apple.com/us/album/thum/1863009357</v>
       </c>
       <c r="L37" t="str">
-        <v>One of Them Ones - Veeze</v>
+        <v>THUM - Violet Grohl</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Como Es Que Se Hace</v>
+        <v>(I'm a) Rock "N" Roller</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/como-es-que-se-hace/1864227584</v>
+        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-23</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Como Es Que Se Hace - Single</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G38" t="str">
-        <v>3:25</v>
+        <v>3:32</v>
       </c>
       <c r="H38" t="str">
-        <v>Yandel</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/yandel/72929426</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/como-es-que-se-hace/1864227582</v>
+        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
       </c>
       <c r="L38" t="str">
-        <v>Como Es Que Se Hace - Yandel</v>
+        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Ever Since U Left Me (I Went Deaf)</v>
+        <v>Excuses For Love</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/ever-since-u-left-me-i-went-deaf/1863124175</v>
+        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-23</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Coke Wave 3.5: Narcos</v>
+        <v>Hyperlove</v>
       </c>
       <c r="G39" t="str">
-        <v>2:16</v>
+        <v>3:04</v>
       </c>
       <c r="H39" t="str">
-        <v>French Montana</v>
+        <v>MIKA</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/french-montana/475816358</v>
+        <v>https://music.apple.com/us/artist/mika/184932871</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/ever-since-u-left-me-i-went-deaf/1863124168</v>
+        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
       </c>
       <c r="L39" t="str">
-        <v>Ever Since U Left Me (I Went Deaf) - French Montana</v>
+        <v>Excuses For Love - MIKA</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Ay Dale</v>
+        <v>3 Tears</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/ay-dale/1862897966</v>
+        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-23</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Ay Dale - Single</v>
+        <v>3 Tears - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>2:26</v>
+        <v>2:50</v>
       </c>
       <c r="H40" t="str">
-        <v>Farruko</v>
+        <v>Mergui</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/farruko/364377482</v>
+        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/ay-dale/1862897623</v>
+        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
       </c>
       <c r="L40" t="str">
-        <v>Ay Dale - Farruko</v>
+        <v>3 Tears - Mergui</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Teary Eyes</v>
+        <v>Church Girl</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/teary-eyes/1869534187</v>
+        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-23</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Slime Cry</v>
+        <v>Church Girl - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>2:45</v>
+        <v>3:19</v>
       </c>
       <c r="H41" t="str">
-        <v>YoungBoy Never Broke Again</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/youngboy-never-broke-again/1168822104</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/teary-eyes/1869534167</v>
+        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
       </c>
       <c r="L41" t="str">
-        <v>Teary Eyes - YoungBoy Never Broke Again</v>
+        <v>Church Girl - Carly Pearce</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Bop It</v>
+        <v>Funeral</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/bop-it/1867023470</v>
+        <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-23</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>KUNTOLOGY 101</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G42" t="str">
-        <v>2:50</v>
+        <v>4:03</v>
       </c>
       <c r="H42" t="str">
-        <v>Aliyah's Interlude</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/aliyahs-interlude/1708765232</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/bop-it/1867023466</v>
+        <v>https://music.apple.com/us/album/funeral/1867616617</v>
       </c>
       <c r="L42" t="str">
-        <v>Bop It - Aliyah's Interlude</v>
+        <v>Funeral - Dermot Kennedy</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>My Everything</v>
+        <v>Say Yes</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/my-everything/1862940302</v>
+        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-23</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>My Everything - Single</v>
+        <v>Say Yes - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>2:33</v>
+        <v>2:50</v>
       </c>
       <c r="H43" t="str">
-        <v>Lecrae</v>
+        <v>Marques Anthony</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
+        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/my-everything/1862940301</v>
+        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
       </c>
       <c r="L43" t="str">
-        <v>My Everything - Lecrae</v>
+        <v>Say Yes - Marques Anthony</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Whole Other Life</v>
+        <v>LOVE ME (feat. Stevie Wonder)</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/whole-other-life/1858374798</v>
+        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-23</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Nat &amp; Alex Wolff</v>
+        <v>CAMPILATION</v>
       </c>
       <c r="G44" t="str">
-        <v>3:30</v>
+        <v>3:10</v>
       </c>
       <c r="H44" t="str">
-        <v>Nat &amp; Alex Wolff</v>
+        <v>Camper</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/nat-alex-wolff/470903139</v>
+        <v>https://music.apple.com/us/artist/camper/1514886616</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/whole-other-life/1858374775</v>
+        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
       </c>
       <c r="L44" t="str">
-        <v>Whole Other Life - Nat &amp; Alex Wolff</v>
+        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Belladona</v>
+        <v>UP TO MY NECK IN U</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/belladona/1862538378</v>
+        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-23</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Belladona</v>
+        <v>UP TO MY NECK IN U - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>3:32</v>
+        <v>2:17</v>
       </c>
       <c r="H45" t="str">
-        <v>Kenia Os</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/belladona/1862538030</v>
+        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
       </c>
       <c r="L45" t="str">
-        <v>Belladona - Kenia Os</v>
+        <v>UP TO MY NECK IN U - Ledbyher</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Addicted to Love (From "Tell Me Lies (Season 3)")</v>
+        <v>Wallflower</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/addicted-to-love-from-tell-me-lies-season-3/1867024880</v>
+        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-23</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Addicted to Love (From "Tell Me Lies (Season 3)") - Single</v>
+        <v>Wallflower - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>3:05</v>
+        <v>3:25</v>
       </c>
       <c r="H46" t="str">
-        <v>CHVRCHES</v>
+        <v>Sikarus</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
+        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/addicted-to-love-from-tell-me-lies-season-3/1867024879</v>
+        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
       </c>
       <c r="L46" t="str">
-        <v>Addicted to Love (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
+        <v>Wallflower - Sikarus</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Lie2Me</v>
+        <v>You Phase</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/lie2me/1862762675</v>
+        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-23</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Lie2Me - Single</v>
+        <v>You Phase - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>3:03</v>
+        <v>2:51</v>
       </c>
       <c r="H47" t="str">
-        <v>DC THE DON</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/lie2me/1862762674</v>
+        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
       </c>
       <c r="L47" t="str">
-        <v>Lie2Me - DC THE DON</v>
+        <v>You Phase - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>High On Heaven</v>
+        <v>Miss Independent</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/high-on-heaven/1859071765</v>
+        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-23</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>High On Heaven - Single</v>
+        <v>Miss Independent - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>3:19</v>
+        <v>2:40</v>
       </c>
       <c r="H48" t="str">
-        <v>Nessa Barrett</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/high-on-heaven/1859071764</v>
+        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
       </c>
       <c r="L48" t="str">
-        <v>High On Heaven - Nessa Barrett</v>
+        <v>Miss Independent - 1Ski OG</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Most Wanted</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown)</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/most-wanted/1844866135</v>
+        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown/1870678482</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-23</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>My Ego Told Me To</v>
+        <v>SO BE IT</v>
       </c>
       <c r="G49" t="str">
-        <v>2:15</v>
+        <v>5:47</v>
       </c>
       <c r="H49" t="str">
-        <v>Leigh-Anne</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/most-wanted/1844865923</v>
+        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown/1870678481</v>
       </c>
       <c r="L49" t="str">
-        <v>Most Wanted - Leigh-Anne</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) - Elevation Worship</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Anything Is Possible</v>
+        <v>go again</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/anything-is-possible/1867583228</v>
+        <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-23</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Charlie The Wonderdog (Original Songs from the Motion Picture) - Single</v>
+        <v>go again - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>2:57</v>
+        <v>2:07</v>
       </c>
       <c r="H50" t="str">
-        <v>Bryan Adams</v>
+        <v>NateTaylorr</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/bryan-adams/85932</v>
+        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/anything-is-possible/1867583221</v>
+        <v>https://music.apple.com/us/album/go-again/1868987193</v>
       </c>
       <c r="L50" t="str">
-        <v>Anything Is Possible - Bryan Adams</v>
+        <v>go again - NateTaylorr</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Volcano</v>
+        <v>Autopilot</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/volcano/1862739924</v>
+        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-23</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Volcano - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G51" t="str">
-        <v>2:28</v>
+        <v>2:46</v>
       </c>
       <c r="H51" t="str">
-        <v>Girl Tones</v>
+        <v>ALEXSUCKS</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/volcano/1862739923</v>
+        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
       </c>
       <c r="L51" t="str">
-        <v>Volcano - Girl Tones</v>
+        <v>Autopilot - ALEXSUCKS</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Into Oblivion</v>
+        <v>Portrait of My Heart (feat. Brendan Yates)</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/into-oblivion/1868804164</v>
+        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-23</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Into Oblivion</v>
+        <v>Portrait of My Heart - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>3:34</v>
+        <v>3:04</v>
       </c>
       <c r="H52" t="str">
-        <v>Lamb of God</v>
+        <v>SPELLLING</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/into-oblivion/1868804163</v>
+        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
       </c>
       <c r="L52" t="str">
-        <v>Into Oblivion - Lamb of God</v>
+        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Beer and Blood Stains</v>
+        <v>In Violet</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/beer-and-blood-stains/1838992321</v>
+        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-23</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Listen Up!</v>
+        <v>Death in the Business of Whaling</v>
       </c>
       <c r="G53" t="str">
-        <v>3:19</v>
+        <v>4:09</v>
       </c>
       <c r="H53" t="str">
-        <v>New Found Glory</v>
+        <v>Searows</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/new-found-glory/65551</v>
+        <v>https://music.apple.com/us/artist/searows/1607240507</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/beer-and-blood-stains/1838991916</v>
+        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
       </c>
       <c r="L53" t="str">
-        <v>Beer and Blood Stains - New Found Glory</v>
+        <v>In Violet - Searows</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Numb</v>
+        <v>Baby Run</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/numb/1860136324</v>
+        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-23</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Numb - Single</v>
+        <v>Baby Run - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>2:13</v>
+        <v>4:47</v>
       </c>
       <c r="H54" t="str">
-        <v>Marc E. Bassy</v>
+        <v>Jimi Jules</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
+        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/numb/1860136319</v>
+        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
       </c>
       <c r="L54" t="str">
-        <v>Numb - Marc E. Bassy</v>
+        <v>Baby Run - Jimi Jules</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Foxtrot</v>
+        <v>What If We Don't</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/foxtrot/1860110201</v>
+        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-23</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Saputjiji</v>
+        <v>What If We Don't - Single</v>
       </c>
       <c r="G55" t="str">
-        <v>1:33</v>
+        <v>3:06</v>
       </c>
       <c r="H55" t="str">
-        <v>Tanya Tagaq</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/tanya-tagaq/257545265</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/foxtrot/1860109752</v>
+        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
       </c>
       <c r="L55" t="str">
-        <v>Foxtrot - Tanya Tagaq</v>
+        <v>What If We Don't - Ashley McBryde</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Digital Winter</v>
+        <v>Hagamos Que</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/digital-winter/1820332238</v>
+        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-23</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Stand On My Shoulders</v>
+        <v>Hagamos Que - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>3:45</v>
+        <v>2:58</v>
       </c>
       <c r="H56" t="str">
-        <v>Ya Tseen</v>
+        <v>Juanes</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/ya-tseen/1549782831</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/digital-winter/1820332224</v>
+        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
       </c>
       <c r="L56" t="str">
-        <v>Digital Winter - Ya Tseen</v>
+        <v>Hagamos Que - Juanes</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Back To You</v>
+        <v>World Change Me</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/back-to-you/1861380254</v>
+        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-23</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Porcelain</v>
+        <v>World Change Me - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>3:10</v>
+        <v>3:03</v>
       </c>
       <c r="H57" t="str">
-        <v>Peach PRC</v>
+        <v>Max McNown</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/back-to-you/1861380240</v>
+        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
       </c>
       <c r="L57" t="str">
-        <v>Back To You - Peach PRC</v>
+        <v>World Change Me - Max McNown</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Sleepwalker's Pendulum</v>
+        <v>Exclusive</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/sleepwalkers-pendulum/1826115116</v>
+        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-23</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Dreamer+</v>
+        <v>Exclusive - EP</v>
       </c>
       <c r="G58" t="str">
-        <v>3:22</v>
+        <v>3:20</v>
       </c>
       <c r="H58" t="str">
-        <v>Sassy 009</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/sassy-009/1277035471</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/sleepwalkers-pendulum/1826114506</v>
+        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
       </c>
       <c r="L58" t="str">
-        <v>Sleepwalker's Pendulum - Sassy 009</v>
+        <v>Exclusive - Hudson Westbrook</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Ruin Me</v>
+        <v>Say Less</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/ruin-me/1850741533</v>
+        <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-23</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>HEAD FIRST - EP</v>
+        <v>Say Less - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>2:31</v>
+        <v>2:18</v>
       </c>
       <c r="H59" t="str">
-        <v>Corbyn Besson</v>
+        <v>JYT</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/corbyn-besson/810434797</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/ruin-me/1850741514</v>
+        <v>https://music.apple.com/us/album/say-less/1867910115</v>
       </c>
       <c r="L59" t="str">
-        <v>Ruin Me - Corbyn Besson</v>
+        <v>Say Less - JYT</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>w-w-w-w-w</v>
+        <v>Angels Cry</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/w-w-w-w-w/1846462521</v>
+        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-23</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>the apple tree under the sea</v>
+        <v>X's for Eyes (Deluxe)</v>
       </c>
       <c r="G60" t="str">
-        <v>4:26</v>
+        <v>3:52</v>
       </c>
       <c r="H60" t="str">
-        <v>hemlocke springs</v>
+        <v>The Red Jumpsuit Apparatus</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/w-w-w-w-w/1846462383</v>
+        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
       </c>
       <c r="L60" t="str">
-        <v>w-w-w-w-w - hemlocke springs</v>
+        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Struggle Bus</v>
+        <v>Over You</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/struggle-bus/1862024076</v>
+        <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-23</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Struggle Bus - Single</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G61" t="str">
-        <v>3:20</v>
+        <v>4:44</v>
       </c>
       <c r="H61" t="str">
-        <v>Iris Copperman</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/struggle-bus/1862024075</v>
+        <v>https://music.apple.com/us/album/over-you/1846189472</v>
       </c>
       <c r="L61" t="str">
-        <v>Struggle Bus - Iris Copperman</v>
+        <v>Over You - Chet Faker</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Over</v>
+        <v>Chala (My Soul Is on a Loop)</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/over/1862351820</v>
+        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-23</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Over - Single</v>
+        <v>Chala (My Soul Is on a Loop) - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>3:49</v>
+        <v>2:42</v>
       </c>
       <c r="H62" t="str">
-        <v>Sydney Rose</v>
+        <v>Barry Can't Swim</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/sydney-rose/354936789</v>
+        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/over/1862351811</v>
+        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
       </c>
       <c r="L62" t="str">
-        <v>Over - Sydney Rose</v>
+        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Lean</v>
+        <v>starlight feat. Madeline Follin</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/lean/1862829540</v>
+        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-23</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Lean - Single</v>
+        <v>starlight feat. Madeline Follin - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>3:53</v>
+        <v>3:06</v>
       </c>
       <c r="H63" t="str">
-        <v>Charlotte Day Wilson</v>
+        <v>Disco Lines</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
+        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/lean/1862829538</v>
+        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
       </c>
       <c r="L63" t="str">
-        <v>Lean - Charlotte Day Wilson</v>
+        <v>starlight feat. Madeline Follin - Disco Lines</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>F**k It Up</v>
+        <v>Locked In (feat. Trippie Redd)</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/f-k-it-up/1849002929</v>
+        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-23</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>F**k It Up - EP</v>
+        <v>Locked In (feat. Trippie Redd) - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>3:32</v>
+        <v>2:48</v>
       </c>
       <c r="H64" t="str">
-        <v>Master Peace</v>
+        <v>David Guetta</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/master-peace/1477196856</v>
+        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/f-k-it-up/1849002928</v>
+        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
       </c>
       <c r="L64" t="str">
-        <v>F**k It Up - Master Peace</v>
+        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>La Carrera</v>
+        <v>Rejoice</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/la-carrera/1863188476</v>
+        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-23</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>La Carrera - Single</v>
+        <v>Rejoice - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>3:40</v>
+        <v>4:20</v>
       </c>
       <c r="H65" t="str">
-        <v>Moa Rivera</v>
+        <v>Def Leppard</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/moa-rivera/1636808812</v>
+        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/la-carrera/1863188474</v>
+        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
       </c>
       <c r="L65" t="str">
-        <v>La Carrera - Moa Rivera</v>
+        <v>Rejoice - Def Leppard</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>No Lube So Rude</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/no-lube-so-rude/1856065376</v>
+        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-23</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>No Lube So Rude</v>
+        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>2:48</v>
+        <v>2:58</v>
       </c>
       <c r="H66" t="str">
-        <v>Peaches</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/peaches/3028600</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/no-lube-so-rude/1856064995</v>
+        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
       </c>
       <c r="L66" t="str">
-        <v>No Lube So Rude - Peaches</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Somersaults</v>
+        <v>Lucky Day</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/somersaults/1847159408</v>
+        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-23</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Somersaults</v>
+        <v>Speed Kills</v>
       </c>
       <c r="G67" t="str">
-        <v>4:32</v>
+        <v>3:13</v>
       </c>
       <c r="H67" t="str">
-        <v>deathcrash</v>
+        <v>Ally Evenson</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/deathcrash/1461469738</v>
+        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/somersaults/1847159406</v>
+        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
       </c>
       <c r="L67" t="str">
-        <v>Somersaults - deathcrash</v>
+        <v>Lucky Day - Ally Evenson</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2005</v>
+        <v>Breathe On It</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/2005/1854873143</v>
+        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-23</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Almost There</v>
+        <v>Breathe On It - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>3:52</v>
+        <v>4:00</v>
       </c>
       <c r="H68" t="str">
-        <v>The Academy Is...</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/the-academy-is/75024274</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/2005/1854873133</v>
+        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
       </c>
       <c r="L68" t="str">
-        <v>2005 - The Academy Is...</v>
+        <v>Breathe On It - Tauren Wells</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>I Had a Ball</v>
+        <v>Easy</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-ball/1863330906</v>
+        <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-23</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Palm Royale Season 2 (Apple TV Original Series Soundtrack)</v>
+        <v>Easy - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>4:14</v>
+        <v>4:30</v>
       </c>
       <c r="H69" t="str">
-        <v>Kristen Wiig</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/kristen-wiig/273077223</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-ball/1863330900</v>
+        <v>https://music.apple.com/us/album/easy/1863456903</v>
       </c>
       <c r="L69" t="str">
-        <v>I Had a Ball - Kristen Wiig</v>
+        <v>Easy - lydi lynn</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>IDB</v>
+        <v>Break Me In</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/idb/1859084151</v>
+        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-23</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>IDB - Single</v>
+        <v>Break Me In - Single</v>
       </c>
       <c r="G70" t="str">
         <v>2:52</v>
       </c>
       <c r="H70" t="str">
-        <v>42 Dugg</v>
+        <v>Joyce Wrice</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
+        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/idb/1859084147</v>
+        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
       </c>
       <c r="L70" t="str">
-        <v>IDB - 42 Dugg</v>
+        <v>Break Me In - Joyce Wrice</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Feel This Way</v>
+        <v>Long Live Love</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/feel-this-way/1862902478</v>
+        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-23</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Feel This Way - Single</v>
+        <v>Long Live Love - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>3:04</v>
+        <v>2:36</v>
       </c>
       <c r="H71" t="str">
-        <v>Josh Baker</v>
+        <v>Sugar</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
+        <v>https://music.apple.com/us/artist/sugar/530175867</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/feel-this-way/1862902476</v>
+        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
       </c>
       <c r="L71" t="str">
-        <v>Feel This Way - Josh Baker</v>
+        <v>Long Live Love - Sugar</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Falling</v>
+        <v>Depressed</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/falling/1861598107</v>
+        <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-23</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Falling - Single</v>
+        <v>Boycott Heaven</v>
       </c>
       <c r="G72" t="str">
-        <v>3:02</v>
+        <v>3:32</v>
       </c>
       <c r="H72" t="str">
-        <v>Shimza</v>
+        <v>The Format</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/shimza/697739898</v>
+        <v>https://music.apple.com/us/artist/the-format/3064903</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/falling/1861598106</v>
+        <v>https://music.apple.com/us/album/depressed/1840399886</v>
       </c>
       <c r="L72" t="str">
-        <v>Falling - Shimza</v>
+        <v>Depressed - The Format</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Message to You</v>
+        <v>Empty Hands</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/message-to-you/1867275596</v>
+        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-23</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Empty Hands</v>
       </c>
       <c r="G73" t="str">
-        <v>3:37</v>
+        <v>3:09</v>
       </c>
       <c r="H73" t="str">
-        <v>Ty Myers</v>
+        <v>Poppy</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/message-to-you/1867275110</v>
+        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
       </c>
       <c r="L73" t="str">
-        <v>Message to You - Ty Myers</v>
+        <v>Empty Hands - Poppy</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>NOTHING IS REAL</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/nothing-is-real/1866859742</v>
+        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-23</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>NOTHING IS REAL - Single</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="G74" t="str">
-        <v>3:06</v>
+        <v>3:45</v>
       </c>
       <c r="H74" t="str">
-        <v>DESTIN CONRAD</v>
+        <v>NEEDTOBREATHE</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/destin-conrad/852999989</v>
+        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/nothing-is-real/1866859497</v>
+        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
       </c>
       <c r="L74" t="str">
-        <v>NOTHING IS REAL - DESTIN CONRAD</v>
+        <v>The Long Surrender - NEEDTOBREATHE</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>CUÉNTAME</v>
+        <v>Angela</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/cu%C3%A9ntame/1862973854</v>
+        <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-23</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>CUÉNTAME - Single</v>
+        <v>Angela - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>2:42</v>
+        <v>3:32</v>
       </c>
       <c r="H75" t="str">
-        <v>FloyyMenor</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/floyymenor/1676497551</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/cu%C3%A9ntame/1862973853</v>
+        <v>https://music.apple.com/us/album/angela/1866624256</v>
       </c>
       <c r="L75" t="str">
-        <v>CUÉNTAME - FloyyMenor</v>
+        <v>Angela - Hayden Everett</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DANCE...</v>
+        <v>Disappear</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/dance/1867531306</v>
+        <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-23</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>Greyhound</v>
       </c>
       <c r="G76" t="str">
-        <v>4:47</v>
+        <v>3:31</v>
       </c>
       <c r="H76" t="str">
-        <v>Slayyyter</v>
+        <v>Katie Tupper</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/dance/1867530577</v>
+        <v>https://music.apple.com/us/album/disappear/1847663546</v>
       </c>
       <c r="L76" t="str">
-        <v>DANCE... - Slayyyter</v>
+        <v>Disappear - Katie Tupper</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>welcome to the circus</v>
+        <v>Catapult</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/welcome-to-the-circus/1861011604</v>
+        <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-23</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>welcome to the circus - Single</v>
+        <v>Catapult - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>2:29</v>
+        <v>2:57</v>
       </c>
       <c r="H77" t="str">
-        <v>Jagwar Twin</v>
+        <v>Cape Francis</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/jagwar-twin/1429051937</v>
+        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/welcome-to-the-circus/1861011603</v>
+        <v>https://music.apple.com/us/album/catapult/1862951333</v>
       </c>
       <c r="L77" t="str">
-        <v>welcome to the circus - Jagwar Twin</v>
+        <v>Catapult - Cape Francis</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>playlist</v>
+        <v>Think Twice</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/playlist/1859009927</v>
+        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-23</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>playlist - Single</v>
+        <v>Think Twice - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>2:44</v>
+        <v>2:22</v>
       </c>
       <c r="H78" t="str">
-        <v>Tenroc</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/tenroc/1711844910</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/playlist/1859009923</v>
+        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
       </c>
       <c r="L78" t="str">
-        <v>playlist - Tenroc</v>
+        <v>Think Twice - Leonie Biney</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Marlboro Man</v>
+        <v>LOVESONGS</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/marlboro-man/1862008741</v>
+        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-23</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Marlboro Man - Single</v>
+        <v>BEAUTIFUL MADNESS</v>
       </c>
       <c r="G79" t="str">
-        <v>3:23</v>
+        <v>3:33</v>
       </c>
       <c r="H79" t="str">
-        <v>Midland</v>
+        <v>Agnes</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/midland/1171869852</v>
+        <v>https://music.apple.com/us/artist/agnes/42568985</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/marlboro-man/1862008740</v>
+        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
       </c>
       <c r="L79" t="str">
-        <v>Marlboro Man - Midland</v>
+        <v>LOVESONGS - Agnes</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Enabling</v>
+        <v>Down South</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/enabling/1860993048</v>
+        <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-23</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Enabling - Single</v>
+        <v>Down South - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:18</v>
+        <v>2:19</v>
       </c>
       <c r="H80" t="str">
-        <v>Tenille Townes</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/tenille-townes/1367713770</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/enabling/1860992859</v>
+        <v>https://music.apple.com/us/album/down-south/1861010788</v>
       </c>
       <c r="L80" t="str">
-        <v>Enabling - Tenille Townes</v>
+        <v>Down South - Trap Dickey</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Two Broken Hearts</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/two-broken-hearts/1841485428</v>
+        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-23</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Steel Town</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:53</v>
+        <v>2:16</v>
       </c>
       <c r="H81" t="str">
-        <v>Morgan Evans</v>
+        <v>SALIMATA</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/morgan-evans/262665075</v>
+        <v>https://music.apple.com/us/artist/salimata/690253822</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/two-broken-hearts/1841484758</v>
+        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
       </c>
       <c r="L81" t="str">
-        <v>Two Broken Hearts - Morgan Evans</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Lost in My Bed</v>
+        <v>Love Like This</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/lost-in-my-bed/1862222274</v>
+        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-23</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Lost in My Bed - Single</v>
+        <v>Love Like This - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>3:46</v>
+        <v>3:30</v>
       </c>
       <c r="H82" t="str">
-        <v>Khalil</v>
+        <v>Jacob Banks</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/khalil/1223181975</v>
+        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/lost-in-my-bed/1862222272</v>
+        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
       </c>
       <c r="L82" t="str">
-        <v>Lost in My Bed - Khalil</v>
+        <v>Love Like This - Jacob Banks</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Father Time</v>
+        <v>Plan Plan</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/father-time/1858611581</v>
+        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-23</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Honey Water</v>
+        <v>La Locura</v>
       </c>
       <c r="G83" t="str">
-        <v>1:58</v>
+        <v>3:10</v>
       </c>
       <c r="H83" t="str">
-        <v>Girlfriend</v>
+        <v>Funky</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/girlfriend/1511096374</v>
+        <v>https://music.apple.com/us/artist/funky/80960663</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/father-time/1858611265</v>
+        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
       </c>
       <c r="L83" t="str">
-        <v>Father Time - Girlfriend</v>
+        <v>Plan Plan - Funky</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>MVLAN</v>
+        <v>double edged sword</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/mvlan/1867584574</v>
+        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-23</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>MVLAN - Single</v>
+        <v>double edged sword - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>3:41</v>
+        <v>3:28</v>
       </c>
       <c r="H84" t="str">
-        <v>YOVNGCHIMI</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/yovngchimi/1558257759</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/mvlan/1867584573</v>
+        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
       </c>
       <c r="L84" t="str">
-        <v>MVLAN - YOVNGCHIMI</v>
+        <v>double edged sword - Hailey Picardi</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Name In Blood</v>
+        <v>SOMEWHERE IN BETWEEN</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/name-in-blood/1859687600</v>
+        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-23</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Engines of Demolition</v>
+        <v>SOMEWHERE IN BETWEEN - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>4:36</v>
+        <v>3:27</v>
       </c>
       <c r="H85" t="str">
-        <v>Black Label Society</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
+        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/name-in-blood/1859687597</v>
+        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
       </c>
       <c r="L85" t="str">
-        <v>Name In Blood - Black Label Society</v>
+        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Eyeball</v>
+        <v>The Decay</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/eyeball/1862539350</v>
+        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-23</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Eyeball - EP</v>
+        <v>What Remains (Midnight Edition)</v>
       </c>
       <c r="G86" t="str">
-        <v>2:14</v>
+        <v>3:20</v>
       </c>
       <c r="H86" t="str">
-        <v>They Might Be Giants</v>
+        <v>Pop Evil</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/they-might-be-giants/149020</v>
+        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/eyeball/1862539346</v>
+        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
       </c>
       <c r="L86" t="str">
-        <v>Eyeball - They Might Be Giants</v>
+        <v>The Decay - Pop Evil</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Long Gone</v>
+        <v>3111</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/long-gone/1847573926</v>
+        <v>https://music.apple.com/us/song/3111/1862225387</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-23</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Tenterhooks</v>
+        <v>Goliath</v>
       </c>
       <c r="G87" t="str">
-        <v>3:55</v>
+        <v>4:08</v>
       </c>
       <c r="H87" t="str">
-        <v>Silversun Pickups</v>
+        <v>Exodus</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/long-gone/1847573918</v>
+        <v>https://music.apple.com/us/album/3111/1862225385</v>
       </c>
       <c r="L87" t="str">
-        <v>Long Gone - Silversun Pickups</v>
+        <v>3111 - Exodus</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>iloveitiloveitiloveit</v>
+        <v>Touch My Love And Die</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/iloveitiloveitiloveit/1867034427</v>
+        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-23</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>iloveitiloveitiloveit - Single</v>
+        <v>Touch My Love And Die - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>3:03</v>
+        <v>2:57</v>
       </c>
       <c r="H88" t="str">
-        <v>Bella Kay</v>
+        <v>Myrkur</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/iloveitiloveitiloveit/1867034426</v>
+        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
       </c>
       <c r="L88" t="str">
-        <v>iloveitiloveitiloveit - Bella Kay</v>
+        <v>Touch My Love And Die - Myrkur</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>To The Edge</v>
+        <v>Bomb To A Knife Fight</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/to-the-edge/1863513891</v>
+        <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-23</v>
@@ -3757,790 +3757,30 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>To The Edge - Single</v>
+        <v>Bomb To A Knife Fight - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>3:19</v>
+        <v>2:41</v>
       </c>
       <c r="H89" t="str">
-        <v>Alex Jude</v>
+        <v>The Barbarians of California</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/to-the-edge/1863513887</v>
+        <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
       </c>
       <c r="L89" t="str">
-        <v>To The Edge - Alex Jude</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v>demons</v>
-      </c>
-      <c r="B90" t="str">
-        <v/>
-      </c>
-      <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/demons/1861978106</v>
-      </c>
-      <c r="D90" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E90" t="str">
-        <v/>
-      </c>
-      <c r="F90" t="str">
-        <v>demons - Single</v>
-      </c>
-      <c r="G90" t="str">
-        <v>3:10</v>
-      </c>
-      <c r="H90" t="str">
-        <v>Josiah Queen</v>
-      </c>
-      <c r="I90" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
-      </c>
-      <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/demons/1861978105</v>
-      </c>
-      <c r="L90" t="str">
-        <v>demons - Josiah Queen</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v>Everyone Wants To Feel Like You Do</v>
-      </c>
-      <c r="B91" t="str">
-        <v/>
-      </c>
-      <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/everyone-wants-to-feel-like-you-do/1841949027</v>
-      </c>
-      <c r="D91" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E91" t="str">
-        <v/>
-      </c>
-      <c r="F91" t="str">
-        <v>Valentine</v>
-      </c>
-      <c r="G91" t="str">
-        <v>4:03</v>
-      </c>
-      <c r="H91" t="str">
-        <v>Courtney Marie Andrews</v>
-      </c>
-      <c r="I91" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/courtney-marie-andrews/287157006</v>
-      </c>
-      <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/everyone-wants-to-feel-like-you-do/1841948802</v>
-      </c>
-      <c r="L91" t="str">
-        <v>Everyone Wants To Feel Like You Do - Courtney Marie Andrews</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v>Nothing Comes Easy</v>
-      </c>
-      <c r="B92" t="str">
-        <v/>
-      </c>
-      <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/nothing-comes-easy/1862757046</v>
-      </c>
-      <c r="D92" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E92" t="str">
-        <v/>
-      </c>
-      <c r="F92" t="str">
-        <v>Nothing Comes Easy - Single</v>
-      </c>
-      <c r="G92" t="str">
-        <v>2:54</v>
-      </c>
-      <c r="H92" t="str">
-        <v>Joy Oladokun</v>
-      </c>
-      <c r="I92" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/joy-oladokun/699636664</v>
-      </c>
-      <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/nothing-comes-easy/1862756744</v>
-      </c>
-      <c r="L92" t="str">
-        <v>Nothing Comes Easy - Joy Oladokun</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v>Against the Dying of the Light</v>
-      </c>
-      <c r="B93" t="str">
-        <v/>
-      </c>
-      <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/against-the-dying-of-the-light/1860962165</v>
-      </c>
-      <c r="D93" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E93" t="str">
-        <v/>
-      </c>
-      <c r="F93" t="str">
-        <v>Against the Dying of the Light</v>
-      </c>
-      <c r="G93" t="str">
-        <v>2:28</v>
-      </c>
-      <c r="H93" t="str">
-        <v>José González</v>
-      </c>
-      <c r="I93" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
-      </c>
-      <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/against-the-dying-of-the-light/1860962162</v>
-      </c>
-      <c r="L93" t="str">
-        <v>Against the Dying of the Light - José González</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v>Big Boy Problems</v>
-      </c>
-      <c r="B94" t="str">
-        <v/>
-      </c>
-      <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/big-boy-problems/1851062438</v>
-      </c>
-      <c r="D94" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E94" t="str">
-        <v/>
-      </c>
-      <c r="F94" t="str">
-        <v>Cynthia</v>
-      </c>
-      <c r="G94" t="str">
-        <v>2:30</v>
-      </c>
-      <c r="H94" t="str">
-        <v>Sydney Ross Mitchell</v>
-      </c>
-      <c r="I94" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/sydney-ross-mitchell/1373996317</v>
-      </c>
-      <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/big-boy-problems/1851062193</v>
-      </c>
-      <c r="L94" t="str">
-        <v>Big Boy Problems - Sydney Ross Mitchell</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v>Griever</v>
-      </c>
-      <c r="B95" t="str">
-        <v/>
-      </c>
-      <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/griever/1860950900</v>
-      </c>
-      <c r="D95" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E95" t="str">
-        <v/>
-      </c>
-      <c r="F95" t="str">
-        <v>Griever - Single</v>
-      </c>
-      <c r="G95" t="str">
-        <v>2:31</v>
-      </c>
-      <c r="H95" t="str">
-        <v>Avery Cochrane</v>
-      </c>
-      <c r="I95" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/avery-cochrane/1556978969</v>
-      </c>
-      <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/griever/1860950897</v>
-      </c>
-      <c r="L95" t="str">
-        <v>Griever - Avery Cochrane</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v>7 BESOS</v>
-      </c>
-      <c r="B96" t="str">
-        <v/>
-      </c>
-      <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/7-besos/1862927855</v>
-      </c>
-      <c r="D96" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E96" t="str">
-        <v/>
-      </c>
-      <c r="F96" t="str">
-        <v>7 BESOS - Single</v>
-      </c>
-      <c r="G96" t="str">
-        <v>3:21</v>
-      </c>
-      <c r="H96" t="str">
-        <v>LEGADO 7</v>
-      </c>
-      <c r="I96" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
-      </c>
-      <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/7-besos/1862927851</v>
-      </c>
-      <c r="L96" t="str">
-        <v>7 BESOS - LEGADO 7</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v>UN LEÑO</v>
-      </c>
-      <c r="B97" t="str">
-        <v/>
-      </c>
-      <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/un-le%C3%B1o/1862904727</v>
-      </c>
-      <c r="D97" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E97" t="str">
-        <v/>
-      </c>
-      <c r="F97" t="str">
-        <v>UN LEÑO - Single</v>
-      </c>
-      <c r="G97" t="str">
-        <v>3:00</v>
-      </c>
-      <c r="H97" t="str">
-        <v>Armenta</v>
-      </c>
-      <c r="I97" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/armenta/1479504876</v>
-      </c>
-      <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/un-le%C3%B1o/1862904402</v>
-      </c>
-      <c r="L97" t="str">
-        <v>UN LEÑO - Armenta</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v>Queen's Goodbye</v>
-      </c>
-      <c r="B98" t="str">
-        <v/>
-      </c>
-      <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/queens-goodbye/1858554528</v>
-      </c>
-      <c r="D98" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E98" t="str">
-        <v/>
-      </c>
-      <c r="F98" t="str">
-        <v>Mārara</v>
-      </c>
-      <c r="G98" t="str">
-        <v>3:46</v>
-      </c>
-      <c r="H98" t="str">
-        <v>15 15</v>
-      </c>
-      <c r="I98" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
-      </c>
-      <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/queens-goodbye/1858554036</v>
-      </c>
-      <c r="L98" t="str">
-        <v>Queen's Goodbye - 15 15</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v>Bring Me Back To Life</v>
-      </c>
-      <c r="B99" t="str">
-        <v/>
-      </c>
-      <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/bring-me-back-to-life/1851634795</v>
-      </c>
-      <c r="D99" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E99" t="str">
-        <v/>
-      </c>
-      <c r="F99" t="str">
-        <v>Melancholia - EP</v>
-      </c>
-      <c r="G99" t="str">
-        <v>3:24</v>
-      </c>
-      <c r="H99" t="str">
-        <v>JELISA</v>
-      </c>
-      <c r="I99" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/jelisa/1588318671</v>
-      </c>
-      <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/bring-me-back-to-life/1851634783</v>
-      </c>
-      <c r="L99" t="str">
-        <v>Bring Me Back To Life - JELISA</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <v>I Don't Care</v>
-      </c>
-      <c r="B100" t="str">
-        <v/>
-      </c>
-      <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/i-dont-care/1868429644</v>
-      </c>
-      <c r="D100" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E100" t="str">
-        <v/>
-      </c>
-      <c r="F100" t="str">
-        <v>I Don't Care - Single</v>
-      </c>
-      <c r="G100" t="str">
-        <v>3:49</v>
-      </c>
-      <c r="H100" t="str">
-        <v>Buffalo Traffic Jam</v>
-      </c>
-      <c r="I100" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
-      </c>
-      <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/i-dont-care/1868429639</v>
-      </c>
-      <c r="L100" t="str">
-        <v>I Don't Care - Buffalo Traffic Jam</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>Elastico (feat. KATE LINN)</v>
-      </c>
-      <c r="B101" t="str">
-        <v/>
-      </c>
-      <c r="C101" t="str">
-        <v>https://music.apple.com/us/song/elastico-feat-kate-linn/1862157500</v>
-      </c>
-      <c r="D101" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E101" t="str">
-        <v/>
-      </c>
-      <c r="F101" t="str">
-        <v>Elastico (feat. KATE LINN) - Single</v>
-      </c>
-      <c r="G101" t="str">
-        <v>3:20</v>
-      </c>
-      <c r="H101" t="str">
-        <v>Fantomel</v>
-      </c>
-      <c r="I101" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J101" t="str">
-        <v>https://music.apple.com/us/artist/fantomel/1736085960</v>
-      </c>
-      <c r="K101" t="str">
-        <v>https://music.apple.com/us/album/elastico-feat-kate-linn/1862157496</v>
-      </c>
-      <c r="L101" t="str">
-        <v>Elastico (feat. KATE LINN) - Fantomel</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Black &amp; Gold</v>
-      </c>
-      <c r="B102" t="str">
-        <v/>
-      </c>
-      <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/black-gold/1853914794</v>
-      </c>
-      <c r="D102" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E102" t="str">
-        <v/>
-      </c>
-      <c r="F102" t="str">
-        <v>Black &amp; Gold - Single</v>
-      </c>
-      <c r="G102" t="str">
-        <v>3:12</v>
-      </c>
-      <c r="H102" t="str">
-        <v>Claptone</v>
-      </c>
-      <c r="I102" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/claptone/470488523</v>
-      </c>
-      <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/black-gold/1853914793</v>
-      </c>
-      <c r="L102" t="str">
-        <v>Black &amp; Gold - Claptone</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>Close Your Eyes</v>
-      </c>
-      <c r="B103" t="str">
-        <v/>
-      </c>
-      <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/close-your-eyes/1860632907</v>
-      </c>
-      <c r="D103" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E103" t="str">
-        <v/>
-      </c>
-      <c r="F103" t="str">
-        <v>Close Your Eyes - Single</v>
-      </c>
-      <c r="G103" t="str">
-        <v>3:33</v>
-      </c>
-      <c r="H103" t="str">
-        <v>Adam Beyer</v>
-      </c>
-      <c r="I103" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/adam-beyer/101672291</v>
-      </c>
-      <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/close-your-eyes/1860632569</v>
-      </c>
-      <c r="L103" t="str">
-        <v>Close Your Eyes - Adam Beyer</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>Movement</v>
-      </c>
-      <c r="B104" t="str">
-        <v/>
-      </c>
-      <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/movement/1867063797</v>
-      </c>
-      <c r="D104" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E104" t="str">
-        <v/>
-      </c>
-      <c r="F104" t="str">
-        <v>Movement - Single</v>
-      </c>
-      <c r="G104" t="str">
-        <v>3:07</v>
-      </c>
-      <c r="H104" t="str">
-        <v>Crankdat</v>
-      </c>
-      <c r="I104" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/crankdat/1073027547</v>
-      </c>
-      <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/movement/1867063796</v>
-      </c>
-      <c r="L104" t="str">
-        <v>Movement - Crankdat</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>Ayi Giri</v>
-      </c>
-      <c r="B105" t="str">
-        <v/>
-      </c>
-      <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/ayi-giri/1867306651</v>
-      </c>
-      <c r="D105" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E105" t="str">
-        <v/>
-      </c>
-      <c r="F105" t="str">
-        <v>Ayi Giri / Dopamine Machine - Single</v>
-      </c>
-      <c r="G105" t="str">
-        <v>3:06</v>
-      </c>
-      <c r="H105" t="str">
-        <v>Lilly Palmer</v>
-      </c>
-      <c r="I105" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/lilly-palmer/340777023</v>
-      </c>
-      <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/ayi-giri/1867306650</v>
-      </c>
-      <c r="L105" t="str">
-        <v>Ayi Giri - Lilly Palmer</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>It's A Sin</v>
-      </c>
-      <c r="B106" t="str">
-        <v/>
-      </c>
-      <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/its-a-sin/1861930282</v>
-      </c>
-      <c r="D106" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E106" t="str">
-        <v/>
-      </c>
-      <c r="F106" t="str">
-        <v>It's A Sin - Single</v>
-      </c>
-      <c r="G106" t="str">
-        <v>4:40</v>
-      </c>
-      <c r="H106" t="str">
-        <v>Ghost</v>
-      </c>
-      <c r="I106" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/ghost/600730426</v>
-      </c>
-      <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/its-a-sin/1861930280</v>
-      </c>
-      <c r="L106" t="str">
-        <v>It's A Sin - Ghost</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Krushers Of The World</v>
-      </c>
-      <c r="B107" t="str">
-        <v/>
-      </c>
-      <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/krushers-of-the-world/1837718526</v>
-      </c>
-      <c r="D107" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E107" t="str">
-        <v/>
-      </c>
-      <c r="F107" t="str">
-        <v>Krushers Of The World</v>
-      </c>
-      <c r="G107" t="str">
-        <v>4:20</v>
-      </c>
-      <c r="H107" t="str">
-        <v>Kreator</v>
-      </c>
-      <c r="I107" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/kreator/3258504</v>
-      </c>
-      <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/krushers-of-the-world/1837718517</v>
-      </c>
-      <c r="L107" t="str">
-        <v>Krushers Of The World - Kreator</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v>Thoroughbreds</v>
-      </c>
-      <c r="B108" t="str">
-        <v/>
-      </c>
-      <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/thoroughbreds/1863532917</v>
-      </c>
-      <c r="D108" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E108" t="str">
-        <v/>
-      </c>
-      <c r="F108" t="str">
-        <v>Peace In Place</v>
-      </c>
-      <c r="G108" t="str">
-        <v>3:24</v>
-      </c>
-      <c r="H108" t="str">
-        <v>Poison the Well</v>
-      </c>
-      <c r="I108" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
-      </c>
-      <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/thoroughbreds/1863532634</v>
-      </c>
-      <c r="L108" t="str">
-        <v>Thoroughbreds - Poison the Well</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="str">
-        <v>Adversary</v>
-      </c>
-      <c r="B109" t="str">
-        <v/>
-      </c>
-      <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/adversary/1861901940</v>
-      </c>
-      <c r="D109" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E109" t="str">
-        <v/>
-      </c>
-      <c r="F109" t="str">
-        <v>Descent</v>
-      </c>
-      <c r="G109" t="str">
-        <v>3:17</v>
-      </c>
-      <c r="H109" t="str">
-        <v>Immolation</v>
-      </c>
-      <c r="I109" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/immolation/64874488</v>
-      </c>
-      <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/adversary/1861901597</v>
-      </c>
-      <c r="L109" t="str">
-        <v>Adversary - Immolation</v>
+        <v>Bomb To A Knife Fight - The Barbarians of California</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L109"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L89"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
@@ -682,7 +682,7 @@
         <v>scared - Single</v>
       </c>
       <c r="G8" t="str">
-        <v>4:03</v>
+        <v>3:46</v>
       </c>
       <c r="H8" t="str">
         <v>Fred again..</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
@@ -2222,13 +2222,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown)</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown/1870678482</v>
+        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-23</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>SO BE IT</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G49" t="str">
         <v>5:47</v>
@@ -2252,10 +2252,10 @@
         <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown/1870678481</v>
+        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
       </c>
       <c r="L49" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) - Elevation Worship</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="50">

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L89"/>
+  <dimension ref="A1:L91"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2070,13 +2070,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>UP TO MY NECK IN U</v>
+        <v>Ojalá</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
+        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-23</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>UP TO MY NECK IN U - Single</v>
+        <v>Ojalá - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>2:17</v>
+        <v>4:11</v>
       </c>
       <c r="H45" t="str">
-        <v>Ledbyher</v>
+        <v>Lunay</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/lunay/938127685</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
+        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
       </c>
       <c r="L45" t="str">
-        <v>UP TO MY NECK IN U - Ledbyher</v>
+        <v>Ojalá - Lunay</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Wallflower</v>
+        <v>UP TO MY NECK IN U</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
+        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-23</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Wallflower - Single</v>
+        <v>UP TO MY NECK IN U - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>3:25</v>
+        <v>2:17</v>
       </c>
       <c r="H46" t="str">
-        <v>Sikarus</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
+        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
       </c>
       <c r="L46" t="str">
-        <v>Wallflower - Sikarus</v>
+        <v>UP TO MY NECK IN U - Ledbyher</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>You Phase</v>
+        <v>Wallflower</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
+        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-23</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>You Phase - Single</v>
+        <v>Wallflower - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>2:51</v>
+        <v>3:25</v>
       </c>
       <c r="H47" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Sikarus</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
+        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
+        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
       </c>
       <c r="L47" t="str">
-        <v>You Phase - Mitchell Tenpenny</v>
+        <v>Wallflower - Sikarus</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Miss Independent</v>
+        <v>You Phase</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
+        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-23</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Miss Independent - Single</v>
+        <v>You Phase - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>2:40</v>
+        <v>2:51</v>
       </c>
       <c r="H48" t="str">
-        <v>1Ski OG</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
+        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
       </c>
       <c r="L48" t="str">
-        <v>Miss Independent - 1Ski OG</v>
+        <v>You Phase - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
+        <v>Miss Independent</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
+        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-23</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>Miss Independent - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>5:47</v>
+        <v>2:40</v>
       </c>
       <c r="H49" t="str">
-        <v>Elevation Worship</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
       </c>
       <c r="L49" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
+        <v>Miss Independent - 1Ski OG</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>go again</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/go-again/1868987466</v>
+        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-23</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>go again - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G50" t="str">
-        <v>2:07</v>
+        <v>5:47</v>
       </c>
       <c r="H50" t="str">
-        <v>NateTaylorr</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/go-again/1868987193</v>
+        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
       </c>
       <c r="L50" t="str">
-        <v>go again - NateTaylorr</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Autopilot</v>
+        <v>go again</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
+        <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-23</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Autopilot</v>
+        <v>go again - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>2:46</v>
+        <v>2:07</v>
       </c>
       <c r="H51" t="str">
-        <v>ALEXSUCKS</v>
+        <v>NateTaylorr</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
+        <v>https://music.apple.com/us/album/go-again/1868987193</v>
       </c>
       <c r="L51" t="str">
-        <v>Autopilot - ALEXSUCKS</v>
+        <v>go again - NateTaylorr</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates)</v>
+        <v>Autopilot</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
+        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-23</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Portrait of My Heart - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G52" t="str">
-        <v>3:04</v>
+        <v>2:46</v>
       </c>
       <c r="H52" t="str">
-        <v>SPELLLING</v>
+        <v>ALEXSUCKS</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
+        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
       </c>
       <c r="L52" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
+        <v>Autopilot - ALEXSUCKS</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>In Violet</v>
+        <v>Portrait of My Heart (feat. Brendan Yates)</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
+        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-23</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Death in the Business of Whaling</v>
+        <v>Portrait of My Heart - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>4:09</v>
+        <v>3:04</v>
       </c>
       <c r="H53" t="str">
-        <v>Searows</v>
+        <v>SPELLLING</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/searows/1607240507</v>
+        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
+        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
       </c>
       <c r="L53" t="str">
-        <v>In Violet - Searows</v>
+        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Baby Run</v>
+        <v>In Violet</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
+        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-23</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Baby Run - Single</v>
+        <v>Death in the Business of Whaling</v>
       </c>
       <c r="G54" t="str">
-        <v>4:47</v>
+        <v>4:09</v>
       </c>
       <c r="H54" t="str">
-        <v>Jimi Jules</v>
+        <v>Searows</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
+        <v>https://music.apple.com/us/artist/searows/1607240507</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
+        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
       </c>
       <c r="L54" t="str">
-        <v>Baby Run - Jimi Jules</v>
+        <v>In Violet - Searows</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>What If We Don't</v>
+        <v>Baby Run</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
+        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-23</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>What If We Don't - Single</v>
+        <v>Baby Run - Single</v>
       </c>
       <c r="G55" t="str">
-        <v>3:06</v>
+        <v>4:47</v>
       </c>
       <c r="H55" t="str">
-        <v>Ashley McBryde</v>
+        <v>Jimi Jules</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
+        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
       </c>
       <c r="L55" t="str">
-        <v>What If We Don't - Ashley McBryde</v>
+        <v>Baby Run - Jimi Jules</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Hagamos Que</v>
+        <v>What If We Don't</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
+        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-23</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Hagamos Que - Single</v>
+        <v>What If We Don't - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>2:58</v>
+        <v>3:06</v>
       </c>
       <c r="H56" t="str">
-        <v>Juanes</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
+        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
       </c>
       <c r="L56" t="str">
-        <v>Hagamos Que - Juanes</v>
+        <v>What If We Don't - Ashley McBryde</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>World Change Me</v>
+        <v>Hagamos Que</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
+        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-23</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>World Change Me - Single</v>
+        <v>Hagamos Que - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>3:03</v>
+        <v>2:58</v>
       </c>
       <c r="H57" t="str">
-        <v>Max McNown</v>
+        <v>Juanes</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
+        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
       </c>
       <c r="L57" t="str">
-        <v>World Change Me - Max McNown</v>
+        <v>Hagamos Que - Juanes</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Exclusive</v>
+        <v>World Change Me</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
+        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-23</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Exclusive - EP</v>
+        <v>World Change Me - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:20</v>
+        <v>3:03</v>
       </c>
       <c r="H58" t="str">
-        <v>Hudson Westbrook</v>
+        <v>Max McNown</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
+        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
       </c>
       <c r="L58" t="str">
-        <v>Exclusive - Hudson Westbrook</v>
+        <v>World Change Me - Max McNown</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Say Less</v>
+        <v>Exclusive</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/say-less/1867910122</v>
+        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-23</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Say Less - Single</v>
+        <v>Exclusive - EP</v>
       </c>
       <c r="G59" t="str">
-        <v>2:18</v>
+        <v>3:20</v>
       </c>
       <c r="H59" t="str">
-        <v>JYT</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/say-less/1867910115</v>
+        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
       </c>
       <c r="L59" t="str">
-        <v>Say Less - JYT</v>
+        <v>Exclusive - Hudson Westbrook</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Angels Cry</v>
+        <v>Say Less</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
+        <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-23</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>X's for Eyes (Deluxe)</v>
+        <v>Say Less - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>3:52</v>
+        <v>2:18</v>
       </c>
       <c r="H60" t="str">
-        <v>The Red Jumpsuit Apparatus</v>
+        <v>JYT</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
+        <v>https://music.apple.com/us/album/say-less/1867910115</v>
       </c>
       <c r="L60" t="str">
-        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
+        <v>Say Less - JYT</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Over You</v>
+        <v>Angels Cry</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/over-you/1846189473</v>
+        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-23</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>A Love For Strangers</v>
+        <v>X's for Eyes (Deluxe)</v>
       </c>
       <c r="G61" t="str">
-        <v>4:44</v>
+        <v>3:52</v>
       </c>
       <c r="H61" t="str">
-        <v>Chet Faker</v>
+        <v>The Red Jumpsuit Apparatus</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/over-you/1846189472</v>
+        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
       </c>
       <c r="L61" t="str">
-        <v>Over You - Chet Faker</v>
+        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Chala (My Soul Is on a Loop)</v>
+        <v>Over You</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
+        <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-23</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Chala (My Soul Is on a Loop) - Single</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G62" t="str">
-        <v>2:42</v>
+        <v>4:44</v>
       </c>
       <c r="H62" t="str">
-        <v>Barry Can't Swim</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
+        <v>https://music.apple.com/us/album/over-you/1846189472</v>
       </c>
       <c r="L62" t="str">
-        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
+        <v>Over You - Chet Faker</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>starlight feat. Madeline Follin</v>
+        <v>Chala (My Soul Is on a Loop)</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
+        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-23</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>starlight feat. Madeline Follin - Single</v>
+        <v>Chala (My Soul Is on a Loop) - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>3:06</v>
+        <v>2:42</v>
       </c>
       <c r="H63" t="str">
-        <v>Disco Lines</v>
+        <v>Barry Can't Swim</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
+        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
+        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
       </c>
       <c r="L63" t="str">
-        <v>starlight feat. Madeline Follin - Disco Lines</v>
+        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Locked In (feat. Trippie Redd)</v>
+        <v>starlight feat. Madeline Follin</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
+        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-23</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Locked In (feat. Trippie Redd) - Single</v>
+        <v>starlight feat. Madeline Follin - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>2:48</v>
+        <v>3:06</v>
       </c>
       <c r="H64" t="str">
-        <v>David Guetta</v>
+        <v>Disco Lines</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
+        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
+        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
       </c>
       <c r="L64" t="str">
-        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
+        <v>starlight feat. Madeline Follin - Disco Lines</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Rejoice</v>
+        <v>Locked In (feat. Trippie Redd)</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
+        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-23</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Rejoice - Single</v>
+        <v>Locked In (feat. Trippie Redd) - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>4:20</v>
+        <v>2:48</v>
       </c>
       <c r="H65" t="str">
-        <v>Def Leppard</v>
+        <v>David Guetta</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
+        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
+        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
       </c>
       <c r="L65" t="str">
-        <v>Rejoice - Def Leppard</v>
+        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
+        <v>Rejoice</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
+        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-23</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
+        <v>Rejoice - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>2:58</v>
+        <v>4:20</v>
       </c>
       <c r="H66" t="str">
-        <v>Honey Dijon</v>
+        <v>Def Leppard</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
+        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
       </c>
       <c r="L66" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
+        <v>Rejoice - Def Leppard</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Lucky Day</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
+        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-23</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Speed Kills</v>
+        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>3:13</v>
+        <v>2:58</v>
       </c>
       <c r="H67" t="str">
-        <v>Ally Evenson</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
+        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
       </c>
       <c r="L67" t="str">
-        <v>Lucky Day - Ally Evenson</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Breathe On It</v>
+        <v>Odisea</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
+        <v>https://music.apple.com/us/song/odisea/1866927906</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-23</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Breathe On It - Single</v>
+        <v>Odisea - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>4:00</v>
+        <v>3:56</v>
       </c>
       <c r="H68" t="str">
-        <v>Tauren Wells</v>
+        <v>BASSYY</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
+        <v>https://music.apple.com/us/album/odisea/1866927904</v>
       </c>
       <c r="L68" t="str">
-        <v>Breathe On It - Tauren Wells</v>
+        <v>Odisea - BASSYY</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Easy</v>
+        <v>Lucky Day</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/easy/1863456906</v>
+        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-23</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Easy - Single</v>
+        <v>Speed Kills</v>
       </c>
       <c r="G69" t="str">
-        <v>4:30</v>
+        <v>3:13</v>
       </c>
       <c r="H69" t="str">
-        <v>lydi lynn</v>
+        <v>Ally Evenson</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/easy/1863456903</v>
+        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
       </c>
       <c r="L69" t="str">
-        <v>Easy - lydi lynn</v>
+        <v>Lucky Day - Ally Evenson</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Break Me In</v>
+        <v>Breathe On It</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
+        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-23</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Break Me In - Single</v>
+        <v>Breathe On It - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>2:52</v>
+        <v>4:00</v>
       </c>
       <c r="H70" t="str">
-        <v>Joyce Wrice</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
+        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
       </c>
       <c r="L70" t="str">
-        <v>Break Me In - Joyce Wrice</v>
+        <v>Breathe On It - Tauren Wells</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Long Live Love</v>
+        <v>Easy</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
+        <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-23</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Long Live Love - Single</v>
+        <v>Easy - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>2:36</v>
+        <v>4:30</v>
       </c>
       <c r="H71" t="str">
-        <v>Sugar</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/sugar/530175867</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
+        <v>https://music.apple.com/us/album/easy/1863456903</v>
       </c>
       <c r="L71" t="str">
-        <v>Long Live Love - Sugar</v>
+        <v>Easy - lydi lynn</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Depressed</v>
+        <v>Break Me In</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/depressed/1840400522</v>
+        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-23</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Boycott Heaven</v>
+        <v>Break Me In - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:32</v>
+        <v>2:52</v>
       </c>
       <c r="H72" t="str">
-        <v>The Format</v>
+        <v>Joyce Wrice</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/the-format/3064903</v>
+        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/depressed/1840399886</v>
+        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
       </c>
       <c r="L72" t="str">
-        <v>Depressed - The Format</v>
+        <v>Break Me In - Joyce Wrice</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Empty Hands</v>
+        <v>Long Live Love</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
+        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-23</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Empty Hands</v>
+        <v>Long Live Love - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>3:09</v>
+        <v>2:36</v>
       </c>
       <c r="H73" t="str">
-        <v>Poppy</v>
+        <v>Sugar</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
+        <v>https://music.apple.com/us/artist/sugar/530175867</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
+        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
       </c>
       <c r="L73" t="str">
-        <v>Empty Hands - Poppy</v>
+        <v>Long Live Love - Sugar</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>The Long Surrender</v>
+        <v>Depressed</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
+        <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-23</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>The Long Surrender</v>
+        <v>Boycott Heaven</v>
       </c>
       <c r="G74" t="str">
-        <v>3:45</v>
+        <v>3:32</v>
       </c>
       <c r="H74" t="str">
-        <v>NEEDTOBREATHE</v>
+        <v>The Format</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
+        <v>https://music.apple.com/us/artist/the-format/3064903</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
+        <v>https://music.apple.com/us/album/depressed/1840399886</v>
       </c>
       <c r="L74" t="str">
-        <v>The Long Surrender - NEEDTOBREATHE</v>
+        <v>Depressed - The Format</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Angela</v>
+        <v>Empty Hands</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/angela/1866624257</v>
+        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-23</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Angela - Single</v>
+        <v>Empty Hands</v>
       </c>
       <c r="G75" t="str">
-        <v>3:32</v>
+        <v>3:09</v>
       </c>
       <c r="H75" t="str">
-        <v>Hayden Everett</v>
+        <v>Poppy</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/angela/1866624256</v>
+        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
       </c>
       <c r="L75" t="str">
-        <v>Angela - Hayden Everett</v>
+        <v>Empty Hands - Poppy</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Disappear</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/disappear/1847663553</v>
+        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-23</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Greyhound</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="G76" t="str">
-        <v>3:31</v>
+        <v>3:45</v>
       </c>
       <c r="H76" t="str">
-        <v>Katie Tupper</v>
+        <v>NEEDTOBREATHE</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
+        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/disappear/1847663546</v>
+        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
       </c>
       <c r="L76" t="str">
-        <v>Disappear - Katie Tupper</v>
+        <v>The Long Surrender - NEEDTOBREATHE</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Catapult</v>
+        <v>Angela</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/catapult/1862951335</v>
+        <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-23</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Catapult - Single</v>
+        <v>Angela - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>2:57</v>
+        <v>3:32</v>
       </c>
       <c r="H77" t="str">
-        <v>Cape Francis</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/catapult/1862951333</v>
+        <v>https://music.apple.com/us/album/angela/1866624256</v>
       </c>
       <c r="L77" t="str">
-        <v>Catapult - Cape Francis</v>
+        <v>Angela - Hayden Everett</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Think Twice</v>
+        <v>Disappear</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
+        <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-23</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Think Twice - Single</v>
+        <v>Greyhound</v>
       </c>
       <c r="G78" t="str">
-        <v>2:22</v>
+        <v>3:31</v>
       </c>
       <c r="H78" t="str">
-        <v>Leonie Biney</v>
+        <v>Katie Tupper</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
+        <v>https://music.apple.com/us/album/disappear/1847663546</v>
       </c>
       <c r="L78" t="str">
-        <v>Think Twice - Leonie Biney</v>
+        <v>Disappear - Katie Tupper</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>LOVESONGS</v>
+        <v>Catapult</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
+        <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-23</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>BEAUTIFUL MADNESS</v>
+        <v>Catapult - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:33</v>
+        <v>2:57</v>
       </c>
       <c r="H79" t="str">
-        <v>Agnes</v>
+        <v>Cape Francis</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/agnes/42568985</v>
+        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
+        <v>https://music.apple.com/us/album/catapult/1862951333</v>
       </c>
       <c r="L79" t="str">
-        <v>LOVESONGS - Agnes</v>
+        <v>Catapult - Cape Francis</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Down South</v>
+        <v>Think Twice</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/down-south/1861010793</v>
+        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-23</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Down South - Single</v>
+        <v>Think Twice - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>2:19</v>
+        <v>2:22</v>
       </c>
       <c r="H80" t="str">
-        <v>Trap Dickey</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/down-south/1861010788</v>
+        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
       </c>
       <c r="L80" t="str">
-        <v>Down South - Trap Dickey</v>
+        <v>Think Twice - Leonie Biney</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
+        <v>LOVESONGS</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
+        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-23</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
+        <v>BEAUTIFUL MADNESS</v>
       </c>
       <c r="G81" t="str">
-        <v>2:16</v>
+        <v>3:33</v>
       </c>
       <c r="H81" t="str">
-        <v>SALIMATA</v>
+        <v>Agnes</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/salimata/690253822</v>
+        <v>https://music.apple.com/us/artist/agnes/42568985</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
+        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
       </c>
       <c r="L81" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
+        <v>LOVESONGS - Agnes</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Love Like This</v>
+        <v>Down South</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
+        <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-23</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Love Like This - Single</v>
+        <v>Down South - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>3:30</v>
+        <v>2:19</v>
       </c>
       <c r="H82" t="str">
-        <v>Jacob Banks</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
+        <v>https://music.apple.com/us/album/down-south/1861010788</v>
       </c>
       <c r="L82" t="str">
-        <v>Love Like This - Jacob Banks</v>
+        <v>Down South - Trap Dickey</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Plan Plan</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
+        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-23</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>La Locura</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>3:10</v>
+        <v>2:16</v>
       </c>
       <c r="H83" t="str">
-        <v>Funky</v>
+        <v>SALIMATA</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/funky/80960663</v>
+        <v>https://music.apple.com/us/artist/salimata/690253822</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
+        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
       </c>
       <c r="L83" t="str">
-        <v>Plan Plan - Funky</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>double edged sword</v>
+        <v>Love Like This</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
+        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-23</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>double edged sword - Single</v>
+        <v>Love Like This - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>3:28</v>
+        <v>3:30</v>
       </c>
       <c r="H84" t="str">
-        <v>Hailey Picardi</v>
+        <v>Jacob Banks</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
+        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
       </c>
       <c r="L84" t="str">
-        <v>double edged sword - Hailey Picardi</v>
+        <v>Love Like This - Jacob Banks</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>SOMEWHERE IN BETWEEN</v>
+        <v>Plan Plan</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
+        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-23</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>SOMEWHERE IN BETWEEN - Single</v>
+        <v>La Locura</v>
       </c>
       <c r="G85" t="str">
-        <v>3:27</v>
+        <v>3:10</v>
       </c>
       <c r="H85" t="str">
-        <v>Matt Hansen</v>
+        <v>Funky</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
+        <v>https://music.apple.com/us/artist/funky/80960663</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
+        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
       </c>
       <c r="L85" t="str">
-        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
+        <v>Plan Plan - Funky</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>The Decay</v>
+        <v>double edged sword</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
+        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-23</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>What Remains (Midnight Edition)</v>
+        <v>double edged sword - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:20</v>
+        <v>3:28</v>
       </c>
       <c r="H86" t="str">
-        <v>Pop Evil</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
+        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
       </c>
       <c r="L86" t="str">
-        <v>The Decay - Pop Evil</v>
+        <v>double edged sword - Hailey Picardi</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>3111</v>
+        <v>SOMEWHERE IN BETWEEN</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/3111/1862225387</v>
+        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-23</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Goliath</v>
+        <v>SOMEWHERE IN BETWEEN - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>4:08</v>
+        <v>3:27</v>
       </c>
       <c r="H87" t="str">
-        <v>Exodus</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/3111/1862225385</v>
+        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
       </c>
       <c r="L87" t="str">
-        <v>3111 - Exodus</v>
+        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Touch My Love And Die</v>
+        <v>The Decay</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-23</v>
@@ -3719,68 +3719,144 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Touch My Love And Die - Single</v>
+        <v>What Remains (Midnight Edition)</v>
       </c>
       <c r="G88" t="str">
-        <v>2:57</v>
+        <v>3:20</v>
       </c>
       <c r="H88" t="str">
-        <v>Myrkur</v>
+        <v>Pop Evil</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
       </c>
       <c r="L88" t="str">
-        <v>Touch My Love And Die - Myrkur</v>
+        <v>The Decay - Pop Evil</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
+        <v>3111</v>
+      </c>
+      <c r="B89" t="str">
+        <v/>
+      </c>
+      <c r="C89" t="str">
+        <v>https://music.apple.com/us/song/3111/1862225387</v>
+      </c>
+      <c r="D89" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v>Goliath</v>
+      </c>
+      <c r="G89" t="str">
+        <v>4:08</v>
+      </c>
+      <c r="H89" t="str">
+        <v>Exodus</v>
+      </c>
+      <c r="I89" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J89" t="str">
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+      </c>
+      <c r="K89" t="str">
+        <v>https://music.apple.com/us/album/3111/1862225385</v>
+      </c>
+      <c r="L89" t="str">
+        <v>3111 - Exodus</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>Touch My Love And Die</v>
+      </c>
+      <c r="B90" t="str">
+        <v/>
+      </c>
+      <c r="C90" t="str">
+        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+      </c>
+      <c r="D90" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v>Touch My Love And Die - Single</v>
+      </c>
+      <c r="G90" t="str">
+        <v>2:57</v>
+      </c>
+      <c r="H90" t="str">
+        <v>Myrkur</v>
+      </c>
+      <c r="I90" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J90" t="str">
+        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+      </c>
+      <c r="K90" t="str">
+        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+      </c>
+      <c r="L90" t="str">
+        <v>Touch My Love And Die - Myrkur</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
         <v>Bomb To A Knife Fight</v>
       </c>
-      <c r="B89" t="str">
-        <v/>
-      </c>
-      <c r="C89" t="str">
+      <c r="B91" t="str">
+        <v/>
+      </c>
+      <c r="C91" t="str">
         <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
-      <c r="D89" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E89" t="str">
-        <v/>
-      </c>
-      <c r="F89" t="str">
+      <c r="D91" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
         <v>Bomb To A Knife Fight - Single</v>
       </c>
-      <c r="G89" t="str">
+      <c r="G91" t="str">
         <v>2:41</v>
       </c>
-      <c r="H89" t="str">
+      <c r="H91" t="str">
         <v>The Barbarians of California</v>
       </c>
-      <c r="I89" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J89" t="str">
+      <c r="I91" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J91" t="str">
         <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
       </c>
-      <c r="K89" t="str">
+      <c r="K91" t="str">
         <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
       </c>
-      <c r="L89" t="str">
+      <c r="L91" t="str">
         <v>Bomb To A Knife Fight - The Barbarians of California</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L89"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L91"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L92"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -778,13 +778,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Flo Jackson</v>
+        <v>ATM</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
+        <v>https://music.apple.com/us/song/atm/1871258339</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-23</v>
@@ -793,36 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>Flo Jackson - Single</v>
+        <v>OCTANE</v>
       </c>
       <c r="G11" t="str">
-        <v>2:23</v>
+        <v>3:00</v>
       </c>
       <c r="H11" t="str">
-        <v>Flo Milli</v>
+        <v>Don Toliver</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
+        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
+        <v>https://music.apple.com/us/album/atm/1871258329</v>
       </c>
       <c r="L11" t="str">
-        <v>Flo Jackson - Flo Milli</v>
+        <v>ATM - Don Toliver</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Site Unseen (feat. Waxahatchee)</v>
+        <v>Flo Jackson</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
+        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-23</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>Creature of Habit</v>
+        <v>Flo Jackson - Single</v>
       </c>
       <c r="G12" t="str">
-        <v>2:46</v>
+        <v>2:23</v>
       </c>
       <c r="H12" t="str">
-        <v>Courtney Barnett</v>
+        <v>Flo Milli</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
+        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
       </c>
       <c r="L12" t="str">
-        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
+        <v>Flo Jackson - Flo Milli</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Puppet Parade</v>
+        <v>Site Unseen (feat. Waxahatchee)</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
+        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-23</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Megadeth</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G13" t="str">
-        <v>4:40</v>
+        <v>2:46</v>
       </c>
       <c r="H13" t="str">
-        <v>Megadeth</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/megadeth/488289</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
+        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
       </c>
       <c r="L13" t="str">
-        <v>Puppet Parade - Megadeth</v>
+        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>To Love Somebody</v>
+        <v>Puppet Parade</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
+        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-23</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>Cruel World</v>
+        <v>Megadeth</v>
       </c>
       <c r="G14" t="str">
-        <v>3:57</v>
+        <v>4:40</v>
       </c>
       <c r="H14" t="str">
-        <v>Holly Humberstone</v>
+        <v>Megadeth</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/megadeth/488289</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
+        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
       </c>
       <c r="L14" t="str">
-        <v>To Love Somebody - Holly Humberstone</v>
+        <v>Puppet Parade - Megadeth</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Nothing Is Impossible With You</v>
+        <v>To Love Somebody</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
+        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-23</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Nothing Is Impossible With You - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G15" t="str">
-        <v>4:14</v>
+        <v>3:57</v>
       </c>
       <c r="H15" t="str">
-        <v>Cleo Sol</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
+        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
       </c>
       <c r="L15" t="str">
-        <v>Nothing Is Impossible With You - Cleo Sol</v>
+        <v>To Love Somebody - Holly Humberstone</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>HYPNOTIZE</v>
+        <v>Nothing Is Impossible With You</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
+        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-23</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>THE CORE - 核</v>
+        <v>Nothing Is Impossible With You - Single</v>
       </c>
       <c r="G16" t="str">
-        <v>2:50</v>
+        <v>4:14</v>
       </c>
       <c r="H16" t="str">
-        <v>XG</v>
+        <v>Cleo Sol</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/xg/1609409493</v>
+        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
+        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
       </c>
       <c r="L16" t="str">
-        <v>HYPNOTIZE - XG</v>
+        <v>Nothing Is Impossible With You - Cleo Sol</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Dead End</v>
+        <v>HYPNOTIZE</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
+        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-23</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Ricochet</v>
+        <v>THE CORE - 核</v>
       </c>
       <c r="G17" t="str">
-        <v>4:05</v>
+        <v>2:50</v>
       </c>
       <c r="H17" t="str">
-        <v>Snail Mail</v>
+        <v>XG</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/xg/1609409493</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
+        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
       </c>
       <c r="L17" t="str">
-        <v>Dead End - Snail Mail</v>
+        <v>HYPNOTIZE - XG</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Do I Wanna Know?</v>
+        <v>Dead End</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
+        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-23</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Do I Wanna Know? - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G18" t="str">
-        <v>3:52</v>
+        <v>4:05</v>
       </c>
       <c r="H18" t="str">
-        <v>Dove Cameron</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
+        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
       </c>
       <c r="L18" t="str">
-        <v>Do I Wanna Know? - Dove Cameron</v>
+        <v>Dead End - Snail Mail</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Una y Otra Vez</v>
+        <v>Do I Wanna Know?</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
+        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-23</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>Do I Wanna Know? - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>3:02</v>
+        <v>3:52</v>
       </c>
       <c r="H19" t="str">
-        <v>Kenia Os</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
+        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
       </c>
       <c r="L19" t="str">
-        <v>Una y Otra Vez - Kenia Os</v>
+        <v>Do I Wanna Know? - Dove Cameron</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>BAD</v>
+        <v>Una y Otra Vez</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/bad/1869095326</v>
+        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-23</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>BAD - Single</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G20" t="str">
-        <v>2:15</v>
+        <v>3:02</v>
       </c>
       <c r="H20" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/bad/1869095325</v>
+        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
       </c>
       <c r="L20" t="str">
-        <v>BAD - Chelsea Cutler</v>
+        <v>Una y Otra Vez - Kenia Os</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Losing You</v>
+        <v>BAD</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
+        <v>https://music.apple.com/us/song/bad/1869095326</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-23</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>F.I.G</v>
+        <v>BAD - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>2:22</v>
+        <v>2:15</v>
       </c>
       <c r="H21" t="str">
-        <v>Naomi Scott</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
+        <v>https://music.apple.com/us/album/bad/1869095325</v>
       </c>
       <c r="L21" t="str">
-        <v>Losing You - Naomi Scott</v>
+        <v>BAD - Chelsea Cutler</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Me Voy A La C******a</v>
+        <v>Losing You</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
+        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-23</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Infinito</v>
+        <v>F.I.G</v>
       </c>
       <c r="G22" t="str">
-        <v>2:14</v>
+        <v>2:22</v>
       </c>
       <c r="H22" t="str">
-        <v>Yandel</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/yandel/72929426</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
+        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
       </c>
       <c r="L22" t="str">
-        <v>Me Voy A La C******a - Yandel</v>
+        <v>Losing You - Naomi Scott</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Sexy For Me</v>
+        <v>Me Voy A La C******a</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
+        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-23</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>The Last Dance (Part 1)</v>
+        <v>Infinito</v>
       </c>
       <c r="G23" t="str">
-        <v>2:08</v>
+        <v>2:14</v>
       </c>
       <c r="H23" t="str">
-        <v>Jason Derulo</v>
+        <v>Yandel</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
+        <v>https://music.apple.com/us/artist/yandel/72929426</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
+        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
       </c>
       <c r="L23" t="str">
-        <v>Sexy For Me - Jason Derulo</v>
+        <v>Me Voy A La C******a - Yandel</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Turbulence</v>
+        <v>Sexy For Me</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
+        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-23</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>REAL, Vol. 1 - EP</v>
+        <v>The Last Dance (Part 1)</v>
       </c>
       <c r="G24" t="str">
-        <v>2:25</v>
+        <v>2:08</v>
       </c>
       <c r="H24" t="str">
-        <v>Wizkid</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
+        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
+        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
       </c>
       <c r="L24" t="str">
-        <v>Turbulence - Wizkid</v>
+        <v>Sexy For Me - Jason Derulo</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>I’m Good (From The Movie “GOAT”)</v>
+        <v>Turbulence</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
+        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-23</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>REAL, Vol. 1 - EP</v>
       </c>
       <c r="G25" t="str">
-        <v>2:59</v>
+        <v>2:25</v>
       </c>
       <c r="H25" t="str">
-        <v>Jelly Roll</v>
+        <v>Wizkid</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
       </c>
       <c r="L25" t="str">
-        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
+        <v>Turbulence - Wizkid</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
+        <v>I’m Good (From The Movie “GOAT”)</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
+        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-23</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G26" t="str">
-        <v>3:47</v>
+        <v>2:59</v>
       </c>
       <c r="H26" t="str">
-        <v>Dolly Parton</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
+        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L26" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
+        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ESCONDIDAS</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
+        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-23</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>SILENCIO HABLA</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>2:53</v>
+        <v>3:47</v>
       </c>
       <c r="H27" t="str">
-        <v>Oscar Ortiz</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
+        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
+        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
       </c>
       <c r="L27" t="str">
-        <v>ESCONDIDAS - Oscar Ortiz</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Alabama Beauty Queen</v>
+        <v>ESCONDIDAS</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
+        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-23</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Act I</v>
+        <v>SILENCIO HABLA</v>
       </c>
       <c r="G28" t="str">
-        <v>3:43</v>
+        <v>2:53</v>
       </c>
       <c r="H28" t="str">
-        <v>Kashus Culpepper</v>
+        <v>Oscar Ortiz</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
+        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
+        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
       </c>
       <c r="L28" t="str">
-        <v>Alabama Beauty Queen - Kashus Culpepper</v>
+        <v>ESCONDIDAS - Oscar Ortiz</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Imposter</v>
+        <v>Alabama Beauty Queen</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/imposter/1842408050</v>
+        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-23</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>How Did I Get Here?</v>
+        <v>Act I</v>
       </c>
       <c r="G29" t="str">
-        <v>2:38</v>
+        <v>3:43</v>
       </c>
       <c r="H29" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Kashus Culpepper</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/imposter/1842408037</v>
+        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
       </c>
       <c r="L29" t="str">
-        <v>Imposter - Louis Tomlinson</v>
+        <v>Alabama Beauty Queen - Kashus Culpepper</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Puddles (Zero 7 Remix)</v>
+        <v>Imposter</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
+        <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-23</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Puddles (Zero 7 Remix) - Single</v>
+        <v>How Did I Get Here?</v>
       </c>
       <c r="G30" t="str">
-        <v>6:01</v>
+        <v>2:38</v>
       </c>
       <c r="H30" t="str">
-        <v>Not for Radio</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
+        <v>https://music.apple.com/us/album/imposter/1842408037</v>
       </c>
       <c r="L30" t="str">
-        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
+        <v>Imposter - Louis Tomlinson</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Little Miss (Misdemeanor)</v>
+        <v>Puddles (Zero 7 Remix)</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
+        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-23</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Little Miss (Misdemeanor) - Single</v>
+        <v>Puddles (Zero 7 Remix) - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>2:24</v>
+        <v>6:01</v>
       </c>
       <c r="H31" t="str">
-        <v>GIRLSET</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
+        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
       </c>
       <c r="L31" t="str">
-        <v>Little Miss (Misdemeanor) - GIRLSET</v>
+        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>I Could Get Used To This</v>
+        <v>Little Miss (Misdemeanor)</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
+        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-23</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>I Could Get Used To This - Single</v>
+        <v>Little Miss (Misdemeanor) - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>3:41</v>
+        <v>2:24</v>
       </c>
       <c r="H32" t="str">
-        <v>Jessie Ware</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
+        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
       </c>
       <c r="L32" t="str">
-        <v>I Could Get Used To This - Jessie Ware</v>
+        <v>Little Miss (Misdemeanor) - GIRLSET</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>LA VILLA</v>
+        <v>I Could Get Used To This</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
+        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-23</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>HOPI SENDÉ</v>
+        <v>I Could Get Used To This - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>3:12</v>
+        <v>3:41</v>
       </c>
       <c r="H33" t="str">
-        <v>Ryan Castro</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
+        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
       </c>
       <c r="L33" t="str">
-        <v>LA VILLA - Ryan Castro</v>
+        <v>I Could Get Used To This - Jessie Ware</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
+        <v>LA VILLA</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
+        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-23</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>HOPI SENDÉ</v>
       </c>
       <c r="G34" t="str">
-        <v>3:27</v>
+        <v>3:12</v>
       </c>
       <c r="H34" t="str">
-        <v>Denzel Curry</v>
+        <v>Ryan Castro</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
+        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
       </c>
       <c r="L34" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
+        <v>LA VILLA - Ryan Castro</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Thick One</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
+        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-23</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Part 3</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G35" t="str">
-        <v>2:49</v>
+        <v>3:27</v>
       </c>
       <c r="H35" t="str">
-        <v>42 Dugg</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
+        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
       </c>
       <c r="L35" t="str">
-        <v>Thick One - 42 Dugg</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>How Much Did You Get For Your Soul</v>
+        <v>Thick One</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
+        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-23</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>World's Gone Wrong</v>
+        <v>Part 3</v>
       </c>
       <c r="G36" t="str">
-        <v>3:59</v>
+        <v>2:49</v>
       </c>
       <c r="H36" t="str">
-        <v>Lucinda Williams</v>
+        <v>42 Dugg</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
+        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
+        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
       </c>
       <c r="L36" t="str">
-        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
+        <v>Thick One - 42 Dugg</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>THUM</v>
+        <v>How Much Did You Get For Your Soul</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/thum/1863009362</v>
+        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-23</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>THUM - Single</v>
+        <v>World's Gone Wrong</v>
       </c>
       <c r="G37" t="str">
-        <v>2:11</v>
+        <v>3:59</v>
       </c>
       <c r="H37" t="str">
-        <v>Violet Grohl</v>
+        <v>Lucinda Williams</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/thum/1863009357</v>
+        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
       </c>
       <c r="L37" t="str">
-        <v>THUM - Violet Grohl</v>
+        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>(I'm a) Rock "N" Roller</v>
+        <v>THUM</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
+        <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-23</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>The Great Satan</v>
+        <v>THUM - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>3:32</v>
+        <v>2:11</v>
       </c>
       <c r="H38" t="str">
-        <v>Rob Zombie</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
+        <v>https://music.apple.com/us/album/thum/1863009357</v>
       </c>
       <c r="L38" t="str">
-        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
+        <v>THUM - Violet Grohl</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Excuses For Love</v>
+        <v>(I'm a) Rock "N" Roller</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
+        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-23</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Hyperlove</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G39" t="str">
-        <v>3:04</v>
+        <v>3:32</v>
       </c>
       <c r="H39" t="str">
-        <v>MIKA</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/mika/184932871</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
+        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
       </c>
       <c r="L39" t="str">
-        <v>Excuses For Love - MIKA</v>
+        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>3 Tears</v>
+        <v>Excuses For Love</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
+        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-23</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3 Tears - Single</v>
+        <v>Hyperlove</v>
       </c>
       <c r="G40" t="str">
-        <v>2:50</v>
+        <v>3:04</v>
       </c>
       <c r="H40" t="str">
-        <v>Mergui</v>
+        <v>MIKA</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
+        <v>https://music.apple.com/us/artist/mika/184932871</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
+        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
       </c>
       <c r="L40" t="str">
-        <v>3 Tears - Mergui</v>
+        <v>Excuses For Love - MIKA</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Church Girl</v>
+        <v>3 Tears</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
+        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-23</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Church Girl - Single</v>
+        <v>3 Tears - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>3:19</v>
+        <v>2:50</v>
       </c>
       <c r="H41" t="str">
-        <v>Carly Pearce</v>
+        <v>Mergui</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
+        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
       </c>
       <c r="L41" t="str">
-        <v>Church Girl - Carly Pearce</v>
+        <v>3 Tears - Mergui</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Funeral</v>
+        <v>Church Girl</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/funeral/1867616928</v>
+        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-23</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>The Weight of the Woods</v>
+        <v>Church Girl - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>4:03</v>
+        <v>3:19</v>
       </c>
       <c r="H42" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/funeral/1867616617</v>
+        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
       </c>
       <c r="L42" t="str">
-        <v>Funeral - Dermot Kennedy</v>
+        <v>Church Girl - Carly Pearce</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Say Yes</v>
+        <v>Funeral</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
+        <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-23</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Say Yes - Single</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G43" t="str">
-        <v>2:50</v>
+        <v>4:03</v>
       </c>
       <c r="H43" t="str">
-        <v>Marques Anthony</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
+        <v>https://music.apple.com/us/album/funeral/1867616617</v>
       </c>
       <c r="L43" t="str">
-        <v>Say Yes - Marques Anthony</v>
+        <v>Funeral - Dermot Kennedy</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>LOVE ME (feat. Stevie Wonder)</v>
+        <v>Say Yes</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
+        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-23</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>CAMPILATION</v>
+        <v>Say Yes - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>3:10</v>
+        <v>2:50</v>
       </c>
       <c r="H44" t="str">
-        <v>Camper</v>
+        <v>Marques Anthony</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/camper/1514886616</v>
+        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
+        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
       </c>
       <c r="L44" t="str">
-        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
+        <v>Say Yes - Marques Anthony</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Ojalá</v>
+        <v>LOVE ME (feat. Stevie Wonder)</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
+        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-23</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Ojalá - Single</v>
+        <v>CAMPILATION</v>
       </c>
       <c r="G45" t="str">
-        <v>4:11</v>
+        <v>3:10</v>
       </c>
       <c r="H45" t="str">
-        <v>Lunay</v>
+        <v>Camper</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/lunay/938127685</v>
+        <v>https://music.apple.com/us/artist/camper/1514886616</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
+        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
       </c>
       <c r="L45" t="str">
-        <v>Ojalá - Lunay</v>
+        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>UP TO MY NECK IN U</v>
+        <v>Ojalá</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
+        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-23</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>UP TO MY NECK IN U - Single</v>
+        <v>Ojalá - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>2:17</v>
+        <v>4:11</v>
       </c>
       <c r="H46" t="str">
-        <v>Ledbyher</v>
+        <v>Lunay</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/lunay/938127685</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
+        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
       </c>
       <c r="L46" t="str">
-        <v>UP TO MY NECK IN U - Ledbyher</v>
+        <v>Ojalá - Lunay</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Wallflower</v>
+        <v>UP TO MY NECK IN U</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
+        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-23</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Wallflower - Single</v>
+        <v>UP TO MY NECK IN U - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>3:25</v>
+        <v>2:17</v>
       </c>
       <c r="H47" t="str">
-        <v>Sikarus</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
+        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
       </c>
       <c r="L47" t="str">
-        <v>Wallflower - Sikarus</v>
+        <v>UP TO MY NECK IN U - Ledbyher</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>You Phase</v>
+        <v>Wallflower</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
+        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-23</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>You Phase - Single</v>
+        <v>Wallflower - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>2:51</v>
+        <v>3:25</v>
       </c>
       <c r="H48" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Sikarus</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
+        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
+        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
       </c>
       <c r="L48" t="str">
-        <v>You Phase - Mitchell Tenpenny</v>
+        <v>Wallflower - Sikarus</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Miss Independent</v>
+        <v>You Phase</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
+        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-23</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Miss Independent - Single</v>
+        <v>You Phase - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>2:40</v>
+        <v>2:51</v>
       </c>
       <c r="H49" t="str">
-        <v>1Ski OG</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
+        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
       </c>
       <c r="L49" t="str">
-        <v>Miss Independent - 1Ski OG</v>
+        <v>You Phase - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
+        <v>Miss Independent</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
+        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-23</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>Miss Independent - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>5:47</v>
+        <v>2:40</v>
       </c>
       <c r="H50" t="str">
-        <v>Elevation Worship</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
       </c>
       <c r="L50" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
+        <v>Miss Independent - 1Ski OG</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>go again</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/go-again/1868987466</v>
+        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-23</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>go again - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G51" t="str">
-        <v>2:07</v>
+        <v>5:47</v>
       </c>
       <c r="H51" t="str">
-        <v>NateTaylorr</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/go-again/1868987193</v>
+        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
       </c>
       <c r="L51" t="str">
-        <v>go again - NateTaylorr</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Autopilot</v>
+        <v>go again</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
+        <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-23</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Autopilot</v>
+        <v>go again - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>2:46</v>
+        <v>2:07</v>
       </c>
       <c r="H52" t="str">
-        <v>ALEXSUCKS</v>
+        <v>NateTaylorr</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
+        <v>https://music.apple.com/us/album/go-again/1868987193</v>
       </c>
       <c r="L52" t="str">
-        <v>Autopilot - ALEXSUCKS</v>
+        <v>go again - NateTaylorr</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates)</v>
+        <v>Autopilot</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
+        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-23</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Portrait of My Heart - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G53" t="str">
-        <v>3:04</v>
+        <v>2:46</v>
       </c>
       <c r="H53" t="str">
-        <v>SPELLLING</v>
+        <v>ALEXSUCKS</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
+        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
       </c>
       <c r="L53" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
+        <v>Autopilot - ALEXSUCKS</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>In Violet</v>
+        <v>Portrait of My Heart (feat. Brendan Yates)</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
+        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-23</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Death in the Business of Whaling</v>
+        <v>Portrait of My Heart - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>4:09</v>
+        <v>3:04</v>
       </c>
       <c r="H54" t="str">
-        <v>Searows</v>
+        <v>SPELLLING</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/searows/1607240507</v>
+        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
+        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
       </c>
       <c r="L54" t="str">
-        <v>In Violet - Searows</v>
+        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Baby Run</v>
+        <v>In Violet</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
+        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-23</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Baby Run - Single</v>
+        <v>Death in the Business of Whaling</v>
       </c>
       <c r="G55" t="str">
-        <v>4:47</v>
+        <v>4:09</v>
       </c>
       <c r="H55" t="str">
-        <v>Jimi Jules</v>
+        <v>Searows</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
+        <v>https://music.apple.com/us/artist/searows/1607240507</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
+        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
       </c>
       <c r="L55" t="str">
-        <v>Baby Run - Jimi Jules</v>
+        <v>In Violet - Searows</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>What If We Don't</v>
+        <v>Baby Run</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
+        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-23</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>What If We Don't - Single</v>
+        <v>Baby Run - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>3:06</v>
+        <v>4:47</v>
       </c>
       <c r="H56" t="str">
-        <v>Ashley McBryde</v>
+        <v>Jimi Jules</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
+        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
       </c>
       <c r="L56" t="str">
-        <v>What If We Don't - Ashley McBryde</v>
+        <v>Baby Run - Jimi Jules</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Hagamos Que</v>
+        <v>What If We Don't</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
+        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-23</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Hagamos Que - Single</v>
+        <v>What If We Don't - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>2:58</v>
+        <v>3:06</v>
       </c>
       <c r="H57" t="str">
-        <v>Juanes</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
+        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
       </c>
       <c r="L57" t="str">
-        <v>Hagamos Que - Juanes</v>
+        <v>What If We Don't - Ashley McBryde</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>World Change Me</v>
+        <v>Hagamos Que</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
+        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-23</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>World Change Me - Single</v>
+        <v>Hagamos Que - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:03</v>
+        <v>2:58</v>
       </c>
       <c r="H58" t="str">
-        <v>Max McNown</v>
+        <v>Juanes</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
+        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
       </c>
       <c r="L58" t="str">
-        <v>World Change Me - Max McNown</v>
+        <v>Hagamos Que - Juanes</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Exclusive</v>
+        <v>World Change Me</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
+        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-23</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Exclusive - EP</v>
+        <v>World Change Me - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>3:20</v>
+        <v>3:03</v>
       </c>
       <c r="H59" t="str">
-        <v>Hudson Westbrook</v>
+        <v>Max McNown</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
+        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
       </c>
       <c r="L59" t="str">
-        <v>Exclusive - Hudson Westbrook</v>
+        <v>World Change Me - Max McNown</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Say Less</v>
+        <v>Exclusive</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/say-less/1867910122</v>
+        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-23</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Say Less - Single</v>
+        <v>Exclusive - EP</v>
       </c>
       <c r="G60" t="str">
-        <v>2:18</v>
+        <v>3:20</v>
       </c>
       <c r="H60" t="str">
-        <v>JYT</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/say-less/1867910115</v>
+        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
       </c>
       <c r="L60" t="str">
-        <v>Say Less - JYT</v>
+        <v>Exclusive - Hudson Westbrook</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Angels Cry</v>
+        <v>Say Less</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
+        <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-23</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>X's for Eyes (Deluxe)</v>
+        <v>Say Less - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>3:52</v>
+        <v>2:18</v>
       </c>
       <c r="H61" t="str">
-        <v>The Red Jumpsuit Apparatus</v>
+        <v>JYT</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
+        <v>https://music.apple.com/us/album/say-less/1867910115</v>
       </c>
       <c r="L61" t="str">
-        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
+        <v>Say Less - JYT</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Over You</v>
+        <v>Angels Cry</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/over-you/1846189473</v>
+        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-23</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>A Love For Strangers</v>
+        <v>X's for Eyes (Deluxe)</v>
       </c>
       <c r="G62" t="str">
-        <v>4:44</v>
+        <v>3:52</v>
       </c>
       <c r="H62" t="str">
-        <v>Chet Faker</v>
+        <v>The Red Jumpsuit Apparatus</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/over-you/1846189472</v>
+        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
       </c>
       <c r="L62" t="str">
-        <v>Over You - Chet Faker</v>
+        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Chala (My Soul Is on a Loop)</v>
+        <v>Over You</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
+        <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-23</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Chala (My Soul Is on a Loop) - Single</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G63" t="str">
-        <v>2:42</v>
+        <v>4:44</v>
       </c>
       <c r="H63" t="str">
-        <v>Barry Can't Swim</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
+        <v>https://music.apple.com/us/album/over-you/1846189472</v>
       </c>
       <c r="L63" t="str">
-        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
+        <v>Over You - Chet Faker</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>starlight feat. Madeline Follin</v>
+        <v>Chala (My Soul Is on a Loop)</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
+        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-23</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>starlight feat. Madeline Follin - Single</v>
+        <v>Chala (My Soul Is on a Loop) - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>3:06</v>
+        <v>2:42</v>
       </c>
       <c r="H64" t="str">
-        <v>Disco Lines</v>
+        <v>Barry Can't Swim</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
+        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
+        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
       </c>
       <c r="L64" t="str">
-        <v>starlight feat. Madeline Follin - Disco Lines</v>
+        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Locked In (feat. Trippie Redd)</v>
+        <v>starlight feat. Madeline Follin</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
+        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-23</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Locked In (feat. Trippie Redd) - Single</v>
+        <v>starlight feat. Madeline Follin - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>2:48</v>
+        <v>3:06</v>
       </c>
       <c r="H65" t="str">
-        <v>David Guetta</v>
+        <v>Disco Lines</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
+        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
+        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
       </c>
       <c r="L65" t="str">
-        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
+        <v>starlight feat. Madeline Follin - Disco Lines</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Rejoice</v>
+        <v>Locked In (feat. Trippie Redd)</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
+        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-23</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Rejoice - Single</v>
+        <v>Locked In (feat. Trippie Redd) - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>4:20</v>
+        <v>2:48</v>
       </c>
       <c r="H66" t="str">
-        <v>Def Leppard</v>
+        <v>David Guetta</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
+        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
+        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
       </c>
       <c r="L66" t="str">
-        <v>Rejoice - Def Leppard</v>
+        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
+        <v>Rejoice</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
+        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-23</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
+        <v>Rejoice - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>2:58</v>
+        <v>4:20</v>
       </c>
       <c r="H67" t="str">
-        <v>Honey Dijon</v>
+        <v>Def Leppard</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
+        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
       </c>
       <c r="L67" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
+        <v>Rejoice - Def Leppard</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Odisea</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/odisea/1866927906</v>
+        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-23</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Odisea - Single</v>
+        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>3:56</v>
+        <v>2:58</v>
       </c>
       <c r="H68" t="str">
-        <v>BASSYY</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/odisea/1866927904</v>
+        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
       </c>
       <c r="L68" t="str">
-        <v>Odisea - BASSYY</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Lucky Day</v>
+        <v>Odisea</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
+        <v>https://music.apple.com/us/song/odisea/1866927906</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-23</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Speed Kills</v>
+        <v>Odisea - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>3:13</v>
+        <v>3:56</v>
       </c>
       <c r="H69" t="str">
-        <v>Ally Evenson</v>
+        <v>BASSYY</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
+        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
+        <v>https://music.apple.com/us/album/odisea/1866927904</v>
       </c>
       <c r="L69" t="str">
-        <v>Lucky Day - Ally Evenson</v>
+        <v>Odisea - BASSYY</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Breathe On It</v>
+        <v>Lucky Day</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
+        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-23</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Breathe On It - Single</v>
+        <v>Speed Kills</v>
       </c>
       <c r="G70" t="str">
-        <v>4:00</v>
+        <v>3:13</v>
       </c>
       <c r="H70" t="str">
-        <v>Tauren Wells</v>
+        <v>Ally Evenson</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
+        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
       </c>
       <c r="L70" t="str">
-        <v>Breathe On It - Tauren Wells</v>
+        <v>Lucky Day - Ally Evenson</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Easy</v>
+        <v>Breathe On It</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/easy/1863456906</v>
+        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-23</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Easy - Single</v>
+        <v>Breathe On It - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>4:30</v>
+        <v>4:00</v>
       </c>
       <c r="H71" t="str">
-        <v>lydi lynn</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/easy/1863456903</v>
+        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
       </c>
       <c r="L71" t="str">
-        <v>Easy - lydi lynn</v>
+        <v>Breathe On It - Tauren Wells</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Break Me In</v>
+        <v>Easy</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
+        <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-23</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Break Me In - Single</v>
+        <v>Easy - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>2:52</v>
+        <v>4:30</v>
       </c>
       <c r="H72" t="str">
-        <v>Joyce Wrice</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
+        <v>https://music.apple.com/us/album/easy/1863456903</v>
       </c>
       <c r="L72" t="str">
-        <v>Break Me In - Joyce Wrice</v>
+        <v>Easy - lydi lynn</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Long Live Love</v>
+        <v>Break Me In</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
+        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-23</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Long Live Love - Single</v>
+        <v>Break Me In - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>2:36</v>
+        <v>2:52</v>
       </c>
       <c r="H73" t="str">
-        <v>Sugar</v>
+        <v>Joyce Wrice</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/sugar/530175867</v>
+        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
+        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
       </c>
       <c r="L73" t="str">
-        <v>Long Live Love - Sugar</v>
+        <v>Break Me In - Joyce Wrice</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Depressed</v>
+        <v>Long Live Love</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/depressed/1840400522</v>
+        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-23</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Boycott Heaven</v>
+        <v>Long Live Love - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>3:32</v>
+        <v>2:36</v>
       </c>
       <c r="H74" t="str">
-        <v>The Format</v>
+        <v>Sugar</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/the-format/3064903</v>
+        <v>https://music.apple.com/us/artist/sugar/530175867</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/depressed/1840399886</v>
+        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
       </c>
       <c r="L74" t="str">
-        <v>Depressed - The Format</v>
+        <v>Long Live Love - Sugar</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Empty Hands</v>
+        <v>Depressed</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
+        <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-23</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Empty Hands</v>
+        <v>Boycott Heaven</v>
       </c>
       <c r="G75" t="str">
-        <v>3:09</v>
+        <v>3:32</v>
       </c>
       <c r="H75" t="str">
-        <v>Poppy</v>
+        <v>The Format</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
+        <v>https://music.apple.com/us/artist/the-format/3064903</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
+        <v>https://music.apple.com/us/album/depressed/1840399886</v>
       </c>
       <c r="L75" t="str">
-        <v>Empty Hands - Poppy</v>
+        <v>Depressed - The Format</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>The Long Surrender</v>
+        <v>Empty Hands</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
+        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-23</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>The Long Surrender</v>
+        <v>Empty Hands</v>
       </c>
       <c r="G76" t="str">
-        <v>3:45</v>
+        <v>3:09</v>
       </c>
       <c r="H76" t="str">
-        <v>NEEDTOBREATHE</v>
+        <v>Poppy</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
+        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
+        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
       </c>
       <c r="L76" t="str">
-        <v>The Long Surrender - NEEDTOBREATHE</v>
+        <v>Empty Hands - Poppy</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Angela</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/angela/1866624257</v>
+        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-23</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Angela - Single</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="G77" t="str">
-        <v>3:32</v>
+        <v>3:45</v>
       </c>
       <c r="H77" t="str">
-        <v>Hayden Everett</v>
+        <v>NEEDTOBREATHE</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/angela/1866624256</v>
+        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
       </c>
       <c r="L77" t="str">
-        <v>Angela - Hayden Everett</v>
+        <v>The Long Surrender - NEEDTOBREATHE</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Disappear</v>
+        <v>Angela</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/disappear/1847663553</v>
+        <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-23</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Greyhound</v>
+        <v>Angela - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>3:31</v>
+        <v>3:32</v>
       </c>
       <c r="H78" t="str">
-        <v>Katie Tupper</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/disappear/1847663546</v>
+        <v>https://music.apple.com/us/album/angela/1866624256</v>
       </c>
       <c r="L78" t="str">
-        <v>Disappear - Katie Tupper</v>
+        <v>Angela - Hayden Everett</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Catapult</v>
+        <v>Disappear</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/catapult/1862951335</v>
+        <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-23</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Catapult - Single</v>
+        <v>Greyhound</v>
       </c>
       <c r="G79" t="str">
-        <v>2:57</v>
+        <v>3:31</v>
       </c>
       <c r="H79" t="str">
-        <v>Cape Francis</v>
+        <v>Katie Tupper</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
+        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/catapult/1862951333</v>
+        <v>https://music.apple.com/us/album/disappear/1847663546</v>
       </c>
       <c r="L79" t="str">
-        <v>Catapult - Cape Francis</v>
+        <v>Disappear - Katie Tupper</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Think Twice</v>
+        <v>Catapult</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
+        <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-23</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Think Twice - Single</v>
+        <v>Catapult - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>2:22</v>
+        <v>2:57</v>
       </c>
       <c r="H80" t="str">
-        <v>Leonie Biney</v>
+        <v>Cape Francis</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
+        <v>https://music.apple.com/us/album/catapult/1862951333</v>
       </c>
       <c r="L80" t="str">
-        <v>Think Twice - Leonie Biney</v>
+        <v>Catapult - Cape Francis</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>LOVESONGS</v>
+        <v>Think Twice</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
+        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-23</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>BEAUTIFUL MADNESS</v>
+        <v>Think Twice - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:33</v>
+        <v>2:22</v>
       </c>
       <c r="H81" t="str">
-        <v>Agnes</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/agnes/42568985</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
+        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
       </c>
       <c r="L81" t="str">
-        <v>LOVESONGS - Agnes</v>
+        <v>Think Twice - Leonie Biney</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Down South</v>
+        <v>LOVESONGS</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/down-south/1861010793</v>
+        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-23</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Down South - Single</v>
+        <v>BEAUTIFUL MADNESS</v>
       </c>
       <c r="G82" t="str">
-        <v>2:19</v>
+        <v>3:33</v>
       </c>
       <c r="H82" t="str">
-        <v>Trap Dickey</v>
+        <v>Agnes</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/agnes/42568985</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/down-south/1861010788</v>
+        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
       </c>
       <c r="L82" t="str">
-        <v>Down South - Trap Dickey</v>
+        <v>LOVESONGS - Agnes</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
+        <v>Down South</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
+        <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-23</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
+        <v>Down South - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>2:16</v>
+        <v>2:19</v>
       </c>
       <c r="H83" t="str">
-        <v>SALIMATA</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/salimata/690253822</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
+        <v>https://music.apple.com/us/album/down-south/1861010788</v>
       </c>
       <c r="L83" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
+        <v>Down South - Trap Dickey</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Love Like This</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
+        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-23</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Love Like This - Single</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>3:30</v>
+        <v>2:16</v>
       </c>
       <c r="H84" t="str">
-        <v>Jacob Banks</v>
+        <v>SALIMATA</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
+        <v>https://music.apple.com/us/artist/salimata/690253822</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
+        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
       </c>
       <c r="L84" t="str">
-        <v>Love Like This - Jacob Banks</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Plan Plan</v>
+        <v>Love Like This</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
+        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-23</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>La Locura</v>
+        <v>Love Like This - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:10</v>
+        <v>3:30</v>
       </c>
       <c r="H85" t="str">
-        <v>Funky</v>
+        <v>Jacob Banks</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/funky/80960663</v>
+        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
+        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
       </c>
       <c r="L85" t="str">
-        <v>Plan Plan - Funky</v>
+        <v>Love Like This - Jacob Banks</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>double edged sword</v>
+        <v>Plan Plan</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
+        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-23</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>double edged sword - Single</v>
+        <v>La Locura</v>
       </c>
       <c r="G86" t="str">
-        <v>3:28</v>
+        <v>3:10</v>
       </c>
       <c r="H86" t="str">
-        <v>Hailey Picardi</v>
+        <v>Funky</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/funky/80960663</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
+        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
       </c>
       <c r="L86" t="str">
-        <v>double edged sword - Hailey Picardi</v>
+        <v>Plan Plan - Funky</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>SOMEWHERE IN BETWEEN</v>
+        <v>double edged sword</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
+        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-23</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>SOMEWHERE IN BETWEEN - Single</v>
+        <v>double edged sword - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>3:27</v>
+        <v>3:28</v>
       </c>
       <c r="H87" t="str">
-        <v>Matt Hansen</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
+        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
       </c>
       <c r="L87" t="str">
-        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
+        <v>double edged sword - Hailey Picardi</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>The Decay</v>
+        <v>SOMEWHERE IN BETWEEN</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
+        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-23</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>What Remains (Midnight Edition)</v>
+        <v>SOMEWHERE IN BETWEEN - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>3:20</v>
+        <v>3:27</v>
       </c>
       <c r="H88" t="str">
-        <v>Pop Evil</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
+        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
+        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
       </c>
       <c r="L88" t="str">
-        <v>The Decay - Pop Evil</v>
+        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>3111</v>
+        <v>The Decay</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/3111/1862225387</v>
+        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-23</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Goliath</v>
+        <v>What Remains (Midnight Edition)</v>
       </c>
       <c r="G89" t="str">
-        <v>4:08</v>
+        <v>3:20</v>
       </c>
       <c r="H89" t="str">
-        <v>Exodus</v>
+        <v>Pop Evil</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/3111/1862225385</v>
+        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
       </c>
       <c r="L89" t="str">
-        <v>3111 - Exodus</v>
+        <v>The Decay - Pop Evil</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Touch My Love And Die</v>
+        <v>3111</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+        <v>https://music.apple.com/us/song/3111/1862225387</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-23</v>
@@ -3795,68 +3795,106 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Touch My Love And Die - Single</v>
+        <v>Goliath</v>
       </c>
       <c r="G90" t="str">
-        <v>2:57</v>
+        <v>4:08</v>
       </c>
       <c r="H90" t="str">
-        <v>Myrkur</v>
+        <v>Exodus</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+        <v>https://music.apple.com/us/album/3111/1862225385</v>
       </c>
       <c r="L90" t="str">
-        <v>Touch My Love And Die - Myrkur</v>
+        <v>3111 - Exodus</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
+        <v>Touch My Love And Die</v>
+      </c>
+      <c r="B91" t="str">
+        <v/>
+      </c>
+      <c r="C91" t="str">
+        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+      </c>
+      <c r="D91" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v>Touch My Love And Die - Single</v>
+      </c>
+      <c r="G91" t="str">
+        <v>2:57</v>
+      </c>
+      <c r="H91" t="str">
+        <v>Myrkur</v>
+      </c>
+      <c r="I91" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J91" t="str">
+        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+      </c>
+      <c r="K91" t="str">
+        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+      </c>
+      <c r="L91" t="str">
+        <v>Touch My Love And Die - Myrkur</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
         <v>Bomb To A Knife Fight</v>
       </c>
-      <c r="B91" t="str">
-        <v/>
-      </c>
-      <c r="C91" t="str">
+      <c r="B92" t="str">
+        <v/>
+      </c>
+      <c r="C92" t="str">
         <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
-      <c r="D91" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E91" t="str">
-        <v/>
-      </c>
-      <c r="F91" t="str">
+      <c r="D92" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
         <v>Bomb To A Knife Fight - Single</v>
       </c>
-      <c r="G91" t="str">
+      <c r="G92" t="str">
         <v>2:41</v>
       </c>
-      <c r="H91" t="str">
+      <c r="H92" t="str">
         <v>The Barbarians of California</v>
       </c>
-      <c r="I91" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J91" t="str">
+      <c r="I92" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J92" t="str">
         <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
       </c>
-      <c r="K91" t="str">
+      <c r="K92" t="str">
         <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
       </c>
-      <c r="L91" t="str">
+      <c r="L92" t="str">
         <v>Bomb To A Knife Fight - The Barbarians of California</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L91"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L92"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L92"/>
+  <dimension ref="A1:L93"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/aperture/1870984033</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/high-key/1847702418</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/scared/1862292863</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/atm/1871258339</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/dead-end/1862845874</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/bad/1869095326</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/losing-you/1863525495</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2032,1869 +2032,1907 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Say Yes</v>
+        <v>dust to dust</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
+        <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Say Yes - Single</v>
+        <v>Rivers of Sugar and Blood - EP</v>
       </c>
       <c r="G44" t="str">
-        <v>2:50</v>
+        <v>3:51</v>
       </c>
       <c r="H44" t="str">
-        <v>Marques Anthony</v>
+        <v>Truman Sinclair</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
+        <v>https://music.apple.com/us/artist/truman-sinclair/1483104826</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
+        <v>https://music.apple.com/us/album/dust-to-dust/1869116937</v>
       </c>
       <c r="L44" t="str">
-        <v>Say Yes - Marques Anthony</v>
+        <v>dust to dust - Truman Sinclair</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>LOVE ME (feat. Stevie Wonder)</v>
+        <v>Say Yes</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
+        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>CAMPILATION</v>
+        <v>Say Yes - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>3:10</v>
+        <v>2:50</v>
       </c>
       <c r="H45" t="str">
-        <v>Camper</v>
+        <v>Marques Anthony</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/camper/1514886616</v>
+        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
+        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
       </c>
       <c r="L45" t="str">
-        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
+        <v>Say Yes - Marques Anthony</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Ojalá</v>
+        <v>LOVE ME (feat. Stevie Wonder)</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
+        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Ojalá - Single</v>
+        <v>CAMPILATION</v>
       </c>
       <c r="G46" t="str">
-        <v>4:11</v>
+        <v>3:10</v>
       </c>
       <c r="H46" t="str">
-        <v>Lunay</v>
+        <v>Camper</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/lunay/938127685</v>
+        <v>https://music.apple.com/us/artist/camper/1514886616</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
+        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
       </c>
       <c r="L46" t="str">
-        <v>Ojalá - Lunay</v>
+        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>UP TO MY NECK IN U</v>
+        <v>Ojalá</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
+        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>UP TO MY NECK IN U - Single</v>
+        <v>Ojalá - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>2:17</v>
+        <v>4:11</v>
       </c>
       <c r="H47" t="str">
-        <v>Ledbyher</v>
+        <v>Lunay</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/lunay/938127685</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
+        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
       </c>
       <c r="L47" t="str">
-        <v>UP TO MY NECK IN U - Ledbyher</v>
+        <v>Ojalá - Lunay</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Wallflower</v>
+        <v>UP TO MY NECK IN U</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
+        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Wallflower - Single</v>
+        <v>UP TO MY NECK IN U - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>3:25</v>
+        <v>2:17</v>
       </c>
       <c r="H48" t="str">
-        <v>Sikarus</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
+        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
       </c>
       <c r="L48" t="str">
-        <v>Wallflower - Sikarus</v>
+        <v>UP TO MY NECK IN U - Ledbyher</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>You Phase</v>
+        <v>Wallflower</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
+        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>You Phase - Single</v>
+        <v>Wallflower - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>2:51</v>
+        <v>3:25</v>
       </c>
       <c r="H49" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Sikarus</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
+        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
+        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
       </c>
       <c r="L49" t="str">
-        <v>You Phase - Mitchell Tenpenny</v>
+        <v>Wallflower - Sikarus</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Miss Independent</v>
+        <v>You Phase</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
+        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Miss Independent - Single</v>
+        <v>You Phase - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>2:40</v>
+        <v>2:51</v>
       </c>
       <c r="H50" t="str">
-        <v>1Ski OG</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
+        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
       </c>
       <c r="L50" t="str">
-        <v>Miss Independent - 1Ski OG</v>
+        <v>You Phase - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
+        <v>Miss Independent</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
+        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>Miss Independent - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>5:47</v>
+        <v>2:40</v>
       </c>
       <c r="H51" t="str">
-        <v>Elevation Worship</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
       </c>
       <c r="L51" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
+        <v>Miss Independent - 1Ski OG</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>go again</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/go-again/1868987466</v>
+        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>go again - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G52" t="str">
-        <v>2:07</v>
+        <v>5:47</v>
       </c>
       <c r="H52" t="str">
-        <v>NateTaylorr</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/go-again/1868987193</v>
+        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
       </c>
       <c r="L52" t="str">
-        <v>go again - NateTaylorr</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Autopilot</v>
+        <v>go again</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
+        <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Autopilot</v>
+        <v>go again - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>2:46</v>
+        <v>2:07</v>
       </c>
       <c r="H53" t="str">
-        <v>ALEXSUCKS</v>
+        <v>NateTaylorr</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
+        <v>https://music.apple.com/us/album/go-again/1868987193</v>
       </c>
       <c r="L53" t="str">
-        <v>Autopilot - ALEXSUCKS</v>
+        <v>go again - NateTaylorr</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates)</v>
+        <v>Autopilot</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
+        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Portrait of My Heart - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G54" t="str">
-        <v>3:04</v>
+        <v>2:46</v>
       </c>
       <c r="H54" t="str">
-        <v>SPELLLING</v>
+        <v>ALEXSUCKS</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
+        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
       </c>
       <c r="L54" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
+        <v>Autopilot - ALEXSUCKS</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>In Violet</v>
+        <v>Portrait of My Heart (feat. Brendan Yates)</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
+        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Death in the Business of Whaling</v>
+        <v>Portrait of My Heart - Single</v>
       </c>
       <c r="G55" t="str">
-        <v>4:09</v>
+        <v>3:04</v>
       </c>
       <c r="H55" t="str">
-        <v>Searows</v>
+        <v>SPELLLING</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/searows/1607240507</v>
+        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
+        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
       </c>
       <c r="L55" t="str">
-        <v>In Violet - Searows</v>
+        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Baby Run</v>
+        <v>In Violet</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
+        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Baby Run - Single</v>
+        <v>Death in the Business of Whaling</v>
       </c>
       <c r="G56" t="str">
-        <v>4:47</v>
+        <v>4:09</v>
       </c>
       <c r="H56" t="str">
-        <v>Jimi Jules</v>
+        <v>Searows</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
+        <v>https://music.apple.com/us/artist/searows/1607240507</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
+        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
       </c>
       <c r="L56" t="str">
-        <v>Baby Run - Jimi Jules</v>
+        <v>In Violet - Searows</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>What If We Don't</v>
+        <v>Baby Run</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
+        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>What If We Don't - Single</v>
+        <v>Baby Run - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>3:06</v>
+        <v>4:47</v>
       </c>
       <c r="H57" t="str">
-        <v>Ashley McBryde</v>
+        <v>Jimi Jules</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
+        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
       </c>
       <c r="L57" t="str">
-        <v>What If We Don't - Ashley McBryde</v>
+        <v>Baby Run - Jimi Jules</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Hagamos Que</v>
+        <v>What If We Don't</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
+        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Hagamos Que - Single</v>
+        <v>What If We Don't - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>2:58</v>
+        <v>3:06</v>
       </c>
       <c r="H58" t="str">
-        <v>Juanes</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
+        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
       </c>
       <c r="L58" t="str">
-        <v>Hagamos Que - Juanes</v>
+        <v>What If We Don't - Ashley McBryde</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>World Change Me</v>
+        <v>Hagamos Que</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
+        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>World Change Me - Single</v>
+        <v>Hagamos Que - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>3:03</v>
+        <v>2:58</v>
       </c>
       <c r="H59" t="str">
-        <v>Max McNown</v>
+        <v>Juanes</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
+        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
       </c>
       <c r="L59" t="str">
-        <v>World Change Me - Max McNown</v>
+        <v>Hagamos Que - Juanes</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Exclusive</v>
+        <v>World Change Me</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
+        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Exclusive - EP</v>
+        <v>World Change Me - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>3:20</v>
+        <v>3:03</v>
       </c>
       <c r="H60" t="str">
-        <v>Hudson Westbrook</v>
+        <v>Max McNown</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
+        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
       </c>
       <c r="L60" t="str">
-        <v>Exclusive - Hudson Westbrook</v>
+        <v>World Change Me - Max McNown</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Say Less</v>
+        <v>Exclusive</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/say-less/1867910122</v>
+        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Say Less - Single</v>
+        <v>Exclusive - EP</v>
       </c>
       <c r="G61" t="str">
-        <v>2:18</v>
+        <v>3:20</v>
       </c>
       <c r="H61" t="str">
-        <v>JYT</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/say-less/1867910115</v>
+        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
       </c>
       <c r="L61" t="str">
-        <v>Say Less - JYT</v>
+        <v>Exclusive - Hudson Westbrook</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Angels Cry</v>
+        <v>Say Less</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
+        <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>X's for Eyes (Deluxe)</v>
+        <v>Say Less - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>3:52</v>
+        <v>2:18</v>
       </c>
       <c r="H62" t="str">
-        <v>The Red Jumpsuit Apparatus</v>
+        <v>JYT</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
+        <v>https://music.apple.com/us/album/say-less/1867910115</v>
       </c>
       <c r="L62" t="str">
-        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
+        <v>Say Less - JYT</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Over You</v>
+        <v>Angels Cry</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/over-you/1846189473</v>
+        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>A Love For Strangers</v>
+        <v>X's for Eyes (Deluxe)</v>
       </c>
       <c r="G63" t="str">
-        <v>4:44</v>
+        <v>3:52</v>
       </c>
       <c r="H63" t="str">
-        <v>Chet Faker</v>
+        <v>The Red Jumpsuit Apparatus</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/over-you/1846189472</v>
+        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
       </c>
       <c r="L63" t="str">
-        <v>Over You - Chet Faker</v>
+        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Chala (My Soul Is on a Loop)</v>
+        <v>Over You</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
+        <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Chala (My Soul Is on a Loop) - Single</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G64" t="str">
-        <v>2:42</v>
+        <v>4:44</v>
       </c>
       <c r="H64" t="str">
-        <v>Barry Can't Swim</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
+        <v>https://music.apple.com/us/album/over-you/1846189472</v>
       </c>
       <c r="L64" t="str">
-        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
+        <v>Over You - Chet Faker</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>starlight feat. Madeline Follin</v>
+        <v>Chala (My Soul Is on a Loop)</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
+        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>starlight feat. Madeline Follin - Single</v>
+        <v>Chala (My Soul Is on a Loop) - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>3:06</v>
+        <v>2:42</v>
       </c>
       <c r="H65" t="str">
-        <v>Disco Lines</v>
+        <v>Barry Can't Swim</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
+        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
+        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
       </c>
       <c r="L65" t="str">
-        <v>starlight feat. Madeline Follin - Disco Lines</v>
+        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Locked In (feat. Trippie Redd)</v>
+        <v>starlight feat. Madeline Follin</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
+        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Locked In (feat. Trippie Redd) - Single</v>
+        <v>starlight feat. Madeline Follin - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>2:48</v>
+        <v>3:06</v>
       </c>
       <c r="H66" t="str">
-        <v>David Guetta</v>
+        <v>Disco Lines</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
+        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
+        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
       </c>
       <c r="L66" t="str">
-        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
+        <v>starlight feat. Madeline Follin - Disco Lines</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Rejoice</v>
+        <v>Locked In (feat. Trippie Redd)</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
+        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Rejoice - Single</v>
+        <v>Locked In (feat. Trippie Redd) - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>4:20</v>
+        <v>2:48</v>
       </c>
       <c r="H67" t="str">
-        <v>Def Leppard</v>
+        <v>David Guetta</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
+        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
+        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
       </c>
       <c r="L67" t="str">
-        <v>Rejoice - Def Leppard</v>
+        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
+        <v>Rejoice</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
+        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
+        <v>Rejoice - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>2:58</v>
+        <v>4:20</v>
       </c>
       <c r="H68" t="str">
-        <v>Honey Dijon</v>
+        <v>Def Leppard</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
+        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
       </c>
       <c r="L68" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
+        <v>Rejoice - Def Leppard</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Odisea</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/odisea/1866927906</v>
+        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Odisea - Single</v>
+        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>3:56</v>
+        <v>2:58</v>
       </c>
       <c r="H69" t="str">
-        <v>BASSYY</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/odisea/1866927904</v>
+        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
       </c>
       <c r="L69" t="str">
-        <v>Odisea - BASSYY</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Lucky Day</v>
+        <v>Odisea</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
+        <v>https://music.apple.com/us/song/odisea/1866927906</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Speed Kills</v>
+        <v>Odisea - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>3:13</v>
+        <v>3:56</v>
       </c>
       <c r="H70" t="str">
-        <v>Ally Evenson</v>
+        <v>BASSYY</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
+        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
+        <v>https://music.apple.com/us/album/odisea/1866927904</v>
       </c>
       <c r="L70" t="str">
-        <v>Lucky Day - Ally Evenson</v>
+        <v>Odisea - BASSYY</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Breathe On It</v>
+        <v>Lucky Day</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
+        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Breathe On It - Single</v>
+        <v>Speed Kills</v>
       </c>
       <c r="G71" t="str">
-        <v>4:00</v>
+        <v>3:13</v>
       </c>
       <c r="H71" t="str">
-        <v>Tauren Wells</v>
+        <v>Ally Evenson</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
+        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
       </c>
       <c r="L71" t="str">
-        <v>Breathe On It - Tauren Wells</v>
+        <v>Lucky Day - Ally Evenson</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Easy</v>
+        <v>Breathe On It</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/easy/1863456906</v>
+        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Easy - Single</v>
+        <v>Breathe On It - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>4:30</v>
+        <v>4:00</v>
       </c>
       <c r="H72" t="str">
-        <v>lydi lynn</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/easy/1863456903</v>
+        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
       </c>
       <c r="L72" t="str">
-        <v>Easy - lydi lynn</v>
+        <v>Breathe On It - Tauren Wells</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Break Me In</v>
+        <v>Easy</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
+        <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Break Me In - Single</v>
+        <v>Easy - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>2:52</v>
+        <v>4:30</v>
       </c>
       <c r="H73" t="str">
-        <v>Joyce Wrice</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
+        <v>https://music.apple.com/us/album/easy/1863456903</v>
       </c>
       <c r="L73" t="str">
-        <v>Break Me In - Joyce Wrice</v>
+        <v>Easy - lydi lynn</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Long Live Love</v>
+        <v>Break Me In</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
+        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Long Live Love - Single</v>
+        <v>Break Me In - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>2:36</v>
+        <v>2:52</v>
       </c>
       <c r="H74" t="str">
-        <v>Sugar</v>
+        <v>Joyce Wrice</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/sugar/530175867</v>
+        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
+        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
       </c>
       <c r="L74" t="str">
-        <v>Long Live Love - Sugar</v>
+        <v>Break Me In - Joyce Wrice</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Depressed</v>
+        <v>Long Live Love</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/depressed/1840400522</v>
+        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Boycott Heaven</v>
+        <v>Long Live Love - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>3:32</v>
+        <v>2:36</v>
       </c>
       <c r="H75" t="str">
-        <v>The Format</v>
+        <v>Sugar</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/the-format/3064903</v>
+        <v>https://music.apple.com/us/artist/sugar/530175867</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/depressed/1840399886</v>
+        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
       </c>
       <c r="L75" t="str">
-        <v>Depressed - The Format</v>
+        <v>Long Live Love - Sugar</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Empty Hands</v>
+        <v>Depressed</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
+        <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Empty Hands</v>
+        <v>Boycott Heaven</v>
       </c>
       <c r="G76" t="str">
-        <v>3:09</v>
+        <v>3:32</v>
       </c>
       <c r="H76" t="str">
-        <v>Poppy</v>
+        <v>The Format</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
+        <v>https://music.apple.com/us/artist/the-format/3064903</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
+        <v>https://music.apple.com/us/album/depressed/1840399886</v>
       </c>
       <c r="L76" t="str">
-        <v>Empty Hands - Poppy</v>
+        <v>Depressed - The Format</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>The Long Surrender</v>
+        <v>Empty Hands</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
+        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>The Long Surrender</v>
+        <v>Empty Hands</v>
       </c>
       <c r="G77" t="str">
-        <v>3:45</v>
+        <v>3:09</v>
       </c>
       <c r="H77" t="str">
-        <v>NEEDTOBREATHE</v>
+        <v>Poppy</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
+        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
+        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
       </c>
       <c r="L77" t="str">
-        <v>The Long Surrender - NEEDTOBREATHE</v>
+        <v>Empty Hands - Poppy</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Angela</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/angela/1866624257</v>
+        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Angela - Single</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="G78" t="str">
-        <v>3:32</v>
+        <v>3:45</v>
       </c>
       <c r="H78" t="str">
-        <v>Hayden Everett</v>
+        <v>NEEDTOBREATHE</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/angela/1866624256</v>
+        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
       </c>
       <c r="L78" t="str">
-        <v>Angela - Hayden Everett</v>
+        <v>The Long Surrender - NEEDTOBREATHE</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Disappear</v>
+        <v>Angela</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/disappear/1847663553</v>
+        <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Greyhound</v>
+        <v>Angela - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:31</v>
+        <v>3:32</v>
       </c>
       <c r="H79" t="str">
-        <v>Katie Tupper</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/disappear/1847663546</v>
+        <v>https://music.apple.com/us/album/angela/1866624256</v>
       </c>
       <c r="L79" t="str">
-        <v>Disappear - Katie Tupper</v>
+        <v>Angela - Hayden Everett</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Catapult</v>
+        <v>Disappear</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/catapult/1862951335</v>
+        <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Catapult - Single</v>
+        <v>Greyhound</v>
       </c>
       <c r="G80" t="str">
-        <v>2:57</v>
+        <v>3:31</v>
       </c>
       <c r="H80" t="str">
-        <v>Cape Francis</v>
+        <v>Katie Tupper</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
+        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/catapult/1862951333</v>
+        <v>https://music.apple.com/us/album/disappear/1847663546</v>
       </c>
       <c r="L80" t="str">
-        <v>Catapult - Cape Francis</v>
+        <v>Disappear - Katie Tupper</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Think Twice</v>
+        <v>Catapult</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
+        <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Think Twice - Single</v>
+        <v>Catapult - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>2:22</v>
+        <v>2:57</v>
       </c>
       <c r="H81" t="str">
-        <v>Leonie Biney</v>
+        <v>Cape Francis</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
+        <v>https://music.apple.com/us/album/catapult/1862951333</v>
       </c>
       <c r="L81" t="str">
-        <v>Think Twice - Leonie Biney</v>
+        <v>Catapult - Cape Francis</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>LOVESONGS</v>
+        <v>Think Twice</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
+        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>BEAUTIFUL MADNESS</v>
+        <v>Think Twice - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>3:33</v>
+        <v>2:22</v>
       </c>
       <c r="H82" t="str">
-        <v>Agnes</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/agnes/42568985</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
+        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
       </c>
       <c r="L82" t="str">
-        <v>LOVESONGS - Agnes</v>
+        <v>Think Twice - Leonie Biney</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Down South</v>
+        <v>LOVESONGS</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/down-south/1861010793</v>
+        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Down South - Single</v>
+        <v>BEAUTIFUL MADNESS</v>
       </c>
       <c r="G83" t="str">
-        <v>2:19</v>
+        <v>3:33</v>
       </c>
       <c r="H83" t="str">
-        <v>Trap Dickey</v>
+        <v>Agnes</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/agnes/42568985</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/down-south/1861010788</v>
+        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
       </c>
       <c r="L83" t="str">
-        <v>Down South - Trap Dickey</v>
+        <v>LOVESONGS - Agnes</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
+        <v>Down South</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
+        <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
+        <v>Down South - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>2:16</v>
+        <v>2:19</v>
       </c>
       <c r="H84" t="str">
-        <v>SALIMATA</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/salimata/690253822</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
+        <v>https://music.apple.com/us/album/down-south/1861010788</v>
       </c>
       <c r="L84" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
+        <v>Down South - Trap Dickey</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Love Like This</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
+        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Love Like This - Single</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:30</v>
+        <v>2:16</v>
       </c>
       <c r="H85" t="str">
-        <v>Jacob Banks</v>
+        <v>SALIMATA</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
+        <v>https://music.apple.com/us/artist/salimata/690253822</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
+        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
       </c>
       <c r="L85" t="str">
-        <v>Love Like This - Jacob Banks</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Plan Plan</v>
+        <v>Love Like This</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
+        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>La Locura</v>
+        <v>Love Like This - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:10</v>
+        <v>3:30</v>
       </c>
       <c r="H86" t="str">
-        <v>Funky</v>
+        <v>Jacob Banks</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/funky/80960663</v>
+        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
+        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
       </c>
       <c r="L86" t="str">
-        <v>Plan Plan - Funky</v>
+        <v>Love Like This - Jacob Banks</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>double edged sword</v>
+        <v>Plan Plan</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
+        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>double edged sword - Single</v>
+        <v>La Locura</v>
       </c>
       <c r="G87" t="str">
-        <v>3:28</v>
+        <v>3:10</v>
       </c>
       <c r="H87" t="str">
-        <v>Hailey Picardi</v>
+        <v>Funky</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/funky/80960663</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
+        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
       </c>
       <c r="L87" t="str">
-        <v>double edged sword - Hailey Picardi</v>
+        <v>Plan Plan - Funky</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>SOMEWHERE IN BETWEEN</v>
+        <v>double edged sword</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
+        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>SOMEWHERE IN BETWEEN - Single</v>
+        <v>double edged sword - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>3:27</v>
+        <v>3:28</v>
       </c>
       <c r="H88" t="str">
-        <v>Matt Hansen</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
+        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
       </c>
       <c r="L88" t="str">
-        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
+        <v>double edged sword - Hailey Picardi</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>The Decay</v>
+        <v>SOMEWHERE IN BETWEEN</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
+        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>What Remains (Midnight Edition)</v>
+        <v>SOMEWHERE IN BETWEEN - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>3:20</v>
+        <v>3:27</v>
       </c>
       <c r="H89" t="str">
-        <v>Pop Evil</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
+        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
+        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
       </c>
       <c r="L89" t="str">
-        <v>The Decay - Pop Evil</v>
+        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>3111</v>
+        <v>The Decay</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/3111/1862225387</v>
+        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Goliath</v>
+        <v>What Remains (Midnight Edition)</v>
       </c>
       <c r="G90" t="str">
-        <v>4:08</v>
+        <v>3:20</v>
       </c>
       <c r="H90" t="str">
-        <v>Exodus</v>
+        <v>Pop Evil</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/3111/1862225385</v>
+        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
       </c>
       <c r="L90" t="str">
-        <v>3111 - Exodus</v>
+        <v>The Decay - Pop Evil</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Touch My Love And Die</v>
+        <v>3111</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+        <v>https://music.apple.com/us/song/3111/1862225387</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Touch My Love And Die - Single</v>
+        <v>Goliath</v>
       </c>
       <c r="G91" t="str">
-        <v>2:57</v>
+        <v>4:08</v>
       </c>
       <c r="H91" t="str">
-        <v>Myrkur</v>
+        <v>Exodus</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+        <v>https://music.apple.com/us/album/3111/1862225385</v>
       </c>
       <c r="L91" t="str">
-        <v>Touch My Love And Die - Myrkur</v>
+        <v>3111 - Exodus</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
+        <v>Touch My Love And Die</v>
+      </c>
+      <c r="B92" t="str">
+        <v/>
+      </c>
+      <c r="C92" t="str">
+        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+      </c>
+      <c r="D92" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v>Touch My Love And Die - Single</v>
+      </c>
+      <c r="G92" t="str">
+        <v>2:57</v>
+      </c>
+      <c r="H92" t="str">
+        <v>Myrkur</v>
+      </c>
+      <c r="I92" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J92" t="str">
+        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+      </c>
+      <c r="K92" t="str">
+        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+      </c>
+      <c r="L92" t="str">
+        <v>Touch My Love And Die - Myrkur</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
         <v>Bomb To A Knife Fight</v>
       </c>
-      <c r="B92" t="str">
-        <v/>
-      </c>
-      <c r="C92" t="str">
+      <c r="B93" t="str">
+        <v/>
+      </c>
+      <c r="C93" t="str">
         <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
-      <c r="D92" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E92" t="str">
-        <v/>
-      </c>
-      <c r="F92" t="str">
+      <c r="D93" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
         <v>Bomb To A Knife Fight - Single</v>
       </c>
-      <c r="G92" t="str">
+      <c r="G93" t="str">
         <v>2:41</v>
       </c>
-      <c r="H92" t="str">
+      <c r="H93" t="str">
         <v>The Barbarians of California</v>
       </c>
-      <c r="I92" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J92" t="str">
+      <c r="I93" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J93" t="str">
         <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
       </c>
-      <c r="K92" t="str">
+      <c r="K93" t="str">
         <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
       </c>
-      <c r="L92" t="str">
+      <c r="L93" t="str">
         <v>Bomb To A Knife Fight - The Barbarians of California</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L92"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L93"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/aperture/1870984033</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/high-key/1847702418</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/scared/1862292863</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/atm/1871258339</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/dead-end/1862845874</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/bad/1869095326</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/losing-you/1863525495</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/odisea/1866927906</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/3111/1862225387</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E93" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/aperture/1870984033</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/high-key/1847702418</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/scared/1862292863</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/atm/1871258339</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/dead-end/1862845874</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/bad/1869095326</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/losing-you/1863525495</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/odisea/1866927906</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/3111/1862225387</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E93" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>La Locura</v>
+        <v>La Locura, Vol. 1</v>
       </c>
       <c r="G87" t="str">
         <v>3:10</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/aperture/1870984033</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/high-key/1847702418</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/scared/1862292863</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/atm/1871258339</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/dead-end/1862845874</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/bad/1869095326</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/losing-you/1863525495</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/odisea/1866927906</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/3111/1862225387</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E93" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L94"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1234,13 +1234,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Me Voy A La C******a</v>
+        <v>Arrhythmia (I Hope You Stay)</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
+        <v>https://music.apple.com/us/song/arrhythmia-i-hope-you-stay/1867164656</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-27</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Infinito</v>
+        <v>Arrhythmia (I Hope You Stay) - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>2:14</v>
+        <v>3:02</v>
       </c>
       <c r="H23" t="str">
-        <v>Yandel</v>
+        <v>The Runarounds</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/yandel/72929426</v>
+        <v>https://music.apple.com/us/artist/the-runarounds/1660817420</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
+        <v>https://music.apple.com/us/album/arrhythmia-i-hope-you-stay/1867164652</v>
       </c>
       <c r="L23" t="str">
-        <v>Me Voy A La C******a - Yandel</v>
+        <v>Arrhythmia (I Hope You Stay) - The Runarounds</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Sexy For Me</v>
+        <v>Me Voy A La C******a</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
+        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-27</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>The Last Dance (Part 1)</v>
+        <v>Infinito</v>
       </c>
       <c r="G24" t="str">
-        <v>2:08</v>
+        <v>2:14</v>
       </c>
       <c r="H24" t="str">
-        <v>Jason Derulo</v>
+        <v>Yandel</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
+        <v>https://music.apple.com/us/artist/yandel/72929426</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
+        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
       </c>
       <c r="L24" t="str">
-        <v>Sexy For Me - Jason Derulo</v>
+        <v>Me Voy A La C******a - Yandel</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Turbulence</v>
+        <v>Sexy For Me</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
+        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-27</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>REAL, Vol. 1 - EP</v>
+        <v>The Last Dance (Part 1)</v>
       </c>
       <c r="G25" t="str">
-        <v>2:25</v>
+        <v>2:08</v>
       </c>
       <c r="H25" t="str">
-        <v>Wizkid</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
+        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
+        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
       </c>
       <c r="L25" t="str">
-        <v>Turbulence - Wizkid</v>
+        <v>Sexy For Me - Jason Derulo</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>I’m Good (From The Movie “GOAT”)</v>
+        <v>Turbulence</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
+        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-27</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>REAL, Vol. 1 - EP</v>
       </c>
       <c r="G26" t="str">
-        <v>2:59</v>
+        <v>2:25</v>
       </c>
       <c r="H26" t="str">
-        <v>Jelly Roll</v>
+        <v>Wizkid</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
       </c>
       <c r="L26" t="str">
-        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
+        <v>Turbulence - Wizkid</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
+        <v>I’m Good (From The Movie “GOAT”)</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
+        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-27</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G27" t="str">
-        <v>3:47</v>
+        <v>2:59</v>
       </c>
       <c r="H27" t="str">
-        <v>Dolly Parton</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
+        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L27" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
+        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ESCONDIDAS</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
+        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-27</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>SILENCIO HABLA</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>2:53</v>
+        <v>3:47</v>
       </c>
       <c r="H28" t="str">
-        <v>Oscar Ortiz</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
+        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
+        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
       </c>
       <c r="L28" t="str">
-        <v>ESCONDIDAS - Oscar Ortiz</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Alabama Beauty Queen</v>
+        <v>ESCONDIDAS</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
+        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-27</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Act I</v>
+        <v>SILENCIO HABLA</v>
       </c>
       <c r="G29" t="str">
-        <v>3:43</v>
+        <v>2:53</v>
       </c>
       <c r="H29" t="str">
-        <v>Kashus Culpepper</v>
+        <v>Oscar Ortiz</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
+        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
+        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
       </c>
       <c r="L29" t="str">
-        <v>Alabama Beauty Queen - Kashus Culpepper</v>
+        <v>ESCONDIDAS - Oscar Ortiz</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Imposter</v>
+        <v>Alabama Beauty Queen</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/imposter/1842408050</v>
+        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-27</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>How Did I Get Here?</v>
+        <v>Act I</v>
       </c>
       <c r="G30" t="str">
-        <v>2:38</v>
+        <v>3:43</v>
       </c>
       <c r="H30" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Kashus Culpepper</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/imposter/1842408037</v>
+        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
       </c>
       <c r="L30" t="str">
-        <v>Imposter - Louis Tomlinson</v>
+        <v>Alabama Beauty Queen - Kashus Culpepper</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Puddles (Zero 7 Remix)</v>
+        <v>Imposter</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
+        <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-27</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Puddles (Zero 7 Remix) - Single</v>
+        <v>How Did I Get Here?</v>
       </c>
       <c r="G31" t="str">
-        <v>6:01</v>
+        <v>2:38</v>
       </c>
       <c r="H31" t="str">
-        <v>Not for Radio</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
+        <v>https://music.apple.com/us/album/imposter/1842408037</v>
       </c>
       <c r="L31" t="str">
-        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
+        <v>Imposter - Louis Tomlinson</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Little Miss (Misdemeanor)</v>
+        <v>Puddles (Zero 7 Remix)</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
+        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-27</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Little Miss (Misdemeanor) - Single</v>
+        <v>Puddles (Zero 7 Remix) - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>2:24</v>
+        <v>6:01</v>
       </c>
       <c r="H32" t="str">
-        <v>GIRLSET</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
+        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
       </c>
       <c r="L32" t="str">
-        <v>Little Miss (Misdemeanor) - GIRLSET</v>
+        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>I Could Get Used To This</v>
+        <v>Little Miss (Misdemeanor)</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
+        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-27</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>I Could Get Used To This - Single</v>
+        <v>Little Miss (Misdemeanor) - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>3:41</v>
+        <v>2:24</v>
       </c>
       <c r="H33" t="str">
-        <v>Jessie Ware</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
+        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
       </c>
       <c r="L33" t="str">
-        <v>I Could Get Used To This - Jessie Ware</v>
+        <v>Little Miss (Misdemeanor) - GIRLSET</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>LA VILLA</v>
+        <v>I Could Get Used To This</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
+        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-27</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>HOPI SENDÉ</v>
+        <v>I Could Get Used To This - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>3:12</v>
+        <v>3:41</v>
       </c>
       <c r="H34" t="str">
-        <v>Ryan Castro</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
+        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
       </c>
       <c r="L34" t="str">
-        <v>LA VILLA - Ryan Castro</v>
+        <v>I Could Get Used To This - Jessie Ware</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
+        <v>LA VILLA</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
+        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-27</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>HOPI SENDÉ</v>
       </c>
       <c r="G35" t="str">
-        <v>3:27</v>
+        <v>3:12</v>
       </c>
       <c r="H35" t="str">
-        <v>Denzel Curry</v>
+        <v>Ryan Castro</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
+        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
       </c>
       <c r="L35" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
+        <v>LA VILLA - Ryan Castro</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Thick One</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
+        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-27</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Part 3</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G36" t="str">
-        <v>2:49</v>
+        <v>3:27</v>
       </c>
       <c r="H36" t="str">
-        <v>42 Dugg</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
+        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
       </c>
       <c r="L36" t="str">
-        <v>Thick One - 42 Dugg</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>How Much Did You Get For Your Soul</v>
+        <v>Thick One</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
+        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-27</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>World's Gone Wrong</v>
+        <v>Part 3</v>
       </c>
       <c r="G37" t="str">
-        <v>3:59</v>
+        <v>2:49</v>
       </c>
       <c r="H37" t="str">
-        <v>Lucinda Williams</v>
+        <v>42 Dugg</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
+        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
+        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
       </c>
       <c r="L37" t="str">
-        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
+        <v>Thick One - 42 Dugg</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>THUM</v>
+        <v>How Much Did You Get For Your Soul</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/thum/1863009362</v>
+        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-27</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>THUM - Single</v>
+        <v>World's Gone Wrong</v>
       </c>
       <c r="G38" t="str">
-        <v>2:11</v>
+        <v>3:59</v>
       </c>
       <c r="H38" t="str">
-        <v>Violet Grohl</v>
+        <v>Lucinda Williams</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/thum/1863009357</v>
+        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
       </c>
       <c r="L38" t="str">
-        <v>THUM - Violet Grohl</v>
+        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>(I'm a) Rock "N" Roller</v>
+        <v>THUM</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
+        <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-27</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>The Great Satan</v>
+        <v>THUM - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>3:32</v>
+        <v>2:11</v>
       </c>
       <c r="H39" t="str">
-        <v>Rob Zombie</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
+        <v>https://music.apple.com/us/album/thum/1863009357</v>
       </c>
       <c r="L39" t="str">
-        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
+        <v>THUM - Violet Grohl</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Excuses For Love</v>
+        <v>(I'm a) Rock "N" Roller</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
+        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-27</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Hyperlove</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G40" t="str">
-        <v>3:04</v>
+        <v>3:32</v>
       </c>
       <c r="H40" t="str">
-        <v>MIKA</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/mika/184932871</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
+        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
       </c>
       <c r="L40" t="str">
-        <v>Excuses For Love - MIKA</v>
+        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>3 Tears</v>
+        <v>Excuses For Love</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
+        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-27</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>3 Tears - Single</v>
+        <v>Hyperlove</v>
       </c>
       <c r="G41" t="str">
-        <v>2:50</v>
+        <v>3:04</v>
       </c>
       <c r="H41" t="str">
-        <v>Mergui</v>
+        <v>MIKA</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
+        <v>https://music.apple.com/us/artist/mika/184932871</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
+        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
       </c>
       <c r="L41" t="str">
-        <v>3 Tears - Mergui</v>
+        <v>Excuses For Love - MIKA</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Church Girl</v>
+        <v>3 Tears</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
+        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-27</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Church Girl - Single</v>
+        <v>3 Tears - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>3:19</v>
+        <v>2:50</v>
       </c>
       <c r="H42" t="str">
-        <v>Carly Pearce</v>
+        <v>Mergui</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
+        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
       </c>
       <c r="L42" t="str">
-        <v>Church Girl - Carly Pearce</v>
+        <v>3 Tears - Mergui</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Funeral</v>
+        <v>Church Girl</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/funeral/1867616928</v>
+        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-27</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>The Weight of the Woods</v>
+        <v>Church Girl - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>4:03</v>
+        <v>3:19</v>
       </c>
       <c r="H43" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/funeral/1867616617</v>
+        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
       </c>
       <c r="L43" t="str">
-        <v>Funeral - Dermot Kennedy</v>
+        <v>Church Girl - Carly Pearce</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>dust to dust</v>
+        <v>Funeral</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
+        <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-27</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Rivers of Sugar and Blood - EP</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G44" t="str">
-        <v>3:51</v>
+        <v>4:03</v>
       </c>
       <c r="H44" t="str">
-        <v>Truman Sinclair</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/truman-sinclair/1483104826</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/dust-to-dust/1869116937</v>
+        <v>https://music.apple.com/us/album/funeral/1867616617</v>
       </c>
       <c r="L44" t="str">
-        <v>dust to dust - Truman Sinclair</v>
+        <v>Funeral - Dermot Kennedy</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Say Yes</v>
+        <v>dust to dust</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
+        <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-27</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Say Yes - Single</v>
+        <v>Rivers of Sugar and Blood - EP</v>
       </c>
       <c r="G45" t="str">
-        <v>2:50</v>
+        <v>3:51</v>
       </c>
       <c r="H45" t="str">
-        <v>Marques Anthony</v>
+        <v>Truman Sinclair</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
+        <v>https://music.apple.com/us/artist/truman-sinclair/1483104826</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
+        <v>https://music.apple.com/us/album/dust-to-dust/1869116937</v>
       </c>
       <c r="L45" t="str">
-        <v>Say Yes - Marques Anthony</v>
+        <v>dust to dust - Truman Sinclair</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>LOVE ME (feat. Stevie Wonder)</v>
+        <v>Say Yes</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
+        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-27</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>CAMPILATION</v>
+        <v>Say Yes - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>3:10</v>
+        <v>2:50</v>
       </c>
       <c r="H46" t="str">
-        <v>Camper</v>
+        <v>Marques Anthony</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/camper/1514886616</v>
+        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
+        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
       </c>
       <c r="L46" t="str">
-        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
+        <v>Say Yes - Marques Anthony</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Ojalá</v>
+        <v>LOVE ME (feat. Stevie Wonder)</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
+        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-27</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Ojalá - Single</v>
+        <v>CAMPILATION</v>
       </c>
       <c r="G47" t="str">
-        <v>4:11</v>
+        <v>3:10</v>
       </c>
       <c r="H47" t="str">
-        <v>Lunay</v>
+        <v>Camper</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/lunay/938127685</v>
+        <v>https://music.apple.com/us/artist/camper/1514886616</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
+        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
       </c>
       <c r="L47" t="str">
-        <v>Ojalá - Lunay</v>
+        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>UP TO MY NECK IN U</v>
+        <v>Ojalá</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
+        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-27</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>UP TO MY NECK IN U - Single</v>
+        <v>Ojalá - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>2:17</v>
+        <v>4:11</v>
       </c>
       <c r="H48" t="str">
-        <v>Ledbyher</v>
+        <v>Lunay</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/lunay/938127685</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
+        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
       </c>
       <c r="L48" t="str">
-        <v>UP TO MY NECK IN U - Ledbyher</v>
+        <v>Ojalá - Lunay</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Wallflower</v>
+        <v>UP TO MY NECK IN U</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
+        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-27</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Wallflower - Single</v>
+        <v>UP TO MY NECK IN U - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>3:25</v>
+        <v>2:17</v>
       </c>
       <c r="H49" t="str">
-        <v>Sikarus</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
+        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
       </c>
       <c r="L49" t="str">
-        <v>Wallflower - Sikarus</v>
+        <v>UP TO MY NECK IN U - Ledbyher</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>You Phase</v>
+        <v>Wallflower</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
+        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-27</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>You Phase - Single</v>
+        <v>Wallflower - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>2:51</v>
+        <v>3:25</v>
       </c>
       <c r="H50" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Sikarus</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
+        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
+        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
       </c>
       <c r="L50" t="str">
-        <v>You Phase - Mitchell Tenpenny</v>
+        <v>Wallflower - Sikarus</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Miss Independent</v>
+        <v>You Phase</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
+        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-27</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Miss Independent - Single</v>
+        <v>You Phase - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>2:40</v>
+        <v>2:51</v>
       </c>
       <c r="H51" t="str">
-        <v>1Ski OG</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
+        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
       </c>
       <c r="L51" t="str">
-        <v>Miss Independent - 1Ski OG</v>
+        <v>You Phase - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
+        <v>Miss Independent</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
+        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-27</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>Miss Independent - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>5:47</v>
+        <v>2:40</v>
       </c>
       <c r="H52" t="str">
-        <v>Elevation Worship</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
       </c>
       <c r="L52" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
+        <v>Miss Independent - 1Ski OG</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>go again</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/go-again/1868987466</v>
+        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-27</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>go again - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G53" t="str">
-        <v>2:07</v>
+        <v>5:47</v>
       </c>
       <c r="H53" t="str">
-        <v>NateTaylorr</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/go-again/1868987193</v>
+        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
       </c>
       <c r="L53" t="str">
-        <v>go again - NateTaylorr</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Autopilot</v>
+        <v>go again</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
+        <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-27</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Autopilot</v>
+        <v>go again - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>2:46</v>
+        <v>2:07</v>
       </c>
       <c r="H54" t="str">
-        <v>ALEXSUCKS</v>
+        <v>NateTaylorr</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
+        <v>https://music.apple.com/us/album/go-again/1868987193</v>
       </c>
       <c r="L54" t="str">
-        <v>Autopilot - ALEXSUCKS</v>
+        <v>go again - NateTaylorr</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates)</v>
+        <v>Autopilot</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
+        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-27</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Portrait of My Heart - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G55" t="str">
-        <v>3:04</v>
+        <v>2:46</v>
       </c>
       <c r="H55" t="str">
-        <v>SPELLLING</v>
+        <v>ALEXSUCKS</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
+        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
       </c>
       <c r="L55" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
+        <v>Autopilot - ALEXSUCKS</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>In Violet</v>
+        <v>Portrait of My Heart (feat. Brendan Yates)</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
+        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-27</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Death in the Business of Whaling</v>
+        <v>Portrait of My Heart - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>4:09</v>
+        <v>3:04</v>
       </c>
       <c r="H56" t="str">
-        <v>Searows</v>
+        <v>SPELLLING</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/searows/1607240507</v>
+        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
+        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
       </c>
       <c r="L56" t="str">
-        <v>In Violet - Searows</v>
+        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Baby Run</v>
+        <v>In Violet</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
+        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-27</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Baby Run - Single</v>
+        <v>Death in the Business of Whaling</v>
       </c>
       <c r="G57" t="str">
-        <v>4:47</v>
+        <v>4:09</v>
       </c>
       <c r="H57" t="str">
-        <v>Jimi Jules</v>
+        <v>Searows</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
+        <v>https://music.apple.com/us/artist/searows/1607240507</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
+        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
       </c>
       <c r="L57" t="str">
-        <v>Baby Run - Jimi Jules</v>
+        <v>In Violet - Searows</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>What If We Don't</v>
+        <v>Baby Run</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
+        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-27</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>What If We Don't - Single</v>
+        <v>Baby Run - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:06</v>
+        <v>4:47</v>
       </c>
       <c r="H58" t="str">
-        <v>Ashley McBryde</v>
+        <v>Jimi Jules</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
+        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
       </c>
       <c r="L58" t="str">
-        <v>What If We Don't - Ashley McBryde</v>
+        <v>Baby Run - Jimi Jules</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Hagamos Que</v>
+        <v>What If We Don't</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
+        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-27</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Hagamos Que - Single</v>
+        <v>What If We Don't - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>2:58</v>
+        <v>3:06</v>
       </c>
       <c r="H59" t="str">
-        <v>Juanes</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
+        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
       </c>
       <c r="L59" t="str">
-        <v>Hagamos Que - Juanes</v>
+        <v>What If We Don't - Ashley McBryde</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>World Change Me</v>
+        <v>Hagamos Que</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
+        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-27</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>World Change Me - Single</v>
+        <v>Hagamos Que - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>3:03</v>
+        <v>2:58</v>
       </c>
       <c r="H60" t="str">
-        <v>Max McNown</v>
+        <v>Juanes</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
+        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
       </c>
       <c r="L60" t="str">
-        <v>World Change Me - Max McNown</v>
+        <v>Hagamos Que - Juanes</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Exclusive</v>
+        <v>World Change Me</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
+        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-27</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Exclusive - EP</v>
+        <v>World Change Me - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>3:20</v>
+        <v>3:03</v>
       </c>
       <c r="H61" t="str">
-        <v>Hudson Westbrook</v>
+        <v>Max McNown</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
+        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
       </c>
       <c r="L61" t="str">
-        <v>Exclusive - Hudson Westbrook</v>
+        <v>World Change Me - Max McNown</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Say Less</v>
+        <v>Exclusive</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/say-less/1867910122</v>
+        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-27</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Say Less - Single</v>
+        <v>Exclusive - EP</v>
       </c>
       <c r="G62" t="str">
-        <v>2:18</v>
+        <v>3:20</v>
       </c>
       <c r="H62" t="str">
-        <v>JYT</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/say-less/1867910115</v>
+        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
       </c>
       <c r="L62" t="str">
-        <v>Say Less - JYT</v>
+        <v>Exclusive - Hudson Westbrook</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Angels Cry</v>
+        <v>Say Less</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
+        <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-27</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>X's for Eyes (Deluxe)</v>
+        <v>Say Less - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>3:52</v>
+        <v>2:18</v>
       </c>
       <c r="H63" t="str">
-        <v>The Red Jumpsuit Apparatus</v>
+        <v>JYT</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
+        <v>https://music.apple.com/us/album/say-less/1867910115</v>
       </c>
       <c r="L63" t="str">
-        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
+        <v>Say Less - JYT</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Over You</v>
+        <v>Angels Cry</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/over-you/1846189473</v>
+        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-27</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>A Love For Strangers</v>
+        <v>X's for Eyes (Deluxe)</v>
       </c>
       <c r="G64" t="str">
-        <v>4:44</v>
+        <v>3:52</v>
       </c>
       <c r="H64" t="str">
-        <v>Chet Faker</v>
+        <v>The Red Jumpsuit Apparatus</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/over-you/1846189472</v>
+        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
       </c>
       <c r="L64" t="str">
-        <v>Over You - Chet Faker</v>
+        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Chala (My Soul Is on a Loop)</v>
+        <v>Over You</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
+        <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-27</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Chala (My Soul Is on a Loop) - Single</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G65" t="str">
-        <v>2:42</v>
+        <v>4:44</v>
       </c>
       <c r="H65" t="str">
-        <v>Barry Can't Swim</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
+        <v>https://music.apple.com/us/album/over-you/1846189472</v>
       </c>
       <c r="L65" t="str">
-        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
+        <v>Over You - Chet Faker</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>starlight feat. Madeline Follin</v>
+        <v>Chala (My Soul Is on a Loop)</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
+        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-27</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>starlight feat. Madeline Follin - Single</v>
+        <v>Chala (My Soul Is on a Loop) - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>3:06</v>
+        <v>2:42</v>
       </c>
       <c r="H66" t="str">
-        <v>Disco Lines</v>
+        <v>Barry Can't Swim</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
+        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
+        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
       </c>
       <c r="L66" t="str">
-        <v>starlight feat. Madeline Follin - Disco Lines</v>
+        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Locked In (feat. Trippie Redd)</v>
+        <v>starlight feat. Madeline Follin</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
+        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-27</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Locked In (feat. Trippie Redd) - Single</v>
+        <v>starlight feat. Madeline Follin - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>2:48</v>
+        <v>3:06</v>
       </c>
       <c r="H67" t="str">
-        <v>David Guetta</v>
+        <v>Disco Lines</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
+        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
+        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
       </c>
       <c r="L67" t="str">
-        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
+        <v>starlight feat. Madeline Follin - Disco Lines</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Rejoice</v>
+        <v>Locked In (feat. Trippie Redd)</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
+        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-27</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Rejoice - Single</v>
+        <v>Locked In (feat. Trippie Redd) - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>4:20</v>
+        <v>2:48</v>
       </c>
       <c r="H68" t="str">
-        <v>Def Leppard</v>
+        <v>David Guetta</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
+        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
+        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
       </c>
       <c r="L68" t="str">
-        <v>Rejoice - Def Leppard</v>
+        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
+        <v>Rejoice</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
+        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-27</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
+        <v>Rejoice - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>2:58</v>
+        <v>4:20</v>
       </c>
       <c r="H69" t="str">
-        <v>Honey Dijon</v>
+        <v>Def Leppard</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
+        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
       </c>
       <c r="L69" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
+        <v>Rejoice - Def Leppard</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Odisea</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/odisea/1866927906</v>
+        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-27</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Odisea - Single</v>
+        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>3:56</v>
+        <v>2:58</v>
       </c>
       <c r="H70" t="str">
-        <v>BASSYY</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/odisea/1866927904</v>
+        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
       </c>
       <c r="L70" t="str">
-        <v>Odisea - BASSYY</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Lucky Day</v>
+        <v>Odisea</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
+        <v>https://music.apple.com/us/song/odisea/1866927906</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-27</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Speed Kills</v>
+        <v>Odisea - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>3:13</v>
+        <v>3:56</v>
       </c>
       <c r="H71" t="str">
-        <v>Ally Evenson</v>
+        <v>BASSYY</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
+        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
+        <v>https://music.apple.com/us/album/odisea/1866927904</v>
       </c>
       <c r="L71" t="str">
-        <v>Lucky Day - Ally Evenson</v>
+        <v>Odisea - BASSYY</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Breathe On It</v>
+        <v>Lucky Day</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
+        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-27</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Breathe On It - Single</v>
+        <v>Speed Kills</v>
       </c>
       <c r="G72" t="str">
-        <v>4:00</v>
+        <v>3:13</v>
       </c>
       <c r="H72" t="str">
-        <v>Tauren Wells</v>
+        <v>Ally Evenson</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
+        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
       </c>
       <c r="L72" t="str">
-        <v>Breathe On It - Tauren Wells</v>
+        <v>Lucky Day - Ally Evenson</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Easy</v>
+        <v>Breathe On It</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/easy/1863456906</v>
+        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-27</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Easy - Single</v>
+        <v>Breathe On It - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>4:30</v>
+        <v>4:00</v>
       </c>
       <c r="H73" t="str">
-        <v>lydi lynn</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/easy/1863456903</v>
+        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
       </c>
       <c r="L73" t="str">
-        <v>Easy - lydi lynn</v>
+        <v>Breathe On It - Tauren Wells</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Break Me In</v>
+        <v>Easy</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
+        <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-27</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Break Me In - Single</v>
+        <v>Easy - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>2:52</v>
+        <v>4:30</v>
       </c>
       <c r="H74" t="str">
-        <v>Joyce Wrice</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
+        <v>https://music.apple.com/us/album/easy/1863456903</v>
       </c>
       <c r="L74" t="str">
-        <v>Break Me In - Joyce Wrice</v>
+        <v>Easy - lydi lynn</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Long Live Love</v>
+        <v>Break Me In</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
+        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-27</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Long Live Love - Single</v>
+        <v>Break Me In - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>2:36</v>
+        <v>2:52</v>
       </c>
       <c r="H75" t="str">
-        <v>Sugar</v>
+        <v>Joyce Wrice</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/sugar/530175867</v>
+        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
+        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
       </c>
       <c r="L75" t="str">
-        <v>Long Live Love - Sugar</v>
+        <v>Break Me In - Joyce Wrice</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Depressed</v>
+        <v>Long Live Love</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/depressed/1840400522</v>
+        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-27</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Boycott Heaven</v>
+        <v>Long Live Love - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>3:32</v>
+        <v>2:36</v>
       </c>
       <c r="H76" t="str">
-        <v>The Format</v>
+        <v>Sugar</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/the-format/3064903</v>
+        <v>https://music.apple.com/us/artist/sugar/530175867</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/depressed/1840399886</v>
+        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
       </c>
       <c r="L76" t="str">
-        <v>Depressed - The Format</v>
+        <v>Long Live Love - Sugar</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Empty Hands</v>
+        <v>Depressed</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
+        <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-27</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Empty Hands</v>
+        <v>Boycott Heaven</v>
       </c>
       <c r="G77" t="str">
-        <v>3:09</v>
+        <v>3:32</v>
       </c>
       <c r="H77" t="str">
-        <v>Poppy</v>
+        <v>The Format</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
+        <v>https://music.apple.com/us/artist/the-format/3064903</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
+        <v>https://music.apple.com/us/album/depressed/1840399886</v>
       </c>
       <c r="L77" t="str">
-        <v>Empty Hands - Poppy</v>
+        <v>Depressed - The Format</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>The Long Surrender</v>
+        <v>Empty Hands</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
+        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-27</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>The Long Surrender</v>
+        <v>Empty Hands</v>
       </c>
       <c r="G78" t="str">
-        <v>3:45</v>
+        <v>3:09</v>
       </c>
       <c r="H78" t="str">
-        <v>NEEDTOBREATHE</v>
+        <v>Poppy</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
+        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
+        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
       </c>
       <c r="L78" t="str">
-        <v>The Long Surrender - NEEDTOBREATHE</v>
+        <v>Empty Hands - Poppy</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Angela</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/angela/1866624257</v>
+        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-27</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Angela - Single</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="G79" t="str">
-        <v>3:32</v>
+        <v>3:45</v>
       </c>
       <c r="H79" t="str">
-        <v>Hayden Everett</v>
+        <v>NEEDTOBREATHE</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/angela/1866624256</v>
+        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
       </c>
       <c r="L79" t="str">
-        <v>Angela - Hayden Everett</v>
+        <v>The Long Surrender - NEEDTOBREATHE</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Disappear</v>
+        <v>Angela</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/disappear/1847663553</v>
+        <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-27</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Greyhound</v>
+        <v>Angela - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:31</v>
+        <v>3:32</v>
       </c>
       <c r="H80" t="str">
-        <v>Katie Tupper</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/disappear/1847663546</v>
+        <v>https://music.apple.com/us/album/angela/1866624256</v>
       </c>
       <c r="L80" t="str">
-        <v>Disappear - Katie Tupper</v>
+        <v>Angela - Hayden Everett</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Catapult</v>
+        <v>Disappear</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/catapult/1862951335</v>
+        <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-27</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Catapult - Single</v>
+        <v>Greyhound</v>
       </c>
       <c r="G81" t="str">
-        <v>2:57</v>
+        <v>3:31</v>
       </c>
       <c r="H81" t="str">
-        <v>Cape Francis</v>
+        <v>Katie Tupper</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
+        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/catapult/1862951333</v>
+        <v>https://music.apple.com/us/album/disappear/1847663546</v>
       </c>
       <c r="L81" t="str">
-        <v>Catapult - Cape Francis</v>
+        <v>Disappear - Katie Tupper</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Think Twice</v>
+        <v>Catapult</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
+        <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-27</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Think Twice - Single</v>
+        <v>Catapult - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>2:22</v>
+        <v>2:57</v>
       </c>
       <c r="H82" t="str">
-        <v>Leonie Biney</v>
+        <v>Cape Francis</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
+        <v>https://music.apple.com/us/album/catapult/1862951333</v>
       </c>
       <c r="L82" t="str">
-        <v>Think Twice - Leonie Biney</v>
+        <v>Catapult - Cape Francis</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>LOVESONGS</v>
+        <v>Think Twice</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
+        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-27</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>BEAUTIFUL MADNESS</v>
+        <v>Think Twice - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>3:33</v>
+        <v>2:22</v>
       </c>
       <c r="H83" t="str">
-        <v>Agnes</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/agnes/42568985</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
+        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
       </c>
       <c r="L83" t="str">
-        <v>LOVESONGS - Agnes</v>
+        <v>Think Twice - Leonie Biney</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Down South</v>
+        <v>LOVESONGS</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/down-south/1861010793</v>
+        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-27</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Down South - Single</v>
+        <v>BEAUTIFUL MADNESS</v>
       </c>
       <c r="G84" t="str">
-        <v>2:19</v>
+        <v>3:33</v>
       </c>
       <c r="H84" t="str">
-        <v>Trap Dickey</v>
+        <v>Agnes</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/agnes/42568985</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/down-south/1861010788</v>
+        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
       </c>
       <c r="L84" t="str">
-        <v>Down South - Trap Dickey</v>
+        <v>LOVESONGS - Agnes</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
+        <v>Down South</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
+        <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-27</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
+        <v>Down South - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>2:16</v>
+        <v>2:19</v>
       </c>
       <c r="H85" t="str">
-        <v>SALIMATA</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/salimata/690253822</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
+        <v>https://music.apple.com/us/album/down-south/1861010788</v>
       </c>
       <c r="L85" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
+        <v>Down South - Trap Dickey</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Love Like This</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
+        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-27</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Love Like This - Single</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:30</v>
+        <v>2:16</v>
       </c>
       <c r="H86" t="str">
-        <v>Jacob Banks</v>
+        <v>SALIMATA</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
+        <v>https://music.apple.com/us/artist/salimata/690253822</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
+        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
       </c>
       <c r="L86" t="str">
-        <v>Love Like This - Jacob Banks</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Plan Plan</v>
+        <v>Love Like This</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
+        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-27</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>La Locura, Vol. 1</v>
+        <v>Love Like This - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>3:10</v>
+        <v>3:30</v>
       </c>
       <c r="H87" t="str">
-        <v>Funky</v>
+        <v>Jacob Banks</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/funky/80960663</v>
+        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
+        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
       </c>
       <c r="L87" t="str">
-        <v>Plan Plan - Funky</v>
+        <v>Love Like This - Jacob Banks</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>double edged sword</v>
+        <v>Plan Plan</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
+        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-27</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>double edged sword - Single</v>
+        <v>La Locura, Vol. 1</v>
       </c>
       <c r="G88" t="str">
-        <v>3:28</v>
+        <v>3:10</v>
       </c>
       <c r="H88" t="str">
-        <v>Hailey Picardi</v>
+        <v>Funky</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/funky/80960663</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
+        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
       </c>
       <c r="L88" t="str">
-        <v>double edged sword - Hailey Picardi</v>
+        <v>Plan Plan - Funky</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>SOMEWHERE IN BETWEEN</v>
+        <v>double edged sword</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
+        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-27</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>SOMEWHERE IN BETWEEN - Single</v>
+        <v>double edged sword - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>3:27</v>
+        <v>3:28</v>
       </c>
       <c r="H89" t="str">
-        <v>Matt Hansen</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
+        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
       </c>
       <c r="L89" t="str">
-        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
+        <v>double edged sword - Hailey Picardi</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>The Decay</v>
+        <v>SOMEWHERE IN BETWEEN</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
+        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-27</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>What Remains (Midnight Edition)</v>
+        <v>SOMEWHERE IN BETWEEN - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>3:20</v>
+        <v>3:27</v>
       </c>
       <c r="H90" t="str">
-        <v>Pop Evil</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
+        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
+        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
       </c>
       <c r="L90" t="str">
-        <v>The Decay - Pop Evil</v>
+        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>3111</v>
+        <v>The Decay</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/3111/1862225387</v>
+        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-27</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Goliath</v>
+        <v>What Remains (Midnight Edition)</v>
       </c>
       <c r="G91" t="str">
-        <v>4:08</v>
+        <v>3:20</v>
       </c>
       <c r="H91" t="str">
-        <v>Exodus</v>
+        <v>Pop Evil</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/3111/1862225385</v>
+        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
       </c>
       <c r="L91" t="str">
-        <v>3111 - Exodus</v>
+        <v>The Decay - Pop Evil</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Touch My Love And Die</v>
+        <v>3111</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+        <v>https://music.apple.com/us/song/3111/1862225387</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-27</v>
@@ -3871,68 +3871,106 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Touch My Love And Die - Single</v>
+        <v>Goliath</v>
       </c>
       <c r="G92" t="str">
-        <v>2:57</v>
+        <v>4:08</v>
       </c>
       <c r="H92" t="str">
-        <v>Myrkur</v>
+        <v>Exodus</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+        <v>https://music.apple.com/us/album/3111/1862225385</v>
       </c>
       <c r="L92" t="str">
-        <v>Touch My Love And Die - Myrkur</v>
+        <v>3111 - Exodus</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
+        <v>Touch My Love And Die</v>
+      </c>
+      <c r="B93" t="str">
+        <v/>
+      </c>
+      <c r="C93" t="str">
+        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+      </c>
+      <c r="D93" t="str">
+        <v>2026-01-27</v>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v>Touch My Love And Die - Single</v>
+      </c>
+      <c r="G93" t="str">
+        <v>2:57</v>
+      </c>
+      <c r="H93" t="str">
+        <v>Myrkur</v>
+      </c>
+      <c r="I93" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J93" t="str">
+        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+      </c>
+      <c r="K93" t="str">
+        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+      </c>
+      <c r="L93" t="str">
+        <v>Touch My Love And Die - Myrkur</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
         <v>Bomb To A Knife Fight</v>
       </c>
-      <c r="B93" t="str">
-        <v/>
-      </c>
-      <c r="C93" t="str">
+      <c r="B94" t="str">
+        <v/>
+      </c>
+      <c r="C94" t="str">
         <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
-      <c r="D93" t="str">
-        <v>2026-01-27</v>
-      </c>
-      <c r="E93" t="str">
-        <v/>
-      </c>
-      <c r="F93" t="str">
+      <c r="D94" t="str">
+        <v>2026-01-27</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
         <v>Bomb To A Knife Fight - Single</v>
       </c>
-      <c r="G93" t="str">
+      <c r="G94" t="str">
         <v>2:41</v>
       </c>
-      <c r="H93" t="str">
+      <c r="H94" t="str">
         <v>The Barbarians of California</v>
       </c>
-      <c r="I93" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J93" t="str">
+      <c r="I94" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J94" t="str">
         <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
       </c>
-      <c r="K93" t="str">
+      <c r="K94" t="str">
         <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
       </c>
-      <c r="L93" t="str">
+      <c r="L94" t="str">
         <v>Bomb To A Knife Fight - The Barbarians of California</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L93"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L94"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/aperture/1870984033</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/high-key/1847702418</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/scared/1862292863</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/atm/1871258339</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/dead-end/1862845874</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/bad/1869095326</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/losing-you/1863525495</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/arrhythmia-i-hope-you-stay/1867164656</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/odisea/1866927906</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/3111/1862225387</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E94" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L95"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Aperture</v>
+        <v>For Hire</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/aperture/1870984033</v>
+        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-28</v>
@@ -451,36 +451,36 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>For Hire - Single</v>
       </c>
       <c r="G2" t="str">
-        <v>5:11</v>
+        <v>3:44</v>
       </c>
       <c r="H2" t="str">
-        <v>Harry Styles</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/aperture/1870984032</v>
+        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
       </c>
       <c r="L2" t="str">
-        <v>Aperture - Harry Styles</v>
+        <v>For Hire - People I’ve Met</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Opening Night</v>
+        <v>Aperture</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
+        <v>https://music.apple.com/us/song/aperture/1870984033</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-28</v>
@@ -489,36 +489,36 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>HELP(2)</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G3" t="str">
-        <v>4:19</v>
+        <v>5:11</v>
       </c>
       <c r="H3" t="str">
-        <v>Arctic Monkeys</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
-        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K3" t="str">
-        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
+        <v>https://music.apple.com/us/album/aperture/1870984032</v>
       </c>
       <c r="L3" t="str">
-        <v>Opening Night - Arctic Monkeys</v>
+        <v>Aperture - Harry Styles</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa)</v>
+        <v>Opening Night</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
+        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-28</v>
@@ -527,36 +527,36 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>Don't Be Dumb</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G4" t="str">
-        <v>2:20</v>
+        <v>4:19</v>
       </c>
       <c r="H4" t="str">
-        <v>A$AP Rocky</v>
+        <v>Arctic Monkeys</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
-        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
+        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
       </c>
       <c r="K4" t="str">
-        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
+        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
       </c>
       <c r="L4" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
+        <v>Opening Night - Arctic Monkeys</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CAMBIARÉ</v>
+        <v>FLACKITO JODYE (feat. Tokischa)</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
+        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-28</v>
@@ -565,36 +565,36 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>CAMBIARÉ - Single</v>
+        <v>Don't Be Dumb</v>
       </c>
       <c r="G5" t="str">
-        <v>3:01</v>
+        <v>2:20</v>
       </c>
       <c r="H5" t="str">
-        <v>Luis Fonsi</v>
+        <v>A$AP Rocky</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
+        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
+        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
       </c>
       <c r="L5" t="str">
-        <v>CAMBIARÉ - Luis Fonsi</v>
+        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Last of a Dying Breed</v>
+        <v>CAMBIARÉ</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
+        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-28</v>
@@ -603,36 +603,36 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>Piss In The Wind</v>
+        <v>CAMBIARÉ - Single</v>
       </c>
       <c r="G6" t="str">
-        <v>2:29</v>
+        <v>3:01</v>
       </c>
       <c r="H6" t="str">
-        <v>Joji</v>
+        <v>Luis Fonsi</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
+        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
       </c>
       <c r="L6" t="str">
-        <v>Last of a Dying Breed - Joji</v>
+        <v>CAMBIARÉ - Luis Fonsi</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>High Key</v>
+        <v>Last of a Dying Breed</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/high-key/1847702418</v>
+        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-28</v>
@@ -641,36 +641,36 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>Vacancy</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G7" t="str">
-        <v>2:12</v>
+        <v>2:29</v>
       </c>
       <c r="H7" t="str">
-        <v>Ari Lennox</v>
+        <v>Joji</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
-        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/high-key/1847702412</v>
+        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
       </c>
       <c r="L7" t="str">
-        <v>High Key - Ari Lennox</v>
+        <v>Last of a Dying Breed - Joji</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>scared</v>
+        <v>High Key</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/scared/1862292863</v>
+        <v>https://music.apple.com/us/song/high-key/1847702418</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-28</v>
@@ -679,36 +679,36 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>scared - Single</v>
+        <v>Vacancy</v>
       </c>
       <c r="G8" t="str">
-        <v>3:46</v>
+        <v>2:12</v>
       </c>
       <c r="H8" t="str">
-        <v>Fred again..</v>
+        <v>Ari Lennox</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/scared/1862292862</v>
+        <v>https://music.apple.com/us/album/high-key/1847702412</v>
       </c>
       <c r="L8" t="str">
-        <v>scared - Fred again..</v>
+        <v>High Key - Ari Lennox</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Death of Love</v>
+        <v>scared</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
+        <v>https://music.apple.com/us/song/scared/1862292863</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-28</v>
@@ -717,36 +717,36 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Trying Times</v>
+        <v>scared - Single</v>
       </c>
       <c r="G9" t="str">
-        <v>3:26</v>
+        <v>3:46</v>
       </c>
       <c r="H9" t="str">
-        <v>James Blake</v>
+        <v>Fred again..</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
+        <v>https://music.apple.com/us/album/scared/1862292862</v>
       </c>
       <c r="L9" t="str">
-        <v>Death of Love - James Blake</v>
+        <v>scared - Fred again..</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Big Ole Fancy House</v>
+        <v>Death of Love</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
+        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-28</v>
@@ -755,36 +755,36 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>Trying Times</v>
       </c>
       <c r="G10" t="str">
-        <v>4:03</v>
+        <v>3:26</v>
       </c>
       <c r="H10" t="str">
-        <v>Parker McCollum</v>
+        <v>James Blake</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
+        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
       </c>
       <c r="L10" t="str">
-        <v>Big Ole Fancy House - Parker McCollum</v>
+        <v>Death of Love - James Blake</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ATM</v>
+        <v>Big Ole Fancy House</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/atm/1871258339</v>
+        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-28</v>
@@ -793,36 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>OCTANE</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G11" t="str">
-        <v>3:00</v>
+        <v>4:03</v>
       </c>
       <c r="H11" t="str">
-        <v>Don Toliver</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/atm/1871258329</v>
+        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
       </c>
       <c r="L11" t="str">
-        <v>ATM - Don Toliver</v>
+        <v>Big Ole Fancy House - Parker McCollum</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Flo Jackson</v>
+        <v>ATM</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
+        <v>https://music.apple.com/us/song/atm/1871258339</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-28</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>Flo Jackson - Single</v>
+        <v>OCTANE</v>
       </c>
       <c r="G12" t="str">
-        <v>2:23</v>
+        <v>3:00</v>
       </c>
       <c r="H12" t="str">
-        <v>Flo Milli</v>
+        <v>Don Toliver</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
+        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
+        <v>https://music.apple.com/us/album/atm/1871258329</v>
       </c>
       <c r="L12" t="str">
-        <v>Flo Jackson - Flo Milli</v>
+        <v>ATM - Don Toliver</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Site Unseen (feat. Waxahatchee)</v>
+        <v>Flo Jackson</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
+        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-28</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Creature of Habit</v>
+        <v>Flo Jackson - Single</v>
       </c>
       <c r="G13" t="str">
-        <v>2:46</v>
+        <v>2:23</v>
       </c>
       <c r="H13" t="str">
-        <v>Courtney Barnett</v>
+        <v>Flo Milli</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
+        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
       </c>
       <c r="L13" t="str">
-        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
+        <v>Flo Jackson - Flo Milli</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Puppet Parade</v>
+        <v>Site Unseen (feat. Waxahatchee)</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
+        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-28</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>Megadeth</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G14" t="str">
-        <v>4:40</v>
+        <v>2:46</v>
       </c>
       <c r="H14" t="str">
-        <v>Megadeth</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/megadeth/488289</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
+        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
       </c>
       <c r="L14" t="str">
-        <v>Puppet Parade - Megadeth</v>
+        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>To Love Somebody</v>
+        <v>Puppet Parade</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
+        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-28</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Cruel World</v>
+        <v>Megadeth</v>
       </c>
       <c r="G15" t="str">
-        <v>3:57</v>
+        <v>4:40</v>
       </c>
       <c r="H15" t="str">
-        <v>Holly Humberstone</v>
+        <v>Megadeth</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/megadeth/488289</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
+        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
       </c>
       <c r="L15" t="str">
-        <v>To Love Somebody - Holly Humberstone</v>
+        <v>Puppet Parade - Megadeth</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Nothing Is Impossible With You</v>
+        <v>To Love Somebody</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
+        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-28</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Nothing Is Impossible With You - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G16" t="str">
-        <v>4:14</v>
+        <v>3:57</v>
       </c>
       <c r="H16" t="str">
-        <v>Cleo Sol</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
+        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
       </c>
       <c r="L16" t="str">
-        <v>Nothing Is Impossible With You - Cleo Sol</v>
+        <v>To Love Somebody - Holly Humberstone</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>HYPNOTIZE</v>
+        <v>Nothing Is Impossible With You</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
+        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-28</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>THE CORE - 核</v>
+        <v>Nothing Is Impossible With You - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>2:50</v>
+        <v>4:14</v>
       </c>
       <c r="H17" t="str">
-        <v>XG</v>
+        <v>Cleo Sol</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/xg/1609409493</v>
+        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
+        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
       </c>
       <c r="L17" t="str">
-        <v>HYPNOTIZE - XG</v>
+        <v>Nothing Is Impossible With You - Cleo Sol</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Dead End</v>
+        <v>HYPNOTIZE</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
+        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-28</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Ricochet</v>
+        <v>THE CORE - 核</v>
       </c>
       <c r="G18" t="str">
-        <v>4:05</v>
+        <v>2:50</v>
       </c>
       <c r="H18" t="str">
-        <v>Snail Mail</v>
+        <v>XG</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/xg/1609409493</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
+        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
       </c>
       <c r="L18" t="str">
-        <v>Dead End - Snail Mail</v>
+        <v>HYPNOTIZE - XG</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Do I Wanna Know?</v>
+        <v>Dead End</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
+        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-28</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Do I Wanna Know? - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G19" t="str">
-        <v>3:52</v>
+        <v>4:05</v>
       </c>
       <c r="H19" t="str">
-        <v>Dove Cameron</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
+        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
       </c>
       <c r="L19" t="str">
-        <v>Do I Wanna Know? - Dove Cameron</v>
+        <v>Dead End - Snail Mail</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Una y Otra Vez</v>
+        <v>Do I Wanna Know?</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
+        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-28</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>Do I Wanna Know? - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>3:02</v>
+        <v>3:52</v>
       </c>
       <c r="H20" t="str">
-        <v>Kenia Os</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
+        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
       </c>
       <c r="L20" t="str">
-        <v>Una y Otra Vez - Kenia Os</v>
+        <v>Do I Wanna Know? - Dove Cameron</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>BAD</v>
+        <v>Una y Otra Vez</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/bad/1869095326</v>
+        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-28</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>BAD - Single</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G21" t="str">
-        <v>2:15</v>
+        <v>3:02</v>
       </c>
       <c r="H21" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/bad/1869095325</v>
+        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
       </c>
       <c r="L21" t="str">
-        <v>BAD - Chelsea Cutler</v>
+        <v>Una y Otra Vez - Kenia Os</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Losing You</v>
+        <v>BAD</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
+        <v>https://music.apple.com/us/song/bad/1869095326</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-28</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>F.I.G</v>
+        <v>BAD - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>2:22</v>
+        <v>2:15</v>
       </c>
       <c r="H22" t="str">
-        <v>Naomi Scott</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
+        <v>https://music.apple.com/us/album/bad/1869095325</v>
       </c>
       <c r="L22" t="str">
-        <v>Losing You - Naomi Scott</v>
+        <v>BAD - Chelsea Cutler</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Arrhythmia (I Hope You Stay)</v>
+        <v>Losing You</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/arrhythmia-i-hope-you-stay/1867164656</v>
+        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-28</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Arrhythmia (I Hope You Stay) - Single</v>
+        <v>F.I.G</v>
       </c>
       <c r="G23" t="str">
-        <v>3:02</v>
+        <v>2:22</v>
       </c>
       <c r="H23" t="str">
-        <v>The Runarounds</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/the-runarounds/1660817420</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/arrhythmia-i-hope-you-stay/1867164652</v>
+        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
       </c>
       <c r="L23" t="str">
-        <v>Arrhythmia (I Hope You Stay) - The Runarounds</v>
+        <v>Losing You - Naomi Scott</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Me Voy A La C******a</v>
+        <v>Arrhythmia (I Hope You Stay)</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
+        <v>https://music.apple.com/us/song/arrhythmia-i-hope-you-stay/1867164656</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-28</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Infinito</v>
+        <v>Arrhythmia (I Hope You Stay) - Single</v>
       </c>
       <c r="G24" t="str">
-        <v>2:14</v>
+        <v>3:02</v>
       </c>
       <c r="H24" t="str">
-        <v>Yandel</v>
+        <v>The Runarounds</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/yandel/72929426</v>
+        <v>https://music.apple.com/us/artist/the-runarounds/1660817420</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
+        <v>https://music.apple.com/us/album/arrhythmia-i-hope-you-stay/1867164652</v>
       </c>
       <c r="L24" t="str">
-        <v>Me Voy A La C******a - Yandel</v>
+        <v>Arrhythmia (I Hope You Stay) - The Runarounds</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Sexy For Me</v>
+        <v>Me Voy A La C******a</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
+        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-28</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>The Last Dance (Part 1)</v>
+        <v>Infinito</v>
       </c>
       <c r="G25" t="str">
-        <v>2:08</v>
+        <v>2:14</v>
       </c>
       <c r="H25" t="str">
-        <v>Jason Derulo</v>
+        <v>Yandel</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
+        <v>https://music.apple.com/us/artist/yandel/72929426</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
+        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
       </c>
       <c r="L25" t="str">
-        <v>Sexy For Me - Jason Derulo</v>
+        <v>Me Voy A La C******a - Yandel</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Turbulence</v>
+        <v>Sexy For Me</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
+        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-28</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>REAL, Vol. 1 - EP</v>
+        <v>The Last Dance (Part 1)</v>
       </c>
       <c r="G26" t="str">
-        <v>2:25</v>
+        <v>2:08</v>
       </c>
       <c r="H26" t="str">
-        <v>Wizkid</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
+        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
+        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
       </c>
       <c r="L26" t="str">
-        <v>Turbulence - Wizkid</v>
+        <v>Sexy For Me - Jason Derulo</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>I’m Good (From The Movie “GOAT”)</v>
+        <v>Turbulence</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
+        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-28</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>REAL, Vol. 1 - EP</v>
       </c>
       <c r="G27" t="str">
-        <v>2:59</v>
+        <v>2:25</v>
       </c>
       <c r="H27" t="str">
-        <v>Jelly Roll</v>
+        <v>Wizkid</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
       </c>
       <c r="L27" t="str">
-        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
+        <v>Turbulence - Wizkid</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
+        <v>I’m Good (From The Movie “GOAT”)</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
+        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-28</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G28" t="str">
-        <v>3:47</v>
+        <v>2:59</v>
       </c>
       <c r="H28" t="str">
-        <v>Dolly Parton</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
+        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L28" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
+        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ESCONDIDAS</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
+        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-28</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>SILENCIO HABLA</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>2:53</v>
+        <v>3:47</v>
       </c>
       <c r="H29" t="str">
-        <v>Oscar Ortiz</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
+        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
+        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
       </c>
       <c r="L29" t="str">
-        <v>ESCONDIDAS - Oscar Ortiz</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Alabama Beauty Queen</v>
+        <v>ESCONDIDAS</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
+        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-28</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Act I</v>
+        <v>SILENCIO HABLA</v>
       </c>
       <c r="G30" t="str">
-        <v>3:43</v>
+        <v>2:53</v>
       </c>
       <c r="H30" t="str">
-        <v>Kashus Culpepper</v>
+        <v>Oscar Ortiz</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
+        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
+        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
       </c>
       <c r="L30" t="str">
-        <v>Alabama Beauty Queen - Kashus Culpepper</v>
+        <v>ESCONDIDAS - Oscar Ortiz</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Imposter</v>
+        <v>Alabama Beauty Queen</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/imposter/1842408050</v>
+        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-28</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>How Did I Get Here?</v>
+        <v>Act I</v>
       </c>
       <c r="G31" t="str">
-        <v>2:38</v>
+        <v>3:43</v>
       </c>
       <c r="H31" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Kashus Culpepper</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/imposter/1842408037</v>
+        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
       </c>
       <c r="L31" t="str">
-        <v>Imposter - Louis Tomlinson</v>
+        <v>Alabama Beauty Queen - Kashus Culpepper</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Puddles (Zero 7 Remix)</v>
+        <v>Imposter</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
+        <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-28</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Puddles (Zero 7 Remix) - Single</v>
+        <v>How Did I Get Here?</v>
       </c>
       <c r="G32" t="str">
-        <v>6:01</v>
+        <v>2:38</v>
       </c>
       <c r="H32" t="str">
-        <v>Not for Radio</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
+        <v>https://music.apple.com/us/album/imposter/1842408037</v>
       </c>
       <c r="L32" t="str">
-        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
+        <v>Imposter - Louis Tomlinson</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Little Miss (Misdemeanor)</v>
+        <v>Puddles (Zero 7 Remix)</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
+        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-28</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Little Miss (Misdemeanor) - Single</v>
+        <v>Puddles (Zero 7 Remix) - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>2:24</v>
+        <v>6:01</v>
       </c>
       <c r="H33" t="str">
-        <v>GIRLSET</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
+        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
       </c>
       <c r="L33" t="str">
-        <v>Little Miss (Misdemeanor) - GIRLSET</v>
+        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>I Could Get Used To This</v>
+        <v>Little Miss (Misdemeanor)</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
+        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-28</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>I Could Get Used To This - Single</v>
+        <v>Little Miss (Misdemeanor) - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>3:41</v>
+        <v>2:24</v>
       </c>
       <c r="H34" t="str">
-        <v>Jessie Ware</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
+        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
       </c>
       <c r="L34" t="str">
-        <v>I Could Get Used To This - Jessie Ware</v>
+        <v>Little Miss (Misdemeanor) - GIRLSET</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>LA VILLA</v>
+        <v>I Could Get Used To This</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
+        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-28</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>HOPI SENDÉ</v>
+        <v>I Could Get Used To This - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>3:12</v>
+        <v>3:41</v>
       </c>
       <c r="H35" t="str">
-        <v>Ryan Castro</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
+        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
       </c>
       <c r="L35" t="str">
-        <v>LA VILLA - Ryan Castro</v>
+        <v>I Could Get Used To This - Jessie Ware</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
+        <v>LA VILLA</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
+        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-28</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>HOPI SENDÉ</v>
       </c>
       <c r="G36" t="str">
-        <v>3:27</v>
+        <v>3:12</v>
       </c>
       <c r="H36" t="str">
-        <v>Denzel Curry</v>
+        <v>Ryan Castro</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
+        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
       </c>
       <c r="L36" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
+        <v>LA VILLA - Ryan Castro</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Thick One</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
+        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-28</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Part 3</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G37" t="str">
-        <v>2:49</v>
+        <v>3:27</v>
       </c>
       <c r="H37" t="str">
-        <v>42 Dugg</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
+        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
       </c>
       <c r="L37" t="str">
-        <v>Thick One - 42 Dugg</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>How Much Did You Get For Your Soul</v>
+        <v>Thick One</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
+        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-28</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>World's Gone Wrong</v>
+        <v>Part 3</v>
       </c>
       <c r="G38" t="str">
-        <v>3:59</v>
+        <v>2:49</v>
       </c>
       <c r="H38" t="str">
-        <v>Lucinda Williams</v>
+        <v>42 Dugg</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
+        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
+        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
       </c>
       <c r="L38" t="str">
-        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
+        <v>Thick One - 42 Dugg</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>THUM</v>
+        <v>How Much Did You Get For Your Soul</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/thum/1863009362</v>
+        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-28</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>THUM - Single</v>
+        <v>World's Gone Wrong</v>
       </c>
       <c r="G39" t="str">
-        <v>2:11</v>
+        <v>3:59</v>
       </c>
       <c r="H39" t="str">
-        <v>Violet Grohl</v>
+        <v>Lucinda Williams</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/thum/1863009357</v>
+        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
       </c>
       <c r="L39" t="str">
-        <v>THUM - Violet Grohl</v>
+        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>(I'm a) Rock "N" Roller</v>
+        <v>THUM</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
+        <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-28</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>The Great Satan</v>
+        <v>THUM - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>3:32</v>
+        <v>2:11</v>
       </c>
       <c r="H40" t="str">
-        <v>Rob Zombie</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
+        <v>https://music.apple.com/us/album/thum/1863009357</v>
       </c>
       <c r="L40" t="str">
-        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
+        <v>THUM - Violet Grohl</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Excuses For Love</v>
+        <v>(I'm a) Rock "N" Roller</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
+        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-28</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Hyperlove</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G41" t="str">
-        <v>3:04</v>
+        <v>3:32</v>
       </c>
       <c r="H41" t="str">
-        <v>MIKA</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/mika/184932871</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
+        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
       </c>
       <c r="L41" t="str">
-        <v>Excuses For Love - MIKA</v>
+        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>3 Tears</v>
+        <v>Excuses For Love</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
+        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-28</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>3 Tears - Single</v>
+        <v>Hyperlove</v>
       </c>
       <c r="G42" t="str">
-        <v>2:50</v>
+        <v>3:04</v>
       </c>
       <c r="H42" t="str">
-        <v>Mergui</v>
+        <v>MIKA</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
+        <v>https://music.apple.com/us/artist/mika/184932871</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
+        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
       </c>
       <c r="L42" t="str">
-        <v>3 Tears - Mergui</v>
+        <v>Excuses For Love - MIKA</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Church Girl</v>
+        <v>3 Tears</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
+        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-28</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Church Girl - Single</v>
+        <v>3 Tears - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>3:19</v>
+        <v>2:50</v>
       </c>
       <c r="H43" t="str">
-        <v>Carly Pearce</v>
+        <v>Mergui</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
+        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
       </c>
       <c r="L43" t="str">
-        <v>Church Girl - Carly Pearce</v>
+        <v>3 Tears - Mergui</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Funeral</v>
+        <v>Church Girl</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/funeral/1867616928</v>
+        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-28</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>The Weight of the Woods</v>
+        <v>Church Girl - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>4:03</v>
+        <v>3:19</v>
       </c>
       <c r="H44" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/funeral/1867616617</v>
+        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
       </c>
       <c r="L44" t="str">
-        <v>Funeral - Dermot Kennedy</v>
+        <v>Church Girl - Carly Pearce</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>dust to dust</v>
+        <v>Funeral</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
+        <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-28</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Rivers of Sugar and Blood - EP</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G45" t="str">
-        <v>3:51</v>
+        <v>4:03</v>
       </c>
       <c r="H45" t="str">
-        <v>Truman Sinclair</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/truman-sinclair/1483104826</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/dust-to-dust/1869116937</v>
+        <v>https://music.apple.com/us/album/funeral/1867616617</v>
       </c>
       <c r="L45" t="str">
-        <v>dust to dust - Truman Sinclair</v>
+        <v>Funeral - Dermot Kennedy</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Say Yes</v>
+        <v>dust to dust</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
+        <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-28</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Say Yes - Single</v>
+        <v>Rivers of Sugar and Blood - EP</v>
       </c>
       <c r="G46" t="str">
-        <v>2:50</v>
+        <v>3:51</v>
       </c>
       <c r="H46" t="str">
-        <v>Marques Anthony</v>
+        <v>Truman Sinclair</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
+        <v>https://music.apple.com/us/artist/truman-sinclair/1483104826</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
+        <v>https://music.apple.com/us/album/dust-to-dust/1869116937</v>
       </c>
       <c r="L46" t="str">
-        <v>Say Yes - Marques Anthony</v>
+        <v>dust to dust - Truman Sinclair</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>LOVE ME (feat. Stevie Wonder)</v>
+        <v>Say Yes</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
+        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-28</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>CAMPILATION</v>
+        <v>Say Yes - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>3:10</v>
+        <v>2:50</v>
       </c>
       <c r="H47" t="str">
-        <v>Camper</v>
+        <v>Marques Anthony</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/camper/1514886616</v>
+        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
+        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
       </c>
       <c r="L47" t="str">
-        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
+        <v>Say Yes - Marques Anthony</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Ojalá</v>
+        <v>LOVE ME (feat. Stevie Wonder)</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
+        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-28</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Ojalá - Single</v>
+        <v>CAMPILATION</v>
       </c>
       <c r="G48" t="str">
-        <v>4:11</v>
+        <v>3:10</v>
       </c>
       <c r="H48" t="str">
-        <v>Lunay</v>
+        <v>Camper</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/lunay/938127685</v>
+        <v>https://music.apple.com/us/artist/camper/1514886616</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
+        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
       </c>
       <c r="L48" t="str">
-        <v>Ojalá - Lunay</v>
+        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>UP TO MY NECK IN U</v>
+        <v>Ojalá</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
+        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-28</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>UP TO MY NECK IN U - Single</v>
+        <v>Ojalá - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>2:17</v>
+        <v>4:11</v>
       </c>
       <c r="H49" t="str">
-        <v>Ledbyher</v>
+        <v>Lunay</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/lunay/938127685</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
+        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
       </c>
       <c r="L49" t="str">
-        <v>UP TO MY NECK IN U - Ledbyher</v>
+        <v>Ojalá - Lunay</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Wallflower</v>
+        <v>UP TO MY NECK IN U</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
+        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-28</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Wallflower - Single</v>
+        <v>UP TO MY NECK IN U - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>3:25</v>
+        <v>2:17</v>
       </c>
       <c r="H50" t="str">
-        <v>Sikarus</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
+        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
       </c>
       <c r="L50" t="str">
-        <v>Wallflower - Sikarus</v>
+        <v>UP TO MY NECK IN U - Ledbyher</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>You Phase</v>
+        <v>Wallflower</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
+        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-28</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>You Phase - Single</v>
+        <v>Wallflower - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>2:51</v>
+        <v>3:25</v>
       </c>
       <c r="H51" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Sikarus</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
+        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
+        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
       </c>
       <c r="L51" t="str">
-        <v>You Phase - Mitchell Tenpenny</v>
+        <v>Wallflower - Sikarus</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Miss Independent</v>
+        <v>You Phase</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
+        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-28</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Miss Independent - Single</v>
+        <v>You Phase - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>2:40</v>
+        <v>2:51</v>
       </c>
       <c r="H52" t="str">
-        <v>1Ski OG</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
+        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
       </c>
       <c r="L52" t="str">
-        <v>Miss Independent - 1Ski OG</v>
+        <v>You Phase - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
+        <v>Miss Independent</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
+        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-28</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>Miss Independent - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>5:47</v>
+        <v>2:40</v>
       </c>
       <c r="H53" t="str">
-        <v>Elevation Worship</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
       </c>
       <c r="L53" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
+        <v>Miss Independent - 1Ski OG</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>go again</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/go-again/1868987466</v>
+        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-28</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>go again - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G54" t="str">
-        <v>2:07</v>
+        <v>5:47</v>
       </c>
       <c r="H54" t="str">
-        <v>NateTaylorr</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/go-again/1868987193</v>
+        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
       </c>
       <c r="L54" t="str">
-        <v>go again - NateTaylorr</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Autopilot</v>
+        <v>go again</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
+        <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-28</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Autopilot</v>
+        <v>go again - Single</v>
       </c>
       <c r="G55" t="str">
-        <v>2:46</v>
+        <v>2:07</v>
       </c>
       <c r="H55" t="str">
-        <v>ALEXSUCKS</v>
+        <v>NateTaylorr</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
+        <v>https://music.apple.com/us/album/go-again/1868987193</v>
       </c>
       <c r="L55" t="str">
-        <v>Autopilot - ALEXSUCKS</v>
+        <v>go again - NateTaylorr</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates)</v>
+        <v>Autopilot</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
+        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-28</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Portrait of My Heart - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G56" t="str">
-        <v>3:04</v>
+        <v>2:46</v>
       </c>
       <c r="H56" t="str">
-        <v>SPELLLING</v>
+        <v>ALEXSUCKS</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
+        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
       </c>
       <c r="L56" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
+        <v>Autopilot - ALEXSUCKS</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>In Violet</v>
+        <v>Portrait of My Heart (feat. Brendan Yates)</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
+        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-28</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Death in the Business of Whaling</v>
+        <v>Portrait of My Heart - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>4:09</v>
+        <v>3:04</v>
       </c>
       <c r="H57" t="str">
-        <v>Searows</v>
+        <v>SPELLLING</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/searows/1607240507</v>
+        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
+        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
       </c>
       <c r="L57" t="str">
-        <v>In Violet - Searows</v>
+        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Baby Run</v>
+        <v>In Violet</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
+        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-28</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Baby Run - Single</v>
+        <v>Death in the Business of Whaling</v>
       </c>
       <c r="G58" t="str">
-        <v>4:47</v>
+        <v>4:09</v>
       </c>
       <c r="H58" t="str">
-        <v>Jimi Jules</v>
+        <v>Searows</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
+        <v>https://music.apple.com/us/artist/searows/1607240507</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
+        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
       </c>
       <c r="L58" t="str">
-        <v>Baby Run - Jimi Jules</v>
+        <v>In Violet - Searows</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>What If We Don't</v>
+        <v>Baby Run</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
+        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-28</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>What If We Don't - Single</v>
+        <v>Baby Run - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>3:06</v>
+        <v>4:47</v>
       </c>
       <c r="H59" t="str">
-        <v>Ashley McBryde</v>
+        <v>Jimi Jules</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
+        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
       </c>
       <c r="L59" t="str">
-        <v>What If We Don't - Ashley McBryde</v>
+        <v>Baby Run - Jimi Jules</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Hagamos Que</v>
+        <v>What If We Don't</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
+        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-28</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Hagamos Que - Single</v>
+        <v>What If We Don't - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>2:58</v>
+        <v>3:06</v>
       </c>
       <c r="H60" t="str">
-        <v>Juanes</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
+        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
       </c>
       <c r="L60" t="str">
-        <v>Hagamos Que - Juanes</v>
+        <v>What If We Don't - Ashley McBryde</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>World Change Me</v>
+        <v>Hagamos Que</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
+        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-28</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>World Change Me - Single</v>
+        <v>Hagamos Que - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>3:03</v>
+        <v>2:58</v>
       </c>
       <c r="H61" t="str">
-        <v>Max McNown</v>
+        <v>Juanes</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
+        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
       </c>
       <c r="L61" t="str">
-        <v>World Change Me - Max McNown</v>
+        <v>Hagamos Que - Juanes</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Exclusive</v>
+        <v>World Change Me</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
+        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-28</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Exclusive - EP</v>
+        <v>World Change Me - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>3:20</v>
+        <v>3:03</v>
       </c>
       <c r="H62" t="str">
-        <v>Hudson Westbrook</v>
+        <v>Max McNown</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
+        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
       </c>
       <c r="L62" t="str">
-        <v>Exclusive - Hudson Westbrook</v>
+        <v>World Change Me - Max McNown</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Say Less</v>
+        <v>Exclusive</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/say-less/1867910122</v>
+        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-28</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Say Less - Single</v>
+        <v>Exclusive - EP</v>
       </c>
       <c r="G63" t="str">
-        <v>2:18</v>
+        <v>3:20</v>
       </c>
       <c r="H63" t="str">
-        <v>JYT</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/say-less/1867910115</v>
+        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
       </c>
       <c r="L63" t="str">
-        <v>Say Less - JYT</v>
+        <v>Exclusive - Hudson Westbrook</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Angels Cry</v>
+        <v>Say Less</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
+        <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-28</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>X's for Eyes (Deluxe)</v>
+        <v>Say Less - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>3:52</v>
+        <v>2:18</v>
       </c>
       <c r="H64" t="str">
-        <v>The Red Jumpsuit Apparatus</v>
+        <v>JYT</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
+        <v>https://music.apple.com/us/album/say-less/1867910115</v>
       </c>
       <c r="L64" t="str">
-        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
+        <v>Say Less - JYT</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Over You</v>
+        <v>Angels Cry</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/over-you/1846189473</v>
+        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-28</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>A Love For Strangers</v>
+        <v>X's for Eyes (Deluxe)</v>
       </c>
       <c r="G65" t="str">
-        <v>4:44</v>
+        <v>3:52</v>
       </c>
       <c r="H65" t="str">
-        <v>Chet Faker</v>
+        <v>The Red Jumpsuit Apparatus</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/over-you/1846189472</v>
+        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
       </c>
       <c r="L65" t="str">
-        <v>Over You - Chet Faker</v>
+        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Chala (My Soul Is on a Loop)</v>
+        <v>Over You</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
+        <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-28</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Chala (My Soul Is on a Loop) - Single</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G66" t="str">
-        <v>2:42</v>
+        <v>4:44</v>
       </c>
       <c r="H66" t="str">
-        <v>Barry Can't Swim</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
+        <v>https://music.apple.com/us/album/over-you/1846189472</v>
       </c>
       <c r="L66" t="str">
-        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
+        <v>Over You - Chet Faker</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>starlight feat. Madeline Follin</v>
+        <v>Chala (My Soul Is on a Loop)</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
+        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-28</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>starlight feat. Madeline Follin - Single</v>
+        <v>Chala (My Soul Is on a Loop) - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>3:06</v>
+        <v>2:42</v>
       </c>
       <c r="H67" t="str">
-        <v>Disco Lines</v>
+        <v>Barry Can't Swim</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
+        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
+        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
       </c>
       <c r="L67" t="str">
-        <v>starlight feat. Madeline Follin - Disco Lines</v>
+        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Locked In (feat. Trippie Redd)</v>
+        <v>starlight feat. Madeline Follin</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
+        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-28</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Locked In (feat. Trippie Redd) - Single</v>
+        <v>starlight feat. Madeline Follin - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>2:48</v>
+        <v>3:06</v>
       </c>
       <c r="H68" t="str">
-        <v>David Guetta</v>
+        <v>Disco Lines</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
+        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
+        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
       </c>
       <c r="L68" t="str">
-        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
+        <v>starlight feat. Madeline Follin - Disco Lines</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Rejoice</v>
+        <v>Locked In (feat. Trippie Redd)</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
+        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-28</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Rejoice - Single</v>
+        <v>Locked In (feat. Trippie Redd) - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>4:20</v>
+        <v>2:48</v>
       </c>
       <c r="H69" t="str">
-        <v>Def Leppard</v>
+        <v>David Guetta</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
+        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
+        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
       </c>
       <c r="L69" t="str">
-        <v>Rejoice - Def Leppard</v>
+        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
+        <v>Rejoice</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
+        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-28</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
+        <v>Rejoice - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>2:58</v>
+        <v>4:20</v>
       </c>
       <c r="H70" t="str">
-        <v>Honey Dijon</v>
+        <v>Def Leppard</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
+        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
       </c>
       <c r="L70" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
+        <v>Rejoice - Def Leppard</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Odisea</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/odisea/1866927906</v>
+        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-28</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Odisea - Single</v>
+        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>3:56</v>
+        <v>2:58</v>
       </c>
       <c r="H71" t="str">
-        <v>BASSYY</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/odisea/1866927904</v>
+        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
       </c>
       <c r="L71" t="str">
-        <v>Odisea - BASSYY</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Lucky Day</v>
+        <v>Odisea</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
+        <v>https://music.apple.com/us/song/odisea/1866927906</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-28</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Speed Kills</v>
+        <v>Odisea - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:13</v>
+        <v>3:56</v>
       </c>
       <c r="H72" t="str">
-        <v>Ally Evenson</v>
+        <v>BASSYY</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
+        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
+        <v>https://music.apple.com/us/album/odisea/1866927904</v>
       </c>
       <c r="L72" t="str">
-        <v>Lucky Day - Ally Evenson</v>
+        <v>Odisea - BASSYY</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Breathe On It</v>
+        <v>Lucky Day</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
+        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-28</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Breathe On It - Single</v>
+        <v>Speed Kills</v>
       </c>
       <c r="G73" t="str">
-        <v>4:00</v>
+        <v>3:13</v>
       </c>
       <c r="H73" t="str">
-        <v>Tauren Wells</v>
+        <v>Ally Evenson</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
+        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
       </c>
       <c r="L73" t="str">
-        <v>Breathe On It - Tauren Wells</v>
+        <v>Lucky Day - Ally Evenson</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Easy</v>
+        <v>Breathe On It</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/easy/1863456906</v>
+        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-28</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Easy - Single</v>
+        <v>Breathe On It - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>4:30</v>
+        <v>4:00</v>
       </c>
       <c r="H74" t="str">
-        <v>lydi lynn</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/easy/1863456903</v>
+        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
       </c>
       <c r="L74" t="str">
-        <v>Easy - lydi lynn</v>
+        <v>Breathe On It - Tauren Wells</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Break Me In</v>
+        <v>Easy</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
+        <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-28</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Break Me In - Single</v>
+        <v>Easy - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>2:52</v>
+        <v>4:30</v>
       </c>
       <c r="H75" t="str">
-        <v>Joyce Wrice</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
+        <v>https://music.apple.com/us/album/easy/1863456903</v>
       </c>
       <c r="L75" t="str">
-        <v>Break Me In - Joyce Wrice</v>
+        <v>Easy - lydi lynn</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Long Live Love</v>
+        <v>Break Me In</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
+        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-28</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Long Live Love - Single</v>
+        <v>Break Me In - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>2:36</v>
+        <v>2:52</v>
       </c>
       <c r="H76" t="str">
-        <v>Sugar</v>
+        <v>Joyce Wrice</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/sugar/530175867</v>
+        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
+        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
       </c>
       <c r="L76" t="str">
-        <v>Long Live Love - Sugar</v>
+        <v>Break Me In - Joyce Wrice</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Depressed</v>
+        <v>Long Live Love</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/depressed/1840400522</v>
+        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-28</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Boycott Heaven</v>
+        <v>Long Live Love - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>3:32</v>
+        <v>2:36</v>
       </c>
       <c r="H77" t="str">
-        <v>The Format</v>
+        <v>Sugar</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/the-format/3064903</v>
+        <v>https://music.apple.com/us/artist/sugar/530175867</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/depressed/1840399886</v>
+        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
       </c>
       <c r="L77" t="str">
-        <v>Depressed - The Format</v>
+        <v>Long Live Love - Sugar</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Empty Hands</v>
+        <v>Depressed</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
+        <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-28</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Empty Hands</v>
+        <v>Boycott Heaven</v>
       </c>
       <c r="G78" t="str">
-        <v>3:09</v>
+        <v>3:32</v>
       </c>
       <c r="H78" t="str">
-        <v>Poppy</v>
+        <v>The Format</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
+        <v>https://music.apple.com/us/artist/the-format/3064903</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
+        <v>https://music.apple.com/us/album/depressed/1840399886</v>
       </c>
       <c r="L78" t="str">
-        <v>Empty Hands - Poppy</v>
+        <v>Depressed - The Format</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>The Long Surrender</v>
+        <v>Empty Hands</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
+        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-28</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>The Long Surrender</v>
+        <v>Empty Hands</v>
       </c>
       <c r="G79" t="str">
-        <v>3:45</v>
+        <v>3:09</v>
       </c>
       <c r="H79" t="str">
-        <v>NEEDTOBREATHE</v>
+        <v>Poppy</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
+        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
+        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
       </c>
       <c r="L79" t="str">
-        <v>The Long Surrender - NEEDTOBREATHE</v>
+        <v>Empty Hands - Poppy</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Angela</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/angela/1866624257</v>
+        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-28</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Angela - Single</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="G80" t="str">
-        <v>3:32</v>
+        <v>3:45</v>
       </c>
       <c r="H80" t="str">
-        <v>Hayden Everett</v>
+        <v>NEEDTOBREATHE</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/angela/1866624256</v>
+        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
       </c>
       <c r="L80" t="str">
-        <v>Angela - Hayden Everett</v>
+        <v>The Long Surrender - NEEDTOBREATHE</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Disappear</v>
+        <v>Angela</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/disappear/1847663553</v>
+        <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-28</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Greyhound</v>
+        <v>Angela - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:31</v>
+        <v>3:32</v>
       </c>
       <c r="H81" t="str">
-        <v>Katie Tupper</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/disappear/1847663546</v>
+        <v>https://music.apple.com/us/album/angela/1866624256</v>
       </c>
       <c r="L81" t="str">
-        <v>Disappear - Katie Tupper</v>
+        <v>Angela - Hayden Everett</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Catapult</v>
+        <v>Disappear</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/catapult/1862951335</v>
+        <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-28</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Catapult - Single</v>
+        <v>Greyhound</v>
       </c>
       <c r="G82" t="str">
-        <v>2:57</v>
+        <v>3:31</v>
       </c>
       <c r="H82" t="str">
-        <v>Cape Francis</v>
+        <v>Katie Tupper</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
+        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/catapult/1862951333</v>
+        <v>https://music.apple.com/us/album/disappear/1847663546</v>
       </c>
       <c r="L82" t="str">
-        <v>Catapult - Cape Francis</v>
+        <v>Disappear - Katie Tupper</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Think Twice</v>
+        <v>Catapult</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
+        <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-28</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Think Twice - Single</v>
+        <v>Catapult - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>2:22</v>
+        <v>2:57</v>
       </c>
       <c r="H83" t="str">
-        <v>Leonie Biney</v>
+        <v>Cape Francis</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
+        <v>https://music.apple.com/us/album/catapult/1862951333</v>
       </c>
       <c r="L83" t="str">
-        <v>Think Twice - Leonie Biney</v>
+        <v>Catapult - Cape Francis</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>LOVESONGS</v>
+        <v>Think Twice</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
+        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-28</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>BEAUTIFUL MADNESS</v>
+        <v>Think Twice - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>3:33</v>
+        <v>2:22</v>
       </c>
       <c r="H84" t="str">
-        <v>Agnes</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/agnes/42568985</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
+        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
       </c>
       <c r="L84" t="str">
-        <v>LOVESONGS - Agnes</v>
+        <v>Think Twice - Leonie Biney</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Down South</v>
+        <v>LOVESONGS</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/down-south/1861010793</v>
+        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-28</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Down South - Single</v>
+        <v>BEAUTIFUL MADNESS</v>
       </c>
       <c r="G85" t="str">
-        <v>2:19</v>
+        <v>3:33</v>
       </c>
       <c r="H85" t="str">
-        <v>Trap Dickey</v>
+        <v>Agnes</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/agnes/42568985</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/down-south/1861010788</v>
+        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
       </c>
       <c r="L85" t="str">
-        <v>Down South - Trap Dickey</v>
+        <v>LOVESONGS - Agnes</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
+        <v>Down South</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
+        <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-28</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
+        <v>Down South - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>2:16</v>
+        <v>2:19</v>
       </c>
       <c r="H86" t="str">
-        <v>SALIMATA</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/salimata/690253822</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
+        <v>https://music.apple.com/us/album/down-south/1861010788</v>
       </c>
       <c r="L86" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
+        <v>Down South - Trap Dickey</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Love Like This</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
+        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-28</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Love Like This - Single</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>3:30</v>
+        <v>2:16</v>
       </c>
       <c r="H87" t="str">
-        <v>Jacob Banks</v>
+        <v>SALIMATA</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
+        <v>https://music.apple.com/us/artist/salimata/690253822</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
+        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
       </c>
       <c r="L87" t="str">
-        <v>Love Like This - Jacob Banks</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Plan Plan</v>
+        <v>Love Like This</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
+        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-28</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>La Locura, Vol. 1</v>
+        <v>Love Like This - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>3:10</v>
+        <v>3:30</v>
       </c>
       <c r="H88" t="str">
-        <v>Funky</v>
+        <v>Jacob Banks</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/funky/80960663</v>
+        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
+        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
       </c>
       <c r="L88" t="str">
-        <v>Plan Plan - Funky</v>
+        <v>Love Like This - Jacob Banks</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>double edged sword</v>
+        <v>Plan Plan</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
+        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-28</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>double edged sword - Single</v>
+        <v>La Locura, Vol. 1</v>
       </c>
       <c r="G89" t="str">
-        <v>3:28</v>
+        <v>3:10</v>
       </c>
       <c r="H89" t="str">
-        <v>Hailey Picardi</v>
+        <v>Funky</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/funky/80960663</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
+        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
       </c>
       <c r="L89" t="str">
-        <v>double edged sword - Hailey Picardi</v>
+        <v>Plan Plan - Funky</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>SOMEWHERE IN BETWEEN</v>
+        <v>double edged sword</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
+        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-28</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>SOMEWHERE IN BETWEEN - Single</v>
+        <v>double edged sword - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>3:27</v>
+        <v>3:28</v>
       </c>
       <c r="H90" t="str">
-        <v>Matt Hansen</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
+        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
       </c>
       <c r="L90" t="str">
-        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
+        <v>double edged sword - Hailey Picardi</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>The Decay</v>
+        <v>SOMEWHERE IN BETWEEN</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
+        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-28</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>What Remains (Midnight Edition)</v>
+        <v>SOMEWHERE IN BETWEEN - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>3:20</v>
+        <v>3:27</v>
       </c>
       <c r="H91" t="str">
-        <v>Pop Evil</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
+        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
+        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
       </c>
       <c r="L91" t="str">
-        <v>The Decay - Pop Evil</v>
+        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>3111</v>
+        <v>The Decay</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/3111/1862225387</v>
+        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-28</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Goliath</v>
+        <v>What Remains (Midnight Edition)</v>
       </c>
       <c r="G92" t="str">
-        <v>4:08</v>
+        <v>3:20</v>
       </c>
       <c r="H92" t="str">
-        <v>Exodus</v>
+        <v>Pop Evil</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/3111/1862225385</v>
+        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
       </c>
       <c r="L92" t="str">
-        <v>3111 - Exodus</v>
+        <v>The Decay - Pop Evil</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Touch My Love And Die</v>
+        <v>3111</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+        <v>https://music.apple.com/us/song/3111/1862225387</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-28</v>
@@ -3909,68 +3909,106 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Touch My Love And Die - Single</v>
+        <v>Goliath</v>
       </c>
       <c r="G93" t="str">
-        <v>2:57</v>
+        <v>4:08</v>
       </c>
       <c r="H93" t="str">
-        <v>Myrkur</v>
+        <v>Exodus</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+        <v>https://music.apple.com/us/album/3111/1862225385</v>
       </c>
       <c r="L93" t="str">
-        <v>Touch My Love And Die - Myrkur</v>
+        <v>3111 - Exodus</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
+        <v>Touch My Love And Die</v>
+      </c>
+      <c r="B94" t="str">
+        <v/>
+      </c>
+      <c r="C94" t="str">
+        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+      </c>
+      <c r="D94" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v>Touch My Love And Die - Single</v>
+      </c>
+      <c r="G94" t="str">
+        <v>2:57</v>
+      </c>
+      <c r="H94" t="str">
+        <v>Myrkur</v>
+      </c>
+      <c r="I94" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J94" t="str">
+        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+      </c>
+      <c r="K94" t="str">
+        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+      </c>
+      <c r="L94" t="str">
+        <v>Touch My Love And Die - Myrkur</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
         <v>Bomb To A Knife Fight</v>
       </c>
-      <c r="B94" t="str">
-        <v/>
-      </c>
-      <c r="C94" t="str">
+      <c r="B95" t="str">
+        <v/>
+      </c>
+      <c r="C95" t="str">
         <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
-      <c r="D94" t="str">
-        <v>2026-01-28</v>
-      </c>
-      <c r="E94" t="str">
-        <v/>
-      </c>
-      <c r="F94" t="str">
+      <c r="D95" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
         <v>Bomb To A Knife Fight - Single</v>
       </c>
-      <c r="G94" t="str">
+      <c r="G95" t="str">
         <v>2:41</v>
       </c>
-      <c r="H94" t="str">
+      <c r="H95" t="str">
         <v>The Barbarians of California</v>
       </c>
-      <c r="I94" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J94" t="str">
+      <c r="I95" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J95" t="str">
         <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
       </c>
-      <c r="K94" t="str">
+      <c r="K95" t="str">
         <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
       </c>
-      <c r="L94" t="str">
+      <c r="L95" t="str">
         <v>Bomb To A Knife Fight - The Barbarians of California</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L94"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L95"/>
   </ignoredErrors>
 </worksheet>
 </file>